--- a/DATA624/project_1/Waterflow_Pipe1.xlsx
+++ b/DATA624/project_1/Waterflow_Pipe1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="19029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeffrey Nieman\Documents\CUNY\Data 624\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/olivia/Documents/CUNY/CUNY_GITHUB_submissions/DATA624/project_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E2B6CA-F870-274B-B04E-0C6B266F318B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7680"/>
+    <workbookView xWindow="0" yWindow="7640" windowWidth="20500" windowHeight="7680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Waterflow_Pipe1" sheetId="1" r:id="rId1"/>
@@ -30,9 +31,10 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm\ AM/PM"/>
+    <numFmt numFmtId="166" formatCode="m/d/yy\ h:mm;@"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -61,14 +63,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="4">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -89,9 +94,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -129,9 +134,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -164,26 +169,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -216,26 +204,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -408,23 +379,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B1001"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>42300.016741832398</v>
       </c>
@@ -432,7 +403,7 @@
         <v>23.369599369548201</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>42300.027811016102</v>
       </c>
@@ -440,7 +411,7 @@
         <v>28.002880634854002</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>42300.037400938199</v>
       </c>
@@ -448,7 +419,7 @@
         <v>23.065894786548402</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>42300.038663751096</v>
       </c>
@@ -456,7 +427,7 @@
         <v>29.972809230763801</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>42300.055060123399</v>
       </c>
@@ -464,7 +435,7 @@
         <v>5.9979531587222699</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>42300.058316777002</v>
       </c>
@@ -472,7 +443,7 @@
         <v>15.935222578465</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>42300.076449199798</v>
       </c>
@@ -480,7 +451,7 @@
         <v>26.6173303418202</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>42300.080252982101</v>
       </c>
@@ -488,7 +459,7 @@
         <v>33.282899655888997</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>42300.082823860903</v>
       </c>
@@ -496,7 +467,7 @@
         <v>12.426691575101</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>42300.119344038001</v>
       </c>
@@ -504,7 +475,7 @@
         <v>21.8334936238113</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>42300.124883340002</v>
       </c>
@@ -512,7 +483,7 @@
         <v>8.4836466894997091</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>42300.135191670401</v>
       </c>
@@ -520,7 +491,7 @@
         <v>29.336901257576699</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>42300.137605514203</v>
       </c>
@@ -528,7 +499,7 @@
         <v>19.809145724297199</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>42300.140436003901</v>
       </c>
@@ -536,7 +507,7 @@
         <v>31.019743940177499</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>42300.157610812901</v>
       </c>
@@ -544,7 +515,7 @@
         <v>18.339962465174899</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>42300.166215283898</v>
       </c>
@@ -552,7 +523,7 @@
         <v>16.888526815699802</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>42300.174891215203</v>
       </c>
@@ -560,7 +531,7 @@
         <v>13.664312428546401</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>42300.198424494301</v>
       </c>
@@ -568,7 +539,7 @@
         <v>17.300073872556101</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>42300.212290127798</v>
       </c>
@@ -576,7 +547,7 @@
         <v>23.260983935177201</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>42300.217931498097</v>
       </c>
@@ -584,7 +555,7 @@
         <v>8.1524963085363602</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>42300.218503488497</v>
       </c>
@@ -592,7 +563,7 @@
         <v>19.875627779135598</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>42300.219228322901</v>
       </c>
@@ -600,7 +571,7 @@
         <v>32.886498894240901</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>42300.220111249298</v>
       </c>
@@ -608,7 +579,7 @@
         <v>22.2603644393994</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>42300.230968645599</v>
       </c>
@@ -616,7 +587,7 @@
         <v>5.7783688470541303</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>42300.2381040576</v>
       </c>
@@ -624,7 +595,7 @@
         <v>32.545556689785897</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>42300.239242040698</v>
       </c>
@@ -632,7 +603,7 @@
         <v>30.687744127799899</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A28">
         <v>42300.240185819799</v>
       </c>
@@ -640,7 +611,7 @@
         <v>29.080906618329301</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>42300.252528563797</v>
       </c>
@@ -648,7 +619,7 @@
         <v>30.047784482157599</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A30">
         <v>42300.261991667699</v>
       </c>
@@ -656,7 +627,7 @@
         <v>5.7524558105313899</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A31">
         <v>42300.273136446798</v>
       </c>
@@ -664,7 +635,7 @@
         <v>30.414162159526601</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A32">
         <v>42300.273366511399</v>
       </c>
@@ -672,7 +643,7 @@
         <v>26.1757160466797</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A33">
         <v>42300.276743519797</v>
       </c>
@@ -680,7 +651,7 @@
         <v>27.155306641106101</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A34">
         <v>42300.279438362297</v>
       </c>
@@ -688,7 +659,7 @@
         <v>13.605942892145899</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A35">
         <v>42300.289154064201</v>
       </c>
@@ -696,7 +667,7 @@
         <v>11.184568391501999</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A36">
         <v>42300.291314187802</v>
       </c>
@@ -704,7 +675,7 @@
         <v>20.383057348690901</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A37">
         <v>42300.317064540897</v>
       </c>
@@ -712,7 +683,7 @@
         <v>13.405331121503</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A38">
         <v>42300.330362435503</v>
       </c>
@@ -720,7 +691,7 @@
         <v>14.4610914444517</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A39">
         <v>42300.331045444203</v>
       </c>
@@ -728,7 +699,7 @@
         <v>27.234671318413302</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A40">
         <v>42300.341235273103</v>
       </c>
@@ -736,7 +707,7 @@
         <v>9.08949772483078</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A41">
         <v>42300.351909953097</v>
       </c>
@@ -744,7 +715,7 @@
         <v>29.162384438702201</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A42">
         <v>42300.373947374399</v>
       </c>
@@ -752,7 +723,7 @@
         <v>24.123214124922299</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A43">
         <v>42300.3756878813</v>
       </c>
@@ -760,7 +731,7 @@
         <v>6.2074432930130001</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A44">
         <v>42300.382994721898</v>
       </c>
@@ -768,7 +739,7 @@
         <v>27.666922710690798</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A45">
         <v>42300.399831637696</v>
       </c>
@@ -776,7 +747,7 @@
         <v>29.781898041936302</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A46">
         <v>42300.4173896348</v>
       </c>
@@ -784,7 +755,7 @@
         <v>19.035462847917501</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A47">
         <v>42300.420727359997</v>
       </c>
@@ -792,7 +763,7 @@
         <v>14.539054714059301</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A48">
         <v>42300.441386214203</v>
       </c>
@@ -800,7 +771,7 @@
         <v>16.304828676353399</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A49">
         <v>42300.460086911502</v>
       </c>
@@ -808,7 +779,7 @@
         <v>9.0895996301509303</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A50">
         <v>42300.460989619198</v>
       </c>
@@ -816,7 +787,7 @@
         <v>24.160478289071801</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A51">
         <v>42300.485019633197</v>
       </c>
@@ -824,7 +795,7 @@
         <v>33.013436312853401</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A52">
         <v>42300.503859521297</v>
       </c>
@@ -832,7 +803,7 @@
         <v>14.9247575870736</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A53">
         <v>42300.524889279397</v>
       </c>
@@ -840,7 +811,7 @@
         <v>20.688466354515199</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A54">
         <v>42300.535590558102</v>
       </c>
@@ -848,7 +819,7 @@
         <v>25.3963058528891</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A55">
         <v>42300.564858339698</v>
       </c>
@@ -856,7 +827,7 @@
         <v>21.6618002863848</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A56">
         <v>42300.568459633898</v>
       </c>
@@ -864,7 +835,7 @@
         <v>23.214093387684802</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A57">
         <v>42300.571550563203</v>
       </c>
@@ -872,7 +843,7 @@
         <v>3.8111889380733799</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A58">
         <v>42300.585393872898</v>
       </c>
@@ -880,7 +851,7 @@
         <v>37.300056158799997</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A59">
         <v>42300.589691940797</v>
       </c>
@@ -888,7 +859,7 @@
         <v>26.468500471591302</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A60">
         <v>42300.5908283639</v>
       </c>
@@ -896,7 +867,7 @@
         <v>30.5322298292255</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A61">
         <v>42300.601062989401</v>
       </c>
@@ -904,7 +875,7 @@
         <v>10.9108862594819</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A62">
         <v>42300.6084001165</v>
       </c>
@@ -912,7 +883,7 @@
         <v>31.534557109902298</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A63">
         <v>42300.616552448999</v>
       </c>
@@ -920,7 +891,7 @@
         <v>13.5525253191426</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A64">
         <v>42300.635023095601</v>
       </c>
@@ -928,7 +899,7 @@
         <v>27.485792346434799</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A65">
         <v>42300.650633617901</v>
       </c>
@@ -936,7 +907,7 @@
         <v>19.1367873766585</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A66">
         <v>42300.652286058998</v>
       </c>
@@ -944,7 +915,7 @@
         <v>26.371215265967599</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A67">
         <v>42300.6610955746</v>
       </c>
@@ -952,7 +923,7 @@
         <v>17.623757439674499</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A68">
         <v>42300.669255827997</v>
       </c>
@@ -960,7 +931,7 @@
         <v>26.7045836941756</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A69">
         <v>42300.676789506098</v>
       </c>
@@ -968,7 +939,7 @@
         <v>36.172464859979002</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A70">
         <v>42300.693015837503</v>
       </c>
@@ -976,7 +947,7 @@
         <v>24.153053803839502</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A71">
         <v>42300.693807284799</v>
       </c>
@@ -984,7 +955,7 @@
         <v>27.510916878668599</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A72">
         <v>42300.696284407401</v>
       </c>
@@ -992,7 +963,7 @@
         <v>34.642727852161897</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A73">
         <v>42300.699395485899</v>
       </c>
@@ -1000,7 +971,7 @@
         <v>16.144607221843501</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A74">
         <v>42300.7206270803</v>
       </c>
@@ -1008,7 +979,7 @@
         <v>18.210856666752498</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A75">
         <v>42300.728828717001</v>
       </c>
@@ -1016,7 +987,7 @@
         <v>7.4859773257319198</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A76">
         <v>42300.729794680199</v>
       </c>
@@ -1024,7 +995,7 @@
         <v>14.8215544223004</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A77">
         <v>42300.756216209498</v>
       </c>
@@ -1032,7 +1003,7 @@
         <v>15.4463367596914</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A78">
         <v>42300.761181835398</v>
       </c>
@@ -1040,7 +1011,7 @@
         <v>21.0848919359109</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A79">
         <v>42300.763305954097</v>
       </c>
@@ -1048,7 +1019,7 @@
         <v>32.985345676427002</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A80">
         <v>42300.789805584202</v>
       </c>
@@ -1056,7 +1027,7 @@
         <v>13.2702444903416</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A81">
         <v>42300.813982952001</v>
       </c>
@@ -1064,7 +1035,7 @@
         <v>15.531714158223799</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A82">
         <v>42300.8323171831</v>
       </c>
@@ -1072,7 +1043,7 @@
         <v>22.6788738219553</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A83">
         <v>42300.832379069499</v>
       </c>
@@ -1080,7 +1051,7 @@
         <v>19.404605184398299</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A84">
         <v>42300.843509455102</v>
       </c>
@@ -1088,7 +1059,7 @@
         <v>23.9967450498246</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A85">
         <v>42300.849725521301</v>
       </c>
@@ -1096,7 +1067,7 @@
         <v>18.409485092762001</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A86">
         <v>42300.852826038601</v>
       </c>
@@ -1104,7 +1075,7 @@
         <v>21.7493918392334</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A87">
         <v>42300.853194237003</v>
       </c>
@@ -1112,7 +1083,7 @@
         <v>25.759675069513001</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A88">
         <v>42300.8584972764</v>
       </c>
@@ -1120,7 +1091,7 @@
         <v>20.225868932529799</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A89">
         <v>42300.862690998903</v>
       </c>
@@ -1128,7 +1099,7 @@
         <v>16.523979010311098</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A90">
         <v>42300.865298338998</v>
       </c>
@@ -1136,7 +1107,7 @@
         <v>9.3281236723486796</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A91">
         <v>42300.869391292297</v>
       </c>
@@ -1144,7 +1115,7 @@
         <v>30.186020874330701</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A92">
         <v>42300.910530480302</v>
       </c>
@@ -1152,7 +1123,7 @@
         <v>15.0925127057655</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A93">
         <v>42300.926182041301</v>
       </c>
@@ -1160,7 +1131,7 @@
         <v>16.576799409942701</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A94">
         <v>42300.929378536101</v>
       </c>
@@ -1168,7 +1139,7 @@
         <v>20.8019563034951</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A95">
         <v>42300.960476641398</v>
       </c>
@@ -1176,7 +1147,7 @@
         <v>33.220434348907801</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A96">
         <v>42300.966301198197</v>
       </c>
@@ -1184,7 +1155,7 @@
         <v>3.4689863002224999</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A97">
         <v>42300.979175741399</v>
       </c>
@@ -1192,7 +1163,7 @@
         <v>24.9802535508394</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A98">
         <v>42301.001178359198</v>
       </c>
@@ -1200,7 +1171,7 @@
         <v>14.8990844685688</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A99">
         <v>42301.008161001701</v>
       </c>
@@ -1208,7 +1179,7 @@
         <v>18.882710153716801</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A100">
         <v>42301.013578025697</v>
       </c>
@@ -1216,7 +1187,7 @@
         <v>14.917665639893</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A101">
         <v>42301.027619460299</v>
       </c>
@@ -1224,7 +1195,7 @@
         <v>14.611356510764599</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A102">
         <v>42301.0349295325</v>
       </c>
@@ -1232,7 +1203,7 @@
         <v>8.2917812954640997</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A103">
         <v>42301.042470670604</v>
       </c>
@@ -1240,7 +1211,7 @@
         <v>32.224858644936702</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A104">
         <v>42301.044858581801</v>
       </c>
@@ -1248,7 +1219,7 @@
         <v>12.116039940092399</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A105">
         <v>42301.047849747803</v>
       </c>
@@ -1256,7 +1227,7 @@
         <v>3.5402290620466101</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A106">
         <v>42301.051026810601</v>
       </c>
@@ -1264,7 +1235,7 @@
         <v>29.955001597374299</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A107">
         <v>42301.0525073155</v>
       </c>
@@ -1272,7 +1243,7 @@
         <v>10.6854791139559</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A108">
         <v>42301.058040424199</v>
       </c>
@@ -1280,7 +1251,7 @@
         <v>4.3338589595528401</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A109">
         <v>42301.066442597999</v>
       </c>
@@ -1288,7 +1259,7 @@
         <v>31.9067316279151</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A110">
         <v>42301.068056472897</v>
       </c>
@@ -1296,7 +1267,7 @@
         <v>19.8585551269246</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A111">
         <v>42301.093623104003</v>
       </c>
@@ -1304,7 +1275,7 @@
         <v>27.8236416191838</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A112">
         <v>42301.107989477103</v>
       </c>
@@ -1312,7 +1283,7 @@
         <v>30.243204185120899</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A113">
         <v>42301.122882820397</v>
       </c>
@@ -1320,7 +1291,7 @@
         <v>27.224878787116499</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A114">
         <v>42301.136335300602</v>
       </c>
@@ -1328,7 +1299,7 @@
         <v>17.3596299419033</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A115">
         <v>42301.139095633698</v>
       </c>
@@ -1336,7 +1307,7 @@
         <v>23.114635750997799</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A116">
         <v>42301.1457866977</v>
       </c>
@@ -1344,7 +1315,7 @@
         <v>17.968615818457799</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A117">
         <v>42301.152890076897</v>
       </c>
@@ -1352,7 +1323,7 @@
         <v>18.797541362136101</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A118">
         <v>42301.156465661901</v>
       </c>
@@ -1360,7 +1331,7 @@
         <v>15.5434720875673</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A119">
         <v>42301.168900076002</v>
       </c>
@@ -1368,7 +1339,7 @@
         <v>21.289698439475298</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A120">
         <v>42301.170593932999</v>
       </c>
@@ -1376,7 +1347,7 @@
         <v>14.368193690337501</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A121">
         <v>42301.171652399702</v>
       </c>
@@ -1384,7 +1355,7 @@
         <v>37.5291079888</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A122">
         <v>42301.172182578397</v>
       </c>
@@ -1392,7 +1363,7 @@
         <v>22.4038612397053</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A123">
         <v>42301.172286574598</v>
       </c>
@@ -1400,7 +1371,7 @@
         <v>29.8257190711732</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A124">
         <v>42301.176402368597</v>
       </c>
@@ -1408,7 +1379,7 @@
         <v>28.8570147346921</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A125">
         <v>42301.187953558299</v>
       </c>
@@ -1416,7 +1387,7 @@
         <v>31.655558734537301</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A126">
         <v>42301.232323523</v>
       </c>
@@ -1424,7 +1395,7 @@
         <v>20.618726868458001</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A127">
         <v>42301.242385164704</v>
       </c>
@@ -1432,7 +1403,7 @@
         <v>19.8953068587468</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A128">
         <v>42301.270011881301</v>
       </c>
@@ -1440,7 +1411,7 @@
         <v>17.667198098130399</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A129">
         <v>42301.280249626798</v>
       </c>
@@ -1448,7 +1419,7 @@
         <v>19.604547781118502</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A130">
         <v>42301.285587250903</v>
       </c>
@@ -1456,7 +1427,7 @@
         <v>13.292334466170701</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A131">
         <v>42301.307260836998</v>
       </c>
@@ -1464,7 +1435,7 @@
         <v>32.916567874098298</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A132">
         <v>42301.321536582996</v>
       </c>
@@ -1472,7 +1443,7 @@
         <v>30.5309475283746</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A133">
         <v>42301.323971046397</v>
       </c>
@@ -1480,7 +1451,7 @@
         <v>15.6303199234312</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A134">
         <v>42301.326454543901</v>
       </c>
@@ -1488,7 +1459,7 @@
         <v>36.094851199566499</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A135">
         <v>42301.330066976603</v>
       </c>
@@ -1496,7 +1467,7 @@
         <v>14.7279940042084</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A136">
         <v>42301.339784708704</v>
       </c>
@@ -1504,7 +1475,7 @@
         <v>35.6152301129394</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A137">
         <v>42301.342727483301</v>
       </c>
@@ -1512,7 +1483,7 @@
         <v>3.3742298217534699</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A138">
         <v>42301.348714984299</v>
       </c>
@@ -1520,7 +1491,7 @@
         <v>28.9943931086564</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A139">
         <v>42301.354248814801</v>
       </c>
@@ -1528,7 +1499,7 @@
         <v>8.7090733276080492</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A140">
         <v>42301.3586572723</v>
       </c>
@@ -1536,7 +1507,7 @@
         <v>12.1661285563004</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A141">
         <v>42301.372176323399</v>
       </c>
@@ -1544,7 +1515,7 @@
         <v>25.880771642488199</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A142">
         <v>42301.374413500002</v>
       </c>
@@ -1552,7 +1523,7 @@
         <v>15.914648115981899</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A143">
         <v>42301.377684547202</v>
       </c>
@@ -1560,7 +1531,7 @@
         <v>35.387907003970902</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A144">
         <v>42301.385105712201</v>
       </c>
@@ -1568,7 +1539,7 @@
         <v>32.5886616436933</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A145">
         <v>42301.391081674097</v>
       </c>
@@ -1576,7 +1547,7 @@
         <v>9.7152060669811995</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A146">
         <v>42301.3972963899</v>
       </c>
@@ -1584,7 +1555,7 @@
         <v>19.9909021329259</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A147">
         <v>42301.405143309101</v>
       </c>
@@ -1592,7 +1563,7 @@
         <v>35.738927897908198</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A148">
         <v>42301.417024736496</v>
       </c>
@@ -1600,7 +1571,7 @@
         <v>12.3022665761843</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A149">
         <v>42301.418724125499</v>
       </c>
@@ -1608,7 +1579,7 @@
         <v>17.440708588091798</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A150">
         <v>42301.425700509499</v>
       </c>
@@ -1616,7 +1587,7 @@
         <v>8.1915736926178297</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A151">
         <v>42301.439445071097</v>
       </c>
@@ -1624,7 +1595,7 @@
         <v>5.7444456351352304</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A152">
         <v>42301.446862478297</v>
       </c>
@@ -1632,7 +1603,7 @@
         <v>5.6118526016396801</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A153">
         <v>42301.491739455101</v>
       </c>
@@ -1640,7 +1611,7 @@
         <v>13.5736406844852</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A154">
         <v>42301.509739695299</v>
       </c>
@@ -1648,7 +1619,7 @@
         <v>8.3475355010202694</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A155">
         <v>42301.512394830803</v>
       </c>
@@ -1656,7 +1627,7 @@
         <v>5.1365415642997396</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A156">
         <v>42301.517204143602</v>
       </c>
@@ -1664,7 +1635,7 @@
         <v>20.7095640061018</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A157">
         <v>42301.5254818553</v>
       </c>
@@ -1672,7 +1643,7 @@
         <v>7.5652463282672402</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A158">
         <v>42301.536688804903</v>
       </c>
@@ -1680,7 +1651,7 @@
         <v>29.6240845034119</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A159">
         <v>42301.541946260797</v>
       </c>
@@ -1688,7 +1659,7 @@
         <v>29.713120612136699</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A160">
         <v>42301.550128353701</v>
       </c>
@@ -1696,7 +1667,7 @@
         <v>18.4567765001329</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A161">
         <v>42301.558282357902</v>
       </c>
@@ -1704,7 +1675,7 @@
         <v>11.26464816625</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A162">
         <v>42301.576639988503</v>
       </c>
@@ -1712,7 +1683,7 @@
         <v>12.5246917198407</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A163">
         <v>42301.576662684798</v>
       </c>
@@ -1720,7 +1691,7 @@
         <v>13.847150391436999</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A164">
         <v>42301.620166314598</v>
       </c>
@@ -1728,7 +1699,7 @@
         <v>11.8447613282151</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A165">
         <v>42301.654491117501</v>
       </c>
@@ -1736,7 +1707,7 @@
         <v>13.688624670511601</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A166">
         <v>42301.667978075202</v>
       </c>
@@ -1744,7 +1715,7 @@
         <v>14.0145482361487</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A167">
         <v>42301.674929434601</v>
       </c>
@@ -1752,7 +1723,7 @@
         <v>19.487639766395699</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A168">
         <v>42301.686969955197</v>
       </c>
@@ -1760,7 +1731,7 @@
         <v>13.4936705822879</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A169">
         <v>42301.688280340102</v>
       </c>
@@ -1768,7 +1739,7 @@
         <v>30.5730251216829</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A170">
         <v>42301.697050805298</v>
       </c>
@@ -1776,7 +1747,7 @@
         <v>30.0701325740485</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A171">
         <v>42301.698064875898</v>
       </c>
@@ -1784,7 +1755,7 @@
         <v>23.0013588793182</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A172">
         <v>42301.699046457397</v>
       </c>
@@ -1792,7 +1763,7 @@
         <v>15.6406814090246</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A173">
         <v>42301.7046320554</v>
       </c>
@@ -1800,7 +1771,7 @@
         <v>15.5412551672229</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A174">
         <v>42301.719874332703</v>
       </c>
@@ -1808,7 +1779,7 @@
         <v>13.0103823476855</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A175">
         <v>42301.723329269596</v>
       </c>
@@ -1816,7 +1787,7 @@
         <v>21.034331213644801</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A176">
         <v>42301.728958858599</v>
       </c>
@@ -1824,7 +1795,7 @@
         <v>10.533891075933701</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A177">
         <v>42301.7312216094</v>
       </c>
@@ -1832,7 +1803,7 @@
         <v>16.163424949111</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A178">
         <v>42301.731976334602</v>
       </c>
@@ -1840,7 +1811,7 @@
         <v>9.2056558851528703</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A179">
         <v>42301.739477192903</v>
       </c>
@@ -1848,7 +1819,7 @@
         <v>21.880139959888499</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A180">
         <v>42301.751668052202</v>
       </c>
@@ -1856,7 +1827,7 @@
         <v>21.0990172035137</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A181">
         <v>42301.755892918103</v>
       </c>
@@ -1864,7 +1835,7 @@
         <v>23.8384309533362</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A182">
         <v>42301.756309903802</v>
       </c>
@@ -1872,7 +1843,7 @@
         <v>13.840717485389201</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A183">
         <v>42301.780123874203</v>
       </c>
@@ -1880,7 +1851,7 @@
         <v>13.500420268408799</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A184">
         <v>42301.786656366603</v>
       </c>
@@ -1888,7 +1859,7 @@
         <v>9.0277800743287901</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A185">
         <v>42301.793796872902</v>
       </c>
@@ -1896,7 +1867,7 @@
         <v>25.1060916548678</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A186">
         <v>42301.803986878796</v>
       </c>
@@ -1904,7 +1875,7 @@
         <v>26.2025010805636</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A187">
         <v>42301.805891698903</v>
       </c>
@@ -1912,7 +1883,7 @@
         <v>26.414528100395099</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A188">
         <v>42301.815930271703</v>
       </c>
@@ -1920,7 +1891,7 @@
         <v>13.367799462873</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A189">
         <v>42301.837284297799</v>
       </c>
@@ -1928,7 +1899,7 @@
         <v>19.210335953570201</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A190">
         <v>42301.837860204403</v>
       </c>
@@ -1936,7 +1907,7 @@
         <v>9.5135091564842895</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A191">
         <v>42301.839318394799</v>
       </c>
@@ -1944,7 +1915,7 @@
         <v>19.588525707379301</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A192">
         <v>42301.8425525895</v>
       </c>
@@ -1952,7 +1923,7 @@
         <v>25.1827409679689</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A193">
         <v>42301.848274528602</v>
       </c>
@@ -1960,7 +1931,7 @@
         <v>25.7064753794346</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A194">
         <v>42301.872009839499</v>
       </c>
@@ -1968,7 +1939,7 @@
         <v>13.2416927002109</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A195">
         <v>42301.8761945281</v>
       </c>
@@ -1976,7 +1947,7 @@
         <v>15.249657508088699</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A196">
         <v>42301.882629534201</v>
       </c>
@@ -1984,7 +1955,7 @@
         <v>18.650854316224599</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A197">
         <v>42301.904854244502</v>
       </c>
@@ -1992,7 +1963,7 @@
         <v>11.663894751775601</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A198">
         <v>42301.9094553088</v>
       </c>
@@ -2000,7 +1971,7 @@
         <v>15.967304388629699</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A199">
         <v>42301.932480579402</v>
       </c>
@@ -2008,7 +1979,7 @@
         <v>26.243780381382098</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A200">
         <v>42301.934221412201</v>
       </c>
@@ -2016,7 +1987,7 @@
         <v>22.1975604010712</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A201">
         <v>42301.947355263597</v>
       </c>
@@ -2024,7 +1995,7 @@
         <v>11.2072572170835</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A202">
         <v>42301.9492976068</v>
       </c>
@@ -2032,7 +2003,7 @@
         <v>21.145070305713901</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A203">
         <v>42301.9493007454</v>
       </c>
@@ -2040,7 +2011,7 @@
         <v>19.284440418322301</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A204">
         <v>42301.956310722198</v>
       </c>
@@ -2048,7 +2019,7 @@
         <v>14.163063216889499</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A205">
         <v>42301.969759179003</v>
       </c>
@@ -2056,7 +2027,7 @@
         <v>9.4506200325222203</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A206">
         <v>42301.970181743403</v>
       </c>
@@ -2064,7 +2035,7 @@
         <v>18.434139623726701</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A207">
         <v>42302.000802541203</v>
       </c>
@@ -2072,7 +2043,7 @@
         <v>24.417248226453601</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A208">
         <v>42302.010737774399</v>
       </c>
@@ -2080,7 +2051,7 @@
         <v>22.3286966038585</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A209">
         <v>42302.0122786383</v>
       </c>
@@ -2088,7 +2059,7 @@
         <v>27.5694249120546</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A210">
         <v>42302.016896042704</v>
       </c>
@@ -2096,7 +2067,7 @@
         <v>18.778383702115399</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A211">
         <v>42302.027792987603</v>
       </c>
@@ -2104,7 +2075,7 @@
         <v>29.6953686159599</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A212">
         <v>42302.035861929398</v>
       </c>
@@ -2112,7 +2083,7 @@
         <v>28.2247151616499</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A213">
         <v>42302.039449304997</v>
       </c>
@@ -2120,7 +2091,7 @@
         <v>20.568090336531299</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A214">
         <v>42302.0437620784</v>
       </c>
@@ -2128,7 +2099,7 @@
         <v>12.528874215183</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A215">
         <v>42302.048027745499</v>
       </c>
@@ -2136,7 +2107,7 @@
         <v>23.4162977293065</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A216">
         <v>42302.058649815102</v>
       </c>
@@ -2144,7 +2115,7 @@
         <v>35.774202496189297</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A217">
         <v>42302.062726763703</v>
       </c>
@@ -2152,7 +2123,7 @@
         <v>35.017588379092103</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A218">
         <v>42302.067207058797</v>
       </c>
@@ -2160,7 +2131,7 @@
         <v>15.854555548931099</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A219">
         <v>42302.079083629302</v>
       </c>
@@ -2168,7 +2139,7 @@
         <v>24.5835997674642</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A220">
         <v>42302.081732632098</v>
       </c>
@@ -2176,7 +2147,7 @@
         <v>16.582312495213301</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A221">
         <v>42302.084316228102</v>
       </c>
@@ -2184,7 +2155,7 @@
         <v>36.785130746074103</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A222">
         <v>42302.090049142796</v>
       </c>
@@ -2192,7 +2163,7 @@
         <v>11.396241247970799</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A223">
         <v>42302.123171738604</v>
       </c>
@@ -2200,7 +2171,7 @@
         <v>21.786938957818698</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A224">
         <v>42302.125986833496</v>
       </c>
@@ -2208,7 +2179,7 @@
         <v>19.484790468684999</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A225">
         <v>42302.159335126002</v>
       </c>
@@ -2216,7 +2187,7 @@
         <v>17.895141840487302</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A226">
         <v>42302.181094086402</v>
       </c>
@@ -2224,7 +2195,7 @@
         <v>29.726704241135099</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A227">
         <v>42302.186250996703</v>
       </c>
@@ -2232,7 +2203,7 @@
         <v>6.3652521842375602</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A228">
         <v>42302.202120370799</v>
       </c>
@@ -2240,7 +2211,7 @@
         <v>23.272000643480599</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A229">
         <v>42302.219628220701</v>
       </c>
@@ -2248,7 +2219,7 @@
         <v>11.154272802226799</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A230">
         <v>42302.233012812103</v>
       </c>
@@ -2256,7 +2227,7 @@
         <v>29.477854047723898</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A231">
         <v>42302.244335478499</v>
       </c>
@@ -2264,7 +2235,7 @@
         <v>19.357379537717101</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A232">
         <v>42302.247649306002</v>
       </c>
@@ -2272,7 +2243,7 @@
         <v>35.990674001726902</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A233">
         <v>42302.254241039802</v>
       </c>
@@ -2280,7 +2251,7 @@
         <v>3.8762208770396098</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A234">
         <v>42302.255047630402</v>
       </c>
@@ -2288,7 +2259,7 @@
         <v>23.610348266959001</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A235">
         <v>42302.262005886201</v>
       </c>
@@ -2296,7 +2267,7 @@
         <v>15.8375584176706</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A236">
         <v>42302.268809868401</v>
       </c>
@@ -2304,7 +2275,7 @@
         <v>17.8310268631379</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A237">
         <v>42302.272688803801</v>
       </c>
@@ -2312,7 +2283,7 @@
         <v>23.212584561235101</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A238">
         <v>42302.293482346002</v>
       </c>
@@ -2320,7 +2291,7 @@
         <v>12.492665379250701</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A239">
         <v>42302.300083043803</v>
       </c>
@@ -2328,7 +2299,7 @@
         <v>17.1942655283551</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A240">
         <v>42302.329725096002</v>
       </c>
@@ -2336,7 +2307,7 @@
         <v>11.122794852330101</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A241">
         <v>42302.331406477897</v>
       </c>
@@ -2344,7 +2315,7 @@
         <v>19.542182516812101</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A242">
         <v>42302.337014339202</v>
       </c>
@@ -2352,7 +2323,7 @@
         <v>16.203565503146098</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A243">
         <v>42302.342201233398</v>
       </c>
@@ -2360,7 +2331,7 @@
         <v>22.444751433936801</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A244">
         <v>42302.351659424603</v>
       </c>
@@ -2368,7 +2339,7 @@
         <v>38.912542614883797</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A245">
         <v>42302.3814157222</v>
       </c>
@@ -2376,7 +2347,7 @@
         <v>25.512180276464399</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A246">
         <v>42302.420830715302</v>
       </c>
@@ -2384,7 +2355,7 @@
         <v>9.9371149319479102</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A247">
         <v>42302.4464611234</v>
       </c>
@@ -2392,7 +2363,7 @@
         <v>11.085878360224701</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A248">
         <v>42302.454347861298</v>
       </c>
@@ -2400,7 +2371,7 @@
         <v>20.6298911262028</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A249">
         <v>42302.456704126103</v>
       </c>
@@ -2408,7 +2379,7 @@
         <v>21.641392288505301</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A250">
         <v>42302.463648509904</v>
       </c>
@@ -2416,7 +2387,7 @@
         <v>25.927651991998001</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A251">
         <v>42302.465409915698</v>
       </c>
@@ -2424,7 +2395,7 @@
         <v>13.8404435089034</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A252">
         <v>42302.475966639096</v>
       </c>
@@ -2432,7 +2403,7 @@
         <v>20.8669508405453</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A253">
         <v>42302.484792601899</v>
       </c>
@@ -2440,7 +2411,7 @@
         <v>10.9241715020289</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A254">
         <v>42302.5233738471</v>
       </c>
@@ -2448,7 +2419,7 @@
         <v>11.2099595986524</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A255">
         <v>42302.538831115598</v>
       </c>
@@ -2456,7 +2427,7 @@
         <v>14.2150794101328</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A256">
         <v>42302.539420819798</v>
       </c>
@@ -2464,7 +2435,7 @@
         <v>27.214242384401398</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A257">
         <v>42302.5409588478</v>
       </c>
@@ -2472,7 +2443,7 @@
         <v>32.051208840847401</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A258">
         <v>42302.545714930799</v>
       </c>
@@ -2480,7 +2451,7 @@
         <v>38.153452315853698</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A259">
         <v>42302.548838014103</v>
       </c>
@@ -2488,7 +2459,7 @@
         <v>24.800755748555201</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A260">
         <v>42302.564006889203</v>
       </c>
@@ -2496,7 +2467,7 @@
         <v>16.6825048709348</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A261">
         <v>42302.564982491604</v>
       </c>
@@ -2504,7 +2475,7 @@
         <v>12.963375803961901</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A262">
         <v>42302.572222025403</v>
       </c>
@@ -2512,7 +2483,7 @@
         <v>11.7728613227109</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A263">
         <v>42302.587173441403</v>
       </c>
@@ -2520,7 +2491,7 @@
         <v>18.646844320456399</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A264">
         <v>42302.587844515198</v>
       </c>
@@ -2528,7 +2499,7 @@
         <v>22.6579381553106</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A265">
         <v>42302.597425394102</v>
       </c>
@@ -2536,7 +2507,7 @@
         <v>15.825159859442399</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A266">
         <v>42302.5992527329</v>
       </c>
@@ -2544,7 +2515,7 @@
         <v>19.6028391207761</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A267">
         <v>42302.604844510301</v>
       </c>
@@ -2552,7 +2523,7 @@
         <v>23.143213441210399</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A268">
         <v>42302.605319857299</v>
       </c>
@@ -2560,7 +2531,7 @@
         <v>12.989419225650201</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A269">
         <v>42302.611429352299</v>
       </c>
@@ -2568,7 +2539,7 @@
         <v>27.762282891103101</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A270">
         <v>42302.619361659803</v>
       </c>
@@ -2576,7 +2547,7 @@
         <v>29.339673730485298</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A271">
         <v>42302.619996114001</v>
       </c>
@@ -2584,7 +2555,7 @@
         <v>14.2620382235727</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A272">
         <v>42302.625277197498</v>
       </c>
@@ -2592,7 +2563,7 @@
         <v>16.895755387907499</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A273">
         <v>42302.627623720698</v>
       </c>
@@ -2600,7 +2571,7 @@
         <v>22.5364382358255</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A274">
         <v>42302.639459327002</v>
       </c>
@@ -2608,7 +2579,7 @@
         <v>27.873837877659199</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A275">
         <v>42302.657140561299</v>
       </c>
@@ -2616,7 +2587,7 @@
         <v>5.7665250777055697</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A276">
         <v>42302.662130625104</v>
       </c>
@@ -2624,7 +2595,7 @@
         <v>27.4369802009982</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A277">
         <v>42302.671260357398</v>
       </c>
@@ -2632,7 +2603,7 @@
         <v>4.9518782929096599</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A278">
         <v>42302.705501657903</v>
       </c>
@@ -2640,7 +2611,7 @@
         <v>21.602307956757102</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A279">
         <v>42302.714487323901</v>
       </c>
@@ -2648,7 +2619,7 @@
         <v>29.974356306633101</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A280">
         <v>42302.759133621403</v>
       </c>
@@ -2656,7 +2627,7 @@
         <v>36.040846446283098</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A281">
         <v>42302.764228845503</v>
       </c>
@@ -2664,7 +2635,7 @@
         <v>13.590471407021401</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A282">
         <v>42302.7668571822</v>
       </c>
@@ -2672,7 +2643,7 @@
         <v>24.4056225169813</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A283">
         <v>42302.791063225501</v>
       </c>
@@ -2680,7 +2651,7 @@
         <v>21.543159657702098</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A284">
         <v>42302.821427201801</v>
       </c>
@@ -2688,7 +2659,7 @@
         <v>7.0343010304102602</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A285">
         <v>42302.821574280897</v>
       </c>
@@ -2696,7 +2667,7 @@
         <v>16.018951722239599</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A286">
         <v>42302.823542240098</v>
       </c>
@@ -2704,7 +2675,7 @@
         <v>6.4647949158714901</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A287">
         <v>42302.828398579899</v>
       </c>
@@ -2712,7 +2683,7 @@
         <v>20.015932080035199</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A288">
         <v>42302.832951685799</v>
       </c>
@@ -2720,7 +2691,7 @@
         <v>23.872171532890999</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A289">
         <v>42302.847649241798</v>
       </c>
@@ -2728,7 +2699,7 @@
         <v>6.8010167023569403</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A290">
         <v>42302.864787910803</v>
       </c>
@@ -2736,7 +2707,7 @@
         <v>17.639642860446902</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A291">
         <v>42302.880027138097</v>
       </c>
@@ -2744,7 +2715,7 @@
         <v>14.1464065771757</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A292">
         <v>42302.889052711202</v>
       </c>
@@ -2752,7 +2723,7 @@
         <v>29.207343581423299</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A293">
         <v>42302.898932390999</v>
       </c>
@@ -2760,7 +2731,7 @@
         <v>23.086044081632899</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A294">
         <v>42302.899134553198</v>
       </c>
@@ -2768,7 +2739,7 @@
         <v>18.6851650794218</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A295">
         <v>42302.906976694801</v>
       </c>
@@ -2776,7 +2747,7 @@
         <v>11.519158444892801</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A296">
         <v>42302.9156554527</v>
       </c>
@@ -2784,7 +2755,7 @@
         <v>16.778935411111199</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A297">
         <v>42302.920545771798</v>
       </c>
@@ -2792,7 +2763,7 @@
         <v>22.861364876486402</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A298">
         <v>42302.932487022699</v>
       </c>
@@ -2800,7 +2771,7 @@
         <v>4.4776982723755498</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A299">
         <v>42302.945034695003</v>
       </c>
@@ -2808,7 +2779,7 @@
         <v>30.3649284415966</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A300">
         <v>42302.987985514999</v>
       </c>
@@ -2816,7 +2787,7 @@
         <v>18.097103488749699</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A301">
         <v>42302.992877422097</v>
       </c>
@@ -2824,7 +2795,7 @@
         <v>21.407190561113499</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A302">
         <v>42303.010564844997</v>
       </c>
@@ -2832,7 +2803,7 @@
         <v>21.830049648673398</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A303">
         <v>42303.014479343001</v>
       </c>
@@ -2840,7 +2811,7 @@
         <v>35.111998768765403</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A304">
         <v>42303.015581726198</v>
       </c>
@@ -2848,7 +2819,7 @@
         <v>16.4743142949029</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A305">
         <v>42303.0386238258</v>
       </c>
@@ -2856,7 +2827,7 @@
         <v>28.948058011282701</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A306">
         <v>42303.043435597203</v>
       </c>
@@ -2864,7 +2835,7 @@
         <v>17.410200759706601</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A307">
         <v>42303.049371768298</v>
       </c>
@@ -2872,7 +2843,7 @@
         <v>5.6500828267340699</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A308">
         <v>42303.049689083899</v>
       </c>
@@ -2880,7 +2851,7 @@
         <v>27.119217126226701</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A309">
         <v>42303.0557106294</v>
       </c>
@@ -2888,7 +2859,7 @@
         <v>34.377131137091702</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A310">
         <v>42303.062369232197</v>
       </c>
@@ -2896,7 +2867,7 @@
         <v>31.513826017582399</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A311">
         <v>42303.062614836002</v>
       </c>
@@ -2904,7 +2875,7 @@
         <v>10.1500898053672</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A312">
         <v>42303.065552585998</v>
       </c>
@@ -2912,7 +2883,7 @@
         <v>23.257435232811599</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A313">
         <v>42303.065746547902</v>
       </c>
@@ -2920,7 +2891,7 @@
         <v>21.373493651276</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A314">
         <v>42303.076384645698</v>
       </c>
@@ -2928,7 +2899,7 @@
         <v>22.293124857784999</v>
       </c>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A315">
         <v>42303.083747798599</v>
       </c>
@@ -2936,7 +2907,7 @@
         <v>17.961744464351</v>
       </c>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A316">
         <v>42303.087497969398</v>
       </c>
@@ -2944,7 +2915,7 @@
         <v>10.535266639430899</v>
       </c>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A317">
         <v>42303.092264375999</v>
       </c>
@@ -2952,7 +2923,7 @@
         <v>27.9680067660662</v>
       </c>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A318">
         <v>42303.1010574678</v>
       </c>
@@ -2960,7 +2931,7 @@
         <v>7.9092154522814404</v>
       </c>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A319">
         <v>42303.105959121101</v>
       </c>
@@ -2968,7 +2939,7 @@
         <v>23.589371240277099</v>
       </c>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A320">
         <v>42303.110437097203</v>
       </c>
@@ -2976,7 +2947,7 @@
         <v>32.882866186575797</v>
       </c>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A321">
         <v>42303.126733813297</v>
       </c>
@@ -2984,7 +2955,7 @@
         <v>16.127026458642099</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A322">
         <v>42303.128304051199</v>
       </c>
@@ -2992,7 +2963,7 @@
         <v>2.4244134435780098</v>
       </c>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A323">
         <v>42303.129904077403</v>
       </c>
@@ -3000,7 +2971,7 @@
         <v>13.9659554078738</v>
       </c>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A324">
         <v>42303.130557623699</v>
       </c>
@@ -3008,7 +2979,7 @@
         <v>11.2935080565271</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A325">
         <v>42303.132897488002</v>
       </c>
@@ -3016,7 +2987,7 @@
         <v>20.318204428556999</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A326">
         <v>42303.148231463303</v>
       </c>
@@ -3024,7 +2995,7 @@
         <v>9.6870254461640304</v>
       </c>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A327">
         <v>42303.154937544903</v>
       </c>
@@ -3032,7 +3003,7 @@
         <v>12.313705993194599</v>
       </c>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A328">
         <v>42303.155080433098</v>
       </c>
@@ -3040,7 +3011,7 @@
         <v>26.627911535730799</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A329">
         <v>42303.156579759998</v>
       </c>
@@ -3048,7 +3019,7 @@
         <v>6.6058211408065599</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A330">
         <v>42303.171099899097</v>
       </c>
@@ -3056,7 +3027,7 @@
         <v>22.553012229970701</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A331">
         <v>42303.1886021705</v>
       </c>
@@ -3064,7 +3035,7 @@
         <v>6.3625394836142002</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A332">
         <v>42303.190285671102</v>
       </c>
@@ -3072,7 +3043,7 @@
         <v>1.88035214311906</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A333">
         <v>42303.192669670701</v>
       </c>
@@ -3080,7 +3051,7 @@
         <v>7.8065989462476697</v>
       </c>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A334">
         <v>42303.194669457902</v>
       </c>
@@ -3088,7 +3059,7 @@
         <v>28.3888332420265</v>
       </c>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A335">
         <v>42303.200306204199</v>
       </c>
@@ -3096,7 +3067,7 @@
         <v>24.3374567612465</v>
       </c>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A336">
         <v>42303.229674792201</v>
       </c>
@@ -3104,7 +3075,7 @@
         <v>20.702872518330899</v>
       </c>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A337">
         <v>42303.246311659903</v>
       </c>
@@ -3112,7 +3083,7 @@
         <v>8.7607480327894809</v>
       </c>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A338">
         <v>42303.251120520901</v>
       </c>
@@ -3120,7 +3091,7 @@
         <v>20.3539807303289</v>
       </c>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A339">
         <v>42303.2569726449</v>
       </c>
@@ -3128,7 +3099,7 @@
         <v>7.4400568624980901</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A340">
         <v>42303.263790615601</v>
       </c>
@@ -3136,7 +3107,7 @@
         <v>24.305299197300499</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A341">
         <v>42303.267108582797</v>
       </c>
@@ -3144,7 +3115,7 @@
         <v>20.199217468934801</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A342">
         <v>42303.269129385197</v>
       </c>
@@ -3152,7 +3123,7 @@
         <v>26.890775247344699</v>
       </c>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A343">
         <v>42303.2743431294</v>
       </c>
@@ -3160,7 +3131,7 @@
         <v>13.720629776946</v>
       </c>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A344">
         <v>42303.280787011099</v>
       </c>
@@ -3168,7 +3139,7 @@
         <v>22.516922361188801</v>
       </c>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A345">
         <v>42303.282211566802</v>
       </c>
@@ -3176,7 +3147,7 @@
         <v>26.2366603175719</v>
       </c>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A346">
         <v>42303.287643957599</v>
       </c>
@@ -3184,7 +3155,7 @@
         <v>6.1647356320184299</v>
       </c>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A347">
         <v>42303.300491604299</v>
       </c>
@@ -3192,7 +3163,7 @@
         <v>29.225422751233399</v>
       </c>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A348">
         <v>42303.304692870399</v>
       </c>
@@ -3200,7 +3171,7 @@
         <v>2.5416202172812601</v>
       </c>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A349">
         <v>42303.311006981603</v>
       </c>
@@ -3208,7 +3179,7 @@
         <v>19.7488433116356</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A350">
         <v>42303.311522287098</v>
       </c>
@@ -3216,7 +3187,7 @@
         <v>18.629946933847599</v>
       </c>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A351">
         <v>42303.312788871903</v>
       </c>
@@ -3224,7 +3195,7 @@
         <v>21.4928065365593</v>
       </c>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A352">
         <v>42303.337275056903</v>
       </c>
@@ -3232,7 +3203,7 @@
         <v>30.6766153068805</v>
       </c>
     </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A353">
         <v>42303.338753359298</v>
       </c>
@@ -3240,7 +3211,7 @@
         <v>27.743591097279101</v>
       </c>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A354">
         <v>42303.351216853996</v>
       </c>
@@ -3248,7 +3219,7 @@
         <v>11.1559788455526</v>
       </c>
     </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A355">
         <v>42303.366944662397</v>
       </c>
@@ -3256,7 +3227,7 @@
         <v>35.673640888305101</v>
       </c>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A356">
         <v>42303.375654475298</v>
       </c>
@@ -3264,7 +3235,7 @@
         <v>24.0836183666752</v>
       </c>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A357">
         <v>42303.390558566098</v>
       </c>
@@ -3272,7 +3243,7 @@
         <v>29.3398907286537</v>
       </c>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A358">
         <v>42303.391029708197</v>
       </c>
@@ -3280,7 +3251,7 @@
         <v>9.0108858355904395</v>
       </c>
     </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A359">
         <v>42303.391858175499</v>
       </c>
@@ -3288,7 +3259,7 @@
         <v>12.9349832513712</v>
       </c>
     </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A360">
         <v>42303.409407161998</v>
       </c>
@@ -3296,7 +3267,7 @@
         <v>17.5310191279913</v>
       </c>
     </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A361">
         <v>42303.411354688003</v>
       </c>
@@ -3304,7 +3275,7 @@
         <v>31.8223921698068</v>
       </c>
     </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A362">
         <v>42303.420463279203</v>
       </c>
@@ -3312,7 +3283,7 @@
         <v>19.0684759620672</v>
       </c>
     </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A363">
         <v>42303.4212107727</v>
       </c>
@@ -3320,7 +3291,7 @@
         <v>6.1421283157919104</v>
       </c>
     </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A364">
         <v>42303.423062838097</v>
       </c>
@@ -3328,7 +3299,7 @@
         <v>15.914329240432901</v>
       </c>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A365">
         <v>42303.425285243997</v>
       </c>
@@ -3336,7 +3307,7 @@
         <v>19.7334538015274</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A366">
         <v>42303.434939613602</v>
       </c>
@@ -3344,7 +3315,7 @@
         <v>7.1672332981670399</v>
       </c>
     </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A367">
         <v>42303.4482169119</v>
       </c>
@@ -3352,7 +3323,7 @@
         <v>17.041633440432499</v>
       </c>
     </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A368">
         <v>42303.450921654403</v>
       </c>
@@ -3360,7 +3331,7 @@
         <v>37.307322077044503</v>
       </c>
     </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A369">
         <v>42303.482942914598</v>
       </c>
@@ -3368,7 +3339,7 @@
         <v>9.9711103399956507</v>
       </c>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A370">
         <v>42303.498350399197</v>
       </c>
@@ -3376,7 +3347,7 @@
         <v>23.996322098973799</v>
       </c>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A371">
         <v>42303.503609503503</v>
       </c>
@@ -3384,7 +3355,7 @@
         <v>28.636649313436401</v>
       </c>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A372">
         <v>42303.539764159803</v>
       </c>
@@ -3392,7 +3363,7 @@
         <v>14.543357741174001</v>
       </c>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A373">
         <v>42303.544690130002</v>
       </c>
@@ -3400,7 +3371,7 @@
         <v>26.006359779527699</v>
       </c>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A374">
         <v>42303.5497364736</v>
       </c>
@@ -3408,7 +3379,7 @@
         <v>11.983167742644101</v>
       </c>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A375">
         <v>42303.553400636702</v>
       </c>
@@ -3416,7 +3387,7 @@
         <v>11.317868345425801</v>
       </c>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A376">
         <v>42303.556913501699</v>
       </c>
@@ -3424,7 +3395,7 @@
         <v>18.358191177456799</v>
       </c>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A377">
         <v>42303.578220505296</v>
       </c>
@@ -3432,7 +3403,7 @@
         <v>18.575015728770001</v>
       </c>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A378">
         <v>42303.584728345602</v>
       </c>
@@ -3440,7 +3411,7 @@
         <v>13.293358455382</v>
       </c>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A379">
         <v>42303.585966753199</v>
       </c>
@@ -3448,7 +3419,7 @@
         <v>15.597068977426201</v>
       </c>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A380">
         <v>42303.587316123303</v>
       </c>
@@ -3456,7 +3427,7 @@
         <v>11.5606279590416</v>
       </c>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A381">
         <v>42303.593902203902</v>
       </c>
@@ -3464,7 +3435,7 @@
         <v>21.923801285924</v>
       </c>
     </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A382">
         <v>42303.603427738999</v>
       </c>
@@ -3472,7 +3443,7 @@
         <v>30.1045830356374</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A383">
         <v>42303.626517927398</v>
       </c>
@@ -3480,7 +3451,7 @@
         <v>19.982949308376099</v>
       </c>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A384">
         <v>42303.633904861701</v>
       </c>
@@ -3488,7 +3459,7 @@
         <v>5.9513578870638399</v>
       </c>
     </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A385">
         <v>42303.644315274301</v>
       </c>
@@ -3496,7 +3467,7 @@
         <v>18.4286018584069</v>
       </c>
     </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A386">
         <v>42303.6514126232</v>
       </c>
@@ -3504,7 +3475,7 @@
         <v>31.812915049538798</v>
       </c>
     </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A387">
         <v>42303.654645653703</v>
       </c>
@@ -3512,7 +3483,7 @@
         <v>24.244281975908201</v>
       </c>
     </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A388">
         <v>42303.6777637911</v>
       </c>
@@ -3520,7 +3491,7 @@
         <v>20.472107511073901</v>
       </c>
     </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A389">
         <v>42303.686905309303</v>
       </c>
@@ -3528,7 +3499,7 @@
         <v>28.827924602839001</v>
       </c>
     </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A390">
         <v>42303.699093728501</v>
       </c>
@@ -3536,7 +3507,7 @@
         <v>19.628813773602801</v>
       </c>
     </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A391">
         <v>42303.738680369097</v>
       </c>
@@ -3544,7 +3515,7 @@
         <v>19.779595798470801</v>
       </c>
     </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A392">
         <v>42303.757844567001</v>
       </c>
@@ -3552,7 +3523,7 @@
         <v>29.5455893461477</v>
       </c>
     </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A393">
         <v>42303.761214711601</v>
       </c>
@@ -3560,7 +3531,7 @@
         <v>10.458315344972901</v>
       </c>
     </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A394">
         <v>42303.763456279397</v>
       </c>
@@ -3568,7 +3539,7 @@
         <v>25.871714120309701</v>
       </c>
     </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A395">
         <v>42303.769827587697</v>
       </c>
@@ -3576,7 +3547,7 @@
         <v>7.3098507250367204</v>
       </c>
     </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A396">
         <v>42303.770837276497</v>
       </c>
@@ -3584,7 +3555,7 @@
         <v>22.8711357172795</v>
       </c>
     </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A397">
         <v>42303.782220115601</v>
       </c>
@@ -3592,7 +3563,7 @@
         <v>23.016887091303001</v>
       </c>
     </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A398">
         <v>42303.78620979</v>
       </c>
@@ -3600,7 +3571,7 @@
         <v>31.888124882471999</v>
       </c>
     </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A399">
         <v>42303.786562197798</v>
       </c>
@@ -3608,7 +3579,7 @@
         <v>15.872455746475</v>
       </c>
     </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A400">
         <v>42303.793450008401</v>
       </c>
@@ -3616,7 +3587,7 @@
         <v>21.736855035476701</v>
       </c>
     </row>
-    <row r="401" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A401">
         <v>42303.7943363062</v>
       </c>
@@ -3624,7 +3595,7 @@
         <v>35.640610833397098</v>
       </c>
     </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A402">
         <v>42303.802183090302</v>
       </c>
@@ -3632,7 +3603,7 @@
         <v>20.4340946101109</v>
       </c>
     </row>
-    <row r="403" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A403">
         <v>42303.802801772603</v>
       </c>
@@ -3640,7 +3611,7 @@
         <v>38.364251172617699</v>
       </c>
     </row>
-    <row r="404" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A404">
         <v>42303.807435260896</v>
       </c>
@@ -3648,7 +3619,7 @@
         <v>19.9169684913672</v>
       </c>
     </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A405">
         <v>42303.810470008197</v>
       </c>
@@ -3656,7 +3627,7 @@
         <v>19.909525957102801</v>
       </c>
     </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A406">
         <v>42303.825040825199</v>
       </c>
@@ -3664,7 +3635,7 @@
         <v>19.7370007250668</v>
       </c>
     </row>
-    <row r="407" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A407">
         <v>42303.828789328902</v>
       </c>
@@ -3672,7 +3643,7 @@
         <v>25.499217923466801</v>
       </c>
     </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A408">
         <v>42303.871269621501</v>
       </c>
@@ -3680,7 +3651,7 @@
         <v>12.099413577676801</v>
       </c>
     </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A409">
         <v>42303.903611889997</v>
       </c>
@@ -3688,7 +3659,7 @@
         <v>21.3472092312355</v>
       </c>
     </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A410">
         <v>42303.9100965775</v>
       </c>
@@ -3696,7 +3667,7 @@
         <v>15.6972087054806</v>
       </c>
     </row>
-    <row r="411" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A411">
         <v>42303.918772969897</v>
       </c>
@@ -3704,7 +3675,7 @@
         <v>22.118142303098999</v>
       </c>
     </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A412">
         <v>42303.923508908403</v>
       </c>
@@ -3712,7 +3683,7 @@
         <v>37.681460782384598</v>
       </c>
     </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A413">
         <v>42303.927877640301</v>
       </c>
@@ -3720,7 +3691,7 @@
         <v>18.017427908015101</v>
       </c>
     </row>
-    <row r="414" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A414">
         <v>42303.937411543302</v>
       </c>
@@ -3728,7 +3699,7 @@
         <v>20.814277543320099</v>
       </c>
     </row>
-    <row r="415" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A415">
         <v>42303.9480587168</v>
       </c>
@@ -3736,7 +3707,7 @@
         <v>20.334498131848999</v>
       </c>
     </row>
-    <row r="416" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A416">
         <v>42303.9609325243</v>
       </c>
@@ -3744,7 +3715,7 @@
         <v>12.3387789767218</v>
       </c>
     </row>
-    <row r="417" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A417">
         <v>42303.967620095798</v>
       </c>
@@ -3752,7 +3723,7 @@
         <v>30.826175203651601</v>
       </c>
     </row>
-    <row r="418" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A418">
         <v>42303.998332153897</v>
       </c>
@@ -3760,7 +3731,7 @@
         <v>34.624444871711503</v>
       </c>
     </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A419">
         <v>42303.9993143826</v>
       </c>
@@ -3768,7 +3739,7 @@
         <v>10.1437659292575</v>
       </c>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A420">
         <v>42304.008887368604</v>
       </c>
@@ -3776,7 +3747,7 @@
         <v>20.9210890802986</v>
       </c>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A421">
         <v>42304.015017697297</v>
       </c>
@@ -3784,7 +3755,7 @@
         <v>4.1610756952741301</v>
       </c>
     </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A422">
         <v>42304.016076471402</v>
       </c>
@@ -3792,7 +3763,7 @@
         <v>22.095022526605501</v>
       </c>
     </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A423">
         <v>42304.028783991198</v>
       </c>
@@ -3800,7 +3771,7 @@
         <v>28.2101733506959</v>
       </c>
     </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A424">
         <v>42304.047627390399</v>
       </c>
@@ -3808,7 +3779,7 @@
         <v>17.573077992401799</v>
       </c>
     </row>
-    <row r="425" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A425">
         <v>42304.051217373599</v>
       </c>
@@ -3816,7 +3787,7 @@
         <v>24.8982598708719</v>
       </c>
     </row>
-    <row r="426" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A426">
         <v>42304.079436406799</v>
       </c>
@@ -3824,7 +3795,7 @@
         <v>29.0963920639797</v>
       </c>
     </row>
-    <row r="427" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A427">
         <v>42304.087892178199</v>
       </c>
@@ -3832,7 +3803,7 @@
         <v>24.664065296037801</v>
       </c>
     </row>
-    <row r="428" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A428">
         <v>42304.102978384501</v>
       </c>
@@ -3840,7 +3811,7 @@
         <v>18.2296473856643</v>
       </c>
     </row>
-    <row r="429" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A429">
         <v>42304.118570089398</v>
       </c>
@@ -3848,7 +3819,7 @@
         <v>27.0451160049228</v>
       </c>
     </row>
-    <row r="430" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A430">
         <v>42304.133302532799</v>
       </c>
@@ -3856,7 +3827,7 @@
         <v>22.7111051187124</v>
       </c>
     </row>
-    <row r="431" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A431">
         <v>42304.137248150902</v>
       </c>
@@ -3864,7 +3835,7 @@
         <v>21.8923133336225</v>
       </c>
     </row>
-    <row r="432" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A432">
         <v>42304.1448122972</v>
       </c>
@@ -3872,7 +3843,7 @@
         <v>1.8349431808898999</v>
       </c>
     </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A433">
         <v>42304.148999048703</v>
       </c>
@@ -3880,7 +3851,7 @@
         <v>11.672493588254801</v>
       </c>
     </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A434">
         <v>42304.149754374601</v>
       </c>
@@ -3888,7 +3859,7 @@
         <v>22.457280116560302</v>
       </c>
     </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A435">
         <v>42304.154436976198</v>
       </c>
@@ -3896,7 +3867,7 @@
         <v>15.334398794650999</v>
       </c>
     </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A436">
         <v>42304.162846037099</v>
       </c>
@@ -3904,7 +3875,7 @@
         <v>30.453793661935499</v>
       </c>
     </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A437">
         <v>42304.166551183102</v>
       </c>
@@ -3912,7 +3883,7 @@
         <v>18.5153465968577</v>
       </c>
     </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A438">
         <v>42304.168988882702</v>
       </c>
@@ -3920,7 +3891,7 @@
         <v>27.8622175326052</v>
       </c>
     </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A439">
         <v>42304.181929680301</v>
       </c>
@@ -3928,7 +3899,7 @@
         <v>22.075402129632</v>
       </c>
     </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A440">
         <v>42304.182994270501</v>
       </c>
@@ -3936,7 +3907,7 @@
         <v>16.577464597804699</v>
       </c>
     </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A441">
         <v>42304.198666008597</v>
       </c>
@@ -3944,7 +3915,7 @@
         <v>33.917747960895603</v>
       </c>
     </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A442">
         <v>42304.2148838883</v>
       </c>
@@ -3952,7 +3923,7 @@
         <v>26.7714786788335</v>
       </c>
     </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A443">
         <v>42304.222303693597</v>
       </c>
@@ -3960,7 +3931,7 @@
         <v>16.975982721409999</v>
       </c>
     </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A444">
         <v>42304.230087823002</v>
       </c>
@@ -3968,7 +3939,7 @@
         <v>5.8968843432307096</v>
       </c>
     </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A445">
         <v>42304.231744315301</v>
       </c>
@@ -3976,7 +3947,7 @@
         <v>9.7043115482043891</v>
       </c>
     </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A446">
         <v>42304.239058043</v>
       </c>
@@ -3984,7 +3955,7 @@
         <v>19.8887160935164</v>
       </c>
     </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A447">
         <v>42304.239996662604</v>
       </c>
@@ -3992,7 +3963,7 @@
         <v>12.176628855529</v>
       </c>
     </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A448">
         <v>42304.244216797299</v>
       </c>
@@ -4000,7 +3971,7 @@
         <v>17.789691506011302</v>
       </c>
     </row>
-    <row r="449" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A449">
         <v>42304.256402962703</v>
       </c>
@@ -4008,7 +3979,7 @@
         <v>20.182560065536599</v>
       </c>
     </row>
-    <row r="450" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A450">
         <v>42304.264429394403</v>
       </c>
@@ -4016,7 +3987,7 @@
         <v>7.2975582723936299</v>
       </c>
     </row>
-    <row r="451" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A451">
         <v>42304.285652062099</v>
       </c>
@@ -4024,7 +3995,7 @@
         <v>19.073031228598001</v>
       </c>
     </row>
-    <row r="452" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A452">
         <v>42304.287700394401</v>
       </c>
@@ -4032,7 +4003,7 @@
         <v>23.098006706373098</v>
       </c>
     </row>
-    <row r="453" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A453">
         <v>42304.287869182597</v>
       </c>
@@ -4040,7 +4011,7 @@
         <v>18.4169926240316</v>
       </c>
     </row>
-    <row r="454" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A454">
         <v>42304.294058328996</v>
       </c>
@@ -4048,7 +4019,7 @@
         <v>11.4177475825458</v>
       </c>
     </row>
-    <row r="455" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A455">
         <v>42304.299707065999</v>
       </c>
@@ -4056,7 +4027,7 @@
         <v>25.302040060364401</v>
       </c>
     </row>
-    <row r="456" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A456">
         <v>42304.300901384799</v>
       </c>
@@ -4064,7 +4035,7 @@
         <v>10.3553502728253</v>
       </c>
     </row>
-    <row r="457" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A457">
         <v>42304.302405251998</v>
       </c>
@@ -4072,7 +4043,7 @@
         <v>16.875639648376701</v>
       </c>
     </row>
-    <row r="458" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A458">
         <v>42304.3102187041</v>
       </c>
@@ -4080,7 +4051,7 @@
         <v>28.26122964835</v>
       </c>
     </row>
-    <row r="459" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A459">
         <v>42304.311774003603</v>
       </c>
@@ -4088,7 +4059,7 @@
         <v>26.794715839228999</v>
       </c>
     </row>
-    <row r="460" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A460">
         <v>42304.321905000797</v>
       </c>
@@ -4096,7 +4067,7 @@
         <v>1.84005067516319</v>
       </c>
     </row>
-    <row r="461" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A461">
         <v>42304.322638859703</v>
       </c>
@@ -4104,7 +4075,7 @@
         <v>22.780228972583799</v>
       </c>
     </row>
-    <row r="462" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A462">
         <v>42304.323106667704</v>
       </c>
@@ -4112,7 +4083,7 @@
         <v>22.9133704992181</v>
       </c>
     </row>
-    <row r="463" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A463">
         <v>42304.325171479803</v>
       </c>
@@ -4120,7 +4091,7 @@
         <v>23.502077366074801</v>
       </c>
     </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A464">
         <v>42304.339669025001</v>
       </c>
@@ -4128,7 +4099,7 @@
         <v>20.597855556205701</v>
       </c>
     </row>
-    <row r="465" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A465">
         <v>42304.350254991899</v>
       </c>
@@ -4136,7 +4107,7 @@
         <v>15.7428434109975</v>
       </c>
     </row>
-    <row r="466" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A466">
         <v>42304.360579382897</v>
       </c>
@@ -4144,7 +4115,7 @@
         <v>4.3009346935802402</v>
       </c>
     </row>
-    <row r="467" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A467">
         <v>42304.360624519497</v>
       </c>
@@ -4152,7 +4123,7 @@
         <v>14.751232673346401</v>
       </c>
     </row>
-    <row r="468" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A468">
         <v>42304.373714542802</v>
       </c>
@@ -4160,7 +4131,7 @@
         <v>13.106006921273901</v>
       </c>
     </row>
-    <row r="469" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A469">
         <v>42304.407466759301</v>
       </c>
@@ -4168,7 +4139,7 @@
         <v>13.329033606205099</v>
       </c>
     </row>
-    <row r="470" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A470">
         <v>42304.433044859601</v>
       </c>
@@ -4176,7 +4147,7 @@
         <v>16.5834235072094</v>
       </c>
     </row>
-    <row r="471" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A471">
         <v>42304.439843612403</v>
       </c>
@@ -4184,7 +4155,7 @@
         <v>16.827503699035301</v>
       </c>
     </row>
-    <row r="472" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A472">
         <v>42304.447062941297</v>
       </c>
@@ -4192,7 +4163,7 @@
         <v>12.2495715605158</v>
       </c>
     </row>
-    <row r="473" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A473">
         <v>42304.498973028902</v>
       </c>
@@ -4200,7 +4171,7 @@
         <v>23.7060725572594</v>
       </c>
     </row>
-    <row r="474" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A474">
         <v>42304.528314249997</v>
       </c>
@@ -4208,7 +4179,7 @@
         <v>25.660000891005701</v>
       </c>
     </row>
-    <row r="475" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A475">
         <v>42304.530841813001</v>
       </c>
@@ -4216,7 +4187,7 @@
         <v>35.462551347127601</v>
       </c>
     </row>
-    <row r="476" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A476">
         <v>42304.535764816901</v>
       </c>
@@ -4224,7 +4195,7 @@
         <v>12.644275480305501</v>
       </c>
     </row>
-    <row r="477" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A477">
         <v>42304.538164313803</v>
       </c>
@@ -4232,7 +4203,7 @@
         <v>14.0667074246659</v>
       </c>
     </row>
-    <row r="478" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A478">
         <v>42304.538790465202</v>
       </c>
@@ -4240,7 +4211,7 @@
         <v>25.7899526563221</v>
       </c>
     </row>
-    <row r="479" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A479">
         <v>42304.545280331004</v>
       </c>
@@ -4248,7 +4219,7 @@
         <v>19.518356201732701</v>
       </c>
     </row>
-    <row r="480" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A480">
         <v>42304.5459031297</v>
       </c>
@@ -4256,7 +4227,7 @@
         <v>12.3426793092525</v>
       </c>
     </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A481">
         <v>42304.5491353779</v>
       </c>
@@ -4264,7 +4235,7 @@
         <v>26.810004608170299</v>
       </c>
     </row>
-    <row r="482" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A482">
         <v>42304.558664452001</v>
       </c>
@@ -4272,7 +4243,7 @@
         <v>12.9993737325756</v>
       </c>
     </row>
-    <row r="483" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A483">
         <v>42304.568380968798</v>
       </c>
@@ -4280,7 +4251,7 @@
         <v>21.557762200203602</v>
       </c>
     </row>
-    <row r="484" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A484">
         <v>42304.572320142099</v>
       </c>
@@ -4288,7 +4259,7 @@
         <v>22.698338660112999</v>
       </c>
     </row>
-    <row r="485" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A485">
         <v>42304.588032532498</v>
       </c>
@@ -4296,7 +4267,7 @@
         <v>22.291994939939901</v>
       </c>
     </row>
-    <row r="486" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A486">
         <v>42304.6022466902</v>
       </c>
@@ -4304,7 +4275,7 @@
         <v>20.133424052661798</v>
       </c>
     </row>
-    <row r="487" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A487">
         <v>42304.643692856102</v>
       </c>
@@ -4312,7 +4283,7 @@
         <v>24.908144780058599</v>
       </c>
     </row>
-    <row r="488" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A488">
         <v>42304.645150469099</v>
       </c>
@@ -4320,7 +4291,7 @@
         <v>31.190743526077501</v>
       </c>
     </row>
-    <row r="489" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A489">
         <v>42304.648847987497</v>
       </c>
@@ -4328,7 +4299,7 @@
         <v>22.448256829800901</v>
       </c>
     </row>
-    <row r="490" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A490">
         <v>42304.664165231603</v>
       </c>
@@ -4336,7 +4307,7 @@
         <v>16.165642968416101</v>
       </c>
     </row>
-    <row r="491" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A491">
         <v>42304.688659114101</v>
       </c>
@@ -4344,7 +4315,7 @@
         <v>17.544573988434301</v>
       </c>
     </row>
-    <row r="492" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A492">
         <v>42304.693184252297</v>
       </c>
@@ -4352,7 +4323,7 @@
         <v>24.487886699601201</v>
       </c>
     </row>
-    <row r="493" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A493">
         <v>42304.693395182898</v>
       </c>
@@ -4360,7 +4331,7 @@
         <v>35.758575172852197</v>
       </c>
     </row>
-    <row r="494" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A494">
         <v>42304.750409127999</v>
       </c>
@@ -4368,7 +4339,7 @@
         <v>22.130041579275201</v>
       </c>
     </row>
-    <row r="495" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A495">
         <v>42304.765161580901</v>
       </c>
@@ -4376,7 +4347,7 @@
         <v>3.8239613943904298</v>
       </c>
     </row>
-    <row r="496" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A496">
         <v>42304.773487078797</v>
       </c>
@@ -4384,7 +4355,7 @@
         <v>21.366360073974601</v>
       </c>
     </row>
-    <row r="497" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A497">
         <v>42304.7746500586</v>
       </c>
@@ -4392,7 +4363,7 @@
         <v>28.956420282505299</v>
       </c>
     </row>
-    <row r="498" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A498">
         <v>42304.815969438903</v>
       </c>
@@ -4400,7 +4371,7 @@
         <v>30.530129398713399</v>
       </c>
     </row>
-    <row r="499" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A499">
         <v>42304.8248499213</v>
       </c>
@@ -4408,7 +4379,7 @@
         <v>9.8878063263667499</v>
       </c>
     </row>
-    <row r="500" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A500">
         <v>42304.834169280199</v>
       </c>
@@ -4416,7 +4387,7 @@
         <v>34.600654803707997</v>
       </c>
     </row>
-    <row r="501" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A501">
         <v>42304.834350897399</v>
       </c>
@@ -4424,7 +4395,7 @@
         <v>20.5175198633173</v>
       </c>
     </row>
-    <row r="502" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A502">
         <v>42304.842752922203</v>
       </c>
@@ -4432,7 +4403,7 @@
         <v>28.409779712013599</v>
       </c>
     </row>
-    <row r="503" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A503">
         <v>42304.851141773303</v>
       </c>
@@ -4440,7 +4411,7 @@
         <v>22.410120072243799</v>
       </c>
     </row>
-    <row r="504" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A504">
         <v>42304.854932847702</v>
       </c>
@@ -4448,7 +4419,7 @@
         <v>18.890813154037598</v>
       </c>
     </row>
-    <row r="505" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A505">
         <v>42304.8614359848</v>
       </c>
@@ -4456,7 +4427,7 @@
         <v>16.6615366731913</v>
       </c>
     </row>
-    <row r="506" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A506">
         <v>42304.863231574796</v>
       </c>
@@ -4464,7 +4435,7 @@
         <v>17.7344154414839</v>
       </c>
     </row>
-    <row r="507" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A507">
         <v>42304.864494709102</v>
       </c>
@@ -4472,7 +4443,7 @@
         <v>32.645647085681603</v>
       </c>
     </row>
-    <row r="508" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A508">
         <v>42304.867487723801</v>
       </c>
@@ -4480,7 +4451,7 @@
         <v>7.2197237022577401</v>
       </c>
     </row>
-    <row r="509" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A509">
         <v>42304.870824149803</v>
       </c>
@@ -4488,7 +4459,7 @@
         <v>12.918679834384401</v>
       </c>
     </row>
-    <row r="510" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A510">
         <v>42304.884790873701</v>
       </c>
@@ -4496,7 +4467,7 @@
         <v>25.439755778005001</v>
       </c>
     </row>
-    <row r="511" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A511">
         <v>42304.891510925198</v>
       </c>
@@ -4504,7 +4475,7 @@
         <v>15.5517862652903</v>
       </c>
     </row>
-    <row r="512" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A512">
         <v>42304.902589803904</v>
       </c>
@@ -4512,7 +4483,7 @@
         <v>19.765019733471199</v>
       </c>
     </row>
-    <row r="513" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A513">
         <v>42304.913456280497</v>
       </c>
@@ -4520,7 +4491,7 @@
         <v>16.4576901676616</v>
       </c>
     </row>
-    <row r="514" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A514">
         <v>42304.955492742003</v>
       </c>
@@ -4528,7 +4499,7 @@
         <v>10.293175873775001</v>
       </c>
     </row>
-    <row r="515" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A515">
         <v>42304.966221476003</v>
       </c>
@@ -4536,7 +4507,7 @@
         <v>1.7819041067090999</v>
       </c>
     </row>
-    <row r="516" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A516">
         <v>42304.984136849504</v>
       </c>
@@ -4544,7 +4515,7 @@
         <v>19.880795604487702</v>
       </c>
     </row>
-    <row r="517" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A517">
         <v>42304.993570136998</v>
       </c>
@@ -4552,7 +4523,7 @@
         <v>13.011420371928599</v>
       </c>
     </row>
-    <row r="518" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A518">
         <v>42304.998489639198</v>
       </c>
@@ -4560,7 +4531,7 @@
         <v>19.132299956979899</v>
       </c>
     </row>
-    <row r="519" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A519">
         <v>42305.049318046898</v>
       </c>
@@ -4568,7 +4539,7 @@
         <v>15.046150627975701</v>
       </c>
     </row>
-    <row r="520" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A520">
         <v>42305.059065884001</v>
       </c>
@@ -4576,7 +4547,7 @@
         <v>37.352759379420696</v>
       </c>
     </row>
-    <row r="521" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A521">
         <v>42305.064060106102</v>
       </c>
@@ -4584,7 +4555,7 @@
         <v>13.0627431489216</v>
       </c>
     </row>
-    <row r="522" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A522">
         <v>42305.064092525499</v>
       </c>
@@ -4592,7 +4563,7 @@
         <v>34.842589218923898</v>
       </c>
     </row>
-    <row r="523" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A523">
         <v>42305.075581181503</v>
       </c>
@@ -4600,7 +4571,7 @@
         <v>20.422970995284899</v>
       </c>
     </row>
-    <row r="524" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A524">
         <v>42305.096773623103</v>
       </c>
@@ -4608,7 +4579,7 @@
         <v>31.749759530056998</v>
       </c>
     </row>
-    <row r="525" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A525">
         <v>42305.099189627697</v>
       </c>
@@ -4616,7 +4587,7 @@
         <v>33.80122296191</v>
       </c>
     </row>
-    <row r="526" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A526">
         <v>42305.120116209197</v>
       </c>
@@ -4624,7 +4595,7 @@
         <v>19.938320198448899</v>
       </c>
     </row>
-    <row r="527" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A527">
         <v>42305.124773078402</v>
       </c>
@@ -4632,7 +4603,7 @@
         <v>13.6039158312291</v>
       </c>
     </row>
-    <row r="528" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A528">
         <v>42305.135791453802</v>
       </c>
@@ -4640,7 +4611,7 @@
         <v>11.8259274425003</v>
       </c>
     </row>
-    <row r="529" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A529">
         <v>42305.155918136399</v>
       </c>
@@ -4648,7 +4619,7 @@
         <v>13.562697029127399</v>
       </c>
     </row>
-    <row r="530" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A530">
         <v>42305.161512204802</v>
       </c>
@@ -4656,7 +4627,7 @@
         <v>20.342014510683398</v>
       </c>
     </row>
-    <row r="531" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A531">
         <v>42305.170450564197</v>
       </c>
@@ -4664,7 +4635,7 @@
         <v>28.6320218228371</v>
       </c>
     </row>
-    <row r="532" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A532">
         <v>42305.171007634897</v>
       </c>
@@ -4672,7 +4643,7 @@
         <v>34.699989524436702</v>
       </c>
     </row>
-    <row r="533" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A533">
         <v>42305.186657370497</v>
       </c>
@@ -4680,7 +4651,7 @@
         <v>35.015636308271901</v>
       </c>
     </row>
-    <row r="534" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A534">
         <v>42305.194461174098</v>
       </c>
@@ -4688,7 +4659,7 @@
         <v>25.312762526601901</v>
       </c>
     </row>
-    <row r="535" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A535">
         <v>42305.204293626499</v>
       </c>
@@ -4696,7 +4667,7 @@
         <v>27.380108156851101</v>
       </c>
     </row>
-    <row r="536" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A536">
         <v>42305.207392486103</v>
       </c>
@@ -4704,7 +4675,7 @@
         <v>8.9469828365806201</v>
       </c>
     </row>
-    <row r="537" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A537">
         <v>42305.207919013999</v>
       </c>
@@ -4712,7 +4683,7 @@
         <v>23.729635615376299</v>
       </c>
     </row>
-    <row r="538" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A538">
         <v>42305.220133454401</v>
       </c>
@@ -4720,7 +4691,7 @@
         <v>20.3906298955919</v>
       </c>
     </row>
-    <row r="539" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A539">
         <v>42305.2234179964</v>
       </c>
@@ -4728,7 +4699,7 @@
         <v>16.25903933403</v>
       </c>
     </row>
-    <row r="540" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A540">
         <v>42305.228194493997</v>
       </c>
@@ -4736,7 +4707,7 @@
         <v>13.635564725391101</v>
       </c>
     </row>
-    <row r="541" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A541">
         <v>42305.244677949602</v>
       </c>
@@ -4744,7 +4715,7 @@
         <v>29.2419588871144</v>
       </c>
     </row>
-    <row r="542" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A542">
         <v>42305.245633500599</v>
       </c>
@@ -4752,7 +4723,7 @@
         <v>14.4675712705327</v>
       </c>
     </row>
-    <row r="543" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A543">
         <v>42305.248378429598</v>
       </c>
@@ -4760,7 +4731,7 @@
         <v>14.1241790915631</v>
       </c>
     </row>
-    <row r="544" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A544">
         <v>42305.248400683602</v>
       </c>
@@ -4768,7 +4739,7 @@
         <v>22.979674401354199</v>
       </c>
     </row>
-    <row r="545" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A545">
         <v>42305.257707288001</v>
       </c>
@@ -4776,7 +4747,7 @@
         <v>13.443790312261401</v>
       </c>
     </row>
-    <row r="546" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A546">
         <v>42305.262762688697</v>
       </c>
@@ -4784,7 +4755,7 @@
         <v>27.598372579487801</v>
       </c>
     </row>
-    <row r="547" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A547">
         <v>42305.277654895799</v>
       </c>
@@ -4792,7 +4763,7 @@
         <v>20.445028663532501</v>
       </c>
     </row>
-    <row r="548" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A548">
         <v>42305.278908321001</v>
       </c>
@@ -4800,7 +4771,7 @@
         <v>15.755541026229499</v>
       </c>
     </row>
-    <row r="549" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A549">
         <v>42305.280027160799</v>
       </c>
@@ -4808,7 +4779,7 @@
         <v>9.5505698638960901</v>
       </c>
     </row>
-    <row r="550" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A550">
         <v>42305.286121060803</v>
       </c>
@@ -4816,7 +4787,7 @@
         <v>15.5055425586044</v>
       </c>
     </row>
-    <row r="551" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A551">
         <v>42305.311721666498</v>
       </c>
@@ -4824,7 +4795,7 @@
         <v>13.627235544060801</v>
       </c>
     </row>
-    <row r="552" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A552">
         <v>42305.319251675202</v>
       </c>
@@ -4832,7 +4803,7 @@
         <v>9.5944633127792596</v>
       </c>
     </row>
-    <row r="553" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A553">
         <v>42305.327992738603</v>
       </c>
@@ -4840,7 +4811,7 @@
         <v>24.911033677606799</v>
       </c>
     </row>
-    <row r="554" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A554">
         <v>42305.331653078603</v>
       </c>
@@ -4848,7 +4819,7 @@
         <v>20.907401841659599</v>
       </c>
     </row>
-    <row r="555" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A555">
         <v>42305.337157795999</v>
       </c>
@@ -4856,7 +4827,7 @@
         <v>13.716140792645501</v>
       </c>
     </row>
-    <row r="556" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A556">
         <v>42305.348567028799</v>
       </c>
@@ -4864,7 +4835,7 @@
         <v>17.905300614401</v>
       </c>
     </row>
-    <row r="557" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A557">
         <v>42305.354123243596</v>
       </c>
@@ -4872,7 +4843,7 @@
         <v>20.654838120407099</v>
       </c>
     </row>
-    <row r="558" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A558">
         <v>42305.363635069603</v>
       </c>
@@ -4880,7 +4851,7 @@
         <v>7.0002983766726103</v>
       </c>
     </row>
-    <row r="559" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A559">
         <v>42305.393593734298</v>
       </c>
@@ -4888,7 +4859,7 @@
         <v>10.060530637924099</v>
       </c>
     </row>
-    <row r="560" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A560">
         <v>42305.416598492498</v>
       </c>
@@ -4896,7 +4867,7 @@
         <v>29.130491603208601</v>
       </c>
     </row>
-    <row r="561" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A561">
         <v>42305.4206714131</v>
       </c>
@@ -4904,7 +4875,7 @@
         <v>18.134866674180898</v>
       </c>
     </row>
-    <row r="562" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A562">
         <v>42305.431550974798</v>
       </c>
@@ -4912,7 +4883,7 @@
         <v>31.447032509836301</v>
       </c>
     </row>
-    <row r="563" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A563">
         <v>42305.432277350599</v>
       </c>
@@ -4920,7 +4891,7 @@
         <v>6.5635666707079698</v>
       </c>
     </row>
-    <row r="564" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A564">
         <v>42305.441476387197</v>
       </c>
@@ -4928,7 +4899,7 @@
         <v>26.086200660712599</v>
       </c>
     </row>
-    <row r="565" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A565">
         <v>42305.458673496702</v>
       </c>
@@ -4936,7 +4907,7 @@
         <v>24.1541330856743</v>
       </c>
     </row>
-    <row r="566" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A566">
         <v>42305.480588882201</v>
       </c>
@@ -4944,7 +4915,7 @@
         <v>24.041463594662201</v>
       </c>
     </row>
-    <row r="567" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A567">
         <v>42305.4944585064</v>
       </c>
@@ -4952,7 +4923,7 @@
         <v>21.0264938265327</v>
       </c>
     </row>
-    <row r="568" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A568">
         <v>42305.498591823198</v>
       </c>
@@ -4960,7 +4931,7 @@
         <v>4.5619467402647604</v>
       </c>
     </row>
-    <row r="569" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A569">
         <v>42305.510704781998</v>
       </c>
@@ -4968,7 +4939,7 @@
         <v>9.1298670396388992</v>
       </c>
     </row>
-    <row r="570" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A570">
         <v>42305.511272539603</v>
       </c>
@@ -4976,7 +4947,7 @@
         <v>18.894903569513399</v>
       </c>
     </row>
-    <row r="571" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A571">
         <v>42305.531566799698</v>
       </c>
@@ -4984,7 +4955,7 @@
         <v>13.386345933116701</v>
       </c>
     </row>
-    <row r="572" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A572">
         <v>42305.538014183199</v>
       </c>
@@ -4992,7 +4963,7 @@
         <v>23.991108629500602</v>
       </c>
     </row>
-    <row r="573" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A573">
         <v>42305.540894200501</v>
       </c>
@@ -5000,7 +4971,7 @@
         <v>10.017909096331501</v>
       </c>
     </row>
-    <row r="574" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A574">
         <v>42305.5498950564</v>
       </c>
@@ -5008,7 +4979,7 @@
         <v>11.1517238746847</v>
       </c>
     </row>
-    <row r="575" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A575">
         <v>42305.559021859699</v>
       </c>
@@ -5016,7 +4987,7 @@
         <v>13.9998293807663</v>
       </c>
     </row>
-    <row r="576" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A576">
         <v>42305.568012862102</v>
       </c>
@@ -5024,7 +4995,7 @@
         <v>16.601619669765999</v>
       </c>
     </row>
-    <row r="577" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A577">
         <v>42305.571609383303</v>
       </c>
@@ -5032,7 +5003,7 @@
         <v>32.986998615737498</v>
       </c>
     </row>
-    <row r="578" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A578">
         <v>42305.5737406685</v>
       </c>
@@ -5040,7 +5011,7 @@
         <v>21.432970111166298</v>
       </c>
     </row>
-    <row r="579" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A579">
         <v>42305.581061804798</v>
       </c>
@@ -5048,7 +5019,7 @@
         <v>31.913805004522899</v>
       </c>
     </row>
-    <row r="580" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A580">
         <v>42305.581798355299</v>
       </c>
@@ -5056,7 +5027,7 @@
         <v>10.6653906621776</v>
       </c>
     </row>
-    <row r="581" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A581">
         <v>42305.589009134601</v>
       </c>
@@ -5064,7 +5035,7 @@
         <v>22.652866861547199</v>
       </c>
     </row>
-    <row r="582" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A582">
         <v>42305.598325070903</v>
       </c>
@@ -5072,7 +5043,7 @@
         <v>13.8636132229153</v>
       </c>
     </row>
-    <row r="583" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A583">
         <v>42305.600818174898</v>
       </c>
@@ -5080,7 +5051,7 @@
         <v>27.361022990982502</v>
       </c>
     </row>
-    <row r="584" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A584">
         <v>42305.620478674602</v>
       </c>
@@ -5088,7 +5059,7 @@
         <v>22.984680577040599</v>
       </c>
     </row>
-    <row r="585" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A585">
         <v>42305.6240216773</v>
       </c>
@@ -5096,7 +5067,7 @@
         <v>10.8945981161859</v>
       </c>
     </row>
-    <row r="586" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A586">
         <v>42305.636945217397</v>
       </c>
@@ -5104,7 +5075,7 @@
         <v>33.211245491614498</v>
       </c>
     </row>
-    <row r="587" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A587">
         <v>42305.662208535403</v>
       </c>
@@ -5112,7 +5083,7 @@
         <v>22.4327783690701</v>
       </c>
     </row>
-    <row r="588" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A588">
         <v>42305.665569962701</v>
       </c>
@@ -5120,7 +5091,7 @@
         <v>24.169848428311301</v>
       </c>
     </row>
-    <row r="589" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A589">
         <v>42305.679576570503</v>
       </c>
@@ -5128,7 +5099,7 @@
         <v>31.4784113856335</v>
       </c>
     </row>
-    <row r="590" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A590">
         <v>42305.692697960803</v>
       </c>
@@ -5136,7 +5107,7 @@
         <v>7.0557538418746901</v>
       </c>
     </row>
-    <row r="591" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A591">
         <v>42305.699586297596</v>
       </c>
@@ -5144,7 +5115,7 @@
         <v>22.505285094002801</v>
       </c>
     </row>
-    <row r="592" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A592">
         <v>42305.706151213999</v>
       </c>
@@ -5152,7 +5123,7 @@
         <v>11.6959662708254</v>
       </c>
     </row>
-    <row r="593" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A593">
         <v>42305.711734730503</v>
       </c>
@@ -5160,7 +5131,7 @@
         <v>25.050275358033101</v>
       </c>
     </row>
-    <row r="594" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A594">
         <v>42305.726563156</v>
       </c>
@@ -5168,7 +5139,7 @@
         <v>16.6206318292551</v>
       </c>
     </row>
-    <row r="595" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A595">
         <v>42305.728134199497</v>
       </c>
@@ -5176,7 +5147,7 @@
         <v>27.097737185334601</v>
       </c>
     </row>
-    <row r="596" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A596">
         <v>42305.753293907801</v>
       </c>
@@ -5184,7 +5155,7 @@
         <v>28.453892794708199</v>
       </c>
     </row>
-    <row r="597" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A597">
         <v>42305.753685831602</v>
       </c>
@@ -5192,7 +5163,7 @@
         <v>24.909666263182501</v>
       </c>
     </row>
-    <row r="598" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A598">
         <v>42305.754828853103</v>
       </c>
@@ -5200,7 +5171,7 @@
         <v>19.052430428311499</v>
       </c>
     </row>
-    <row r="599" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A599">
         <v>42305.769457356299</v>
       </c>
@@ -5208,7 +5179,7 @@
         <v>17.453295264174301</v>
       </c>
     </row>
-    <row r="600" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A600">
         <v>42305.777714686097</v>
       </c>
@@ -5216,7 +5187,7 @@
         <v>10.787873620618701</v>
       </c>
     </row>
-    <row r="601" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A601">
         <v>42305.7839209128</v>
       </c>
@@ -5224,7 +5195,7 @@
         <v>26.564290028980299</v>
       </c>
     </row>
-    <row r="602" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A602">
         <v>42305.785772554504</v>
       </c>
@@ -5232,7 +5203,7 @@
         <v>17.332549995401301</v>
       </c>
     </row>
-    <row r="603" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A603">
         <v>42305.800143342</v>
       </c>
@@ -5240,7 +5211,7 @@
         <v>6.9064572300058202</v>
       </c>
     </row>
-    <row r="604" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A604">
         <v>42305.810385669502</v>
       </c>
@@ -5248,7 +5219,7 @@
         <v>28.4458847054747</v>
       </c>
     </row>
-    <row r="605" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A605">
         <v>42305.815530277003</v>
       </c>
@@ -5256,7 +5227,7 @@
         <v>18.751925487962399</v>
       </c>
     </row>
-    <row r="606" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A606">
         <v>42305.8197106769</v>
       </c>
@@ -5264,7 +5235,7 @@
         <v>25.112732199291798</v>
       </c>
     </row>
-    <row r="607" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A607">
         <v>42305.829539641498</v>
       </c>
@@ -5272,7 +5243,7 @@
         <v>5.4557839239675703</v>
       </c>
     </row>
-    <row r="608" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A608">
         <v>42305.8569717071</v>
       </c>
@@ -5280,7 +5251,7 @@
         <v>26.858954188884798</v>
       </c>
     </row>
-    <row r="609" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A609">
         <v>42305.889508342698</v>
       </c>
@@ -5288,7 +5259,7 @@
         <v>20.756231818478401</v>
       </c>
     </row>
-    <row r="610" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A610">
         <v>42305.908016940703</v>
       </c>
@@ -5296,7 +5267,7 @@
         <v>27.514801537039801</v>
       </c>
     </row>
-    <row r="611" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A611">
         <v>42305.913112765498</v>
       </c>
@@ -5304,7 +5275,7 @@
         <v>8.1214863948181009</v>
       </c>
     </row>
-    <row r="612" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A612">
         <v>42305.922682105302</v>
       </c>
@@ -5312,7 +5283,7 @@
         <v>32.430137338378302</v>
       </c>
     </row>
-    <row r="613" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A613">
         <v>42305.931413692502</v>
       </c>
@@ -5320,7 +5291,7 @@
         <v>7.2818964994331798</v>
       </c>
     </row>
-    <row r="614" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A614">
         <v>42305.9341326004</v>
       </c>
@@ -5328,7 +5299,7 @@
         <v>35.140642536317301</v>
       </c>
     </row>
-    <row r="615" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A615">
         <v>42305.942466610599</v>
       </c>
@@ -5336,7 +5307,7 @@
         <v>9.6794483171557602</v>
       </c>
     </row>
-    <row r="616" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A616">
         <v>42305.954972811101</v>
       </c>
@@ -5344,7 +5315,7 @@
         <v>26.069281471841499</v>
       </c>
     </row>
-    <row r="617" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A617">
         <v>42305.960420349897</v>
       </c>
@@ -5352,7 +5323,7 @@
         <v>22.208753585696201</v>
       </c>
     </row>
-    <row r="618" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A618">
         <v>42305.9827614569</v>
       </c>
@@ -5360,7 +5331,7 @@
         <v>14.4364993121021</v>
       </c>
     </row>
-    <row r="619" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A619">
         <v>42305.983602022097</v>
       </c>
@@ -5368,7 +5339,7 @@
         <v>14.407442204948801</v>
       </c>
     </row>
-    <row r="620" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A620">
         <v>42305.985548518998</v>
       </c>
@@ -5376,7 +5347,7 @@
         <v>32.351417061812498</v>
       </c>
     </row>
-    <row r="621" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A621">
         <v>42305.988715914602</v>
       </c>
@@ -5384,7 +5355,7 @@
         <v>25.337101572031901</v>
       </c>
     </row>
-    <row r="622" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A622">
         <v>42305.992234730802</v>
       </c>
@@ -5392,7 +5363,7 @@
         <v>34.405531466226201</v>
       </c>
     </row>
-    <row r="623" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A623">
         <v>42306.005903813297</v>
       </c>
@@ -5400,7 +5371,7 @@
         <v>5.6292187415452597</v>
       </c>
     </row>
-    <row r="624" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A624">
         <v>42306.0080184744</v>
       </c>
@@ -5408,7 +5379,7 @@
         <v>8.8383513834606209</v>
       </c>
     </row>
-    <row r="625" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A625">
         <v>42306.008908483498</v>
       </c>
@@ -5416,7 +5387,7 @@
         <v>36.416772220016298</v>
       </c>
     </row>
-    <row r="626" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A626">
         <v>42306.021846757198</v>
       </c>
@@ -5424,7 +5395,7 @@
         <v>31.404891223374602</v>
       </c>
     </row>
-    <row r="627" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A627">
         <v>42306.039234843702</v>
       </c>
@@ -5432,7 +5403,7 @@
         <v>10.104051166607199</v>
       </c>
     </row>
-    <row r="628" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A628">
         <v>42306.054808322602</v>
       </c>
@@ -5440,7 +5411,7 @@
         <v>26.652638775051699</v>
       </c>
     </row>
-    <row r="629" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A629">
         <v>42306.062403686898</v>
       </c>
@@ -5448,7 +5419,7 @@
         <v>31.6075325881319</v>
       </c>
     </row>
-    <row r="630" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A630">
         <v>42306.067252343397</v>
       </c>
@@ -5456,7 +5427,7 @@
         <v>14.0578830404766</v>
       </c>
     </row>
-    <row r="631" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A631">
         <v>42306.077069242703</v>
       </c>
@@ -5464,7 +5435,7 @@
         <v>14.669973024608399</v>
       </c>
     </row>
-    <row r="632" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A632">
         <v>42306.098946853701</v>
       </c>
@@ -5472,7 +5443,7 @@
         <v>10.860817992673001</v>
       </c>
     </row>
-    <row r="633" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A633">
         <v>42306.128756395003</v>
       </c>
@@ -5480,7 +5451,7 @@
         <v>19.707401066612999</v>
       </c>
     </row>
-    <row r="634" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A634">
         <v>42306.131565985801</v>
       </c>
@@ -5488,7 +5459,7 @@
         <v>12.7678927990007</v>
       </c>
     </row>
-    <row r="635" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A635">
         <v>42306.1379815041</v>
       </c>
@@ -5496,7 +5467,7 @@
         <v>11.406741156043999</v>
       </c>
     </row>
-    <row r="636" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A636">
         <v>42306.162048430997</v>
       </c>
@@ -5504,7 +5475,7 @@
         <v>6.8293909917111701</v>
       </c>
     </row>
-    <row r="637" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A637">
         <v>42306.184441463898</v>
       </c>
@@ -5512,7 +5483,7 @@
         <v>18.626982301144601</v>
       </c>
     </row>
-    <row r="638" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A638">
         <v>42306.191120187897</v>
       </c>
@@ -5520,7 +5491,7 @@
         <v>25.249255144124199</v>
       </c>
     </row>
-    <row r="639" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A639">
         <v>42306.193160715702</v>
       </c>
@@ -5528,7 +5499,7 @@
         <v>20.0661812842011</v>
       </c>
     </row>
-    <row r="640" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A640">
         <v>42306.207331818398</v>
       </c>
@@ -5536,7 +5507,7 @@
         <v>32.633242976770603</v>
       </c>
     </row>
-    <row r="641" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A641">
         <v>42306.210884716304</v>
       </c>
@@ -5544,7 +5515,7 @@
         <v>19.815994009543001</v>
       </c>
     </row>
-    <row r="642" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A642">
         <v>42306.232989732998</v>
       </c>
@@ -5552,7 +5523,7 @@
         <v>7.3933025209376204</v>
       </c>
     </row>
-    <row r="643" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A643">
         <v>42306.233238219203</v>
       </c>
@@ -5560,7 +5531,7 @@
         <v>30.079256136313401</v>
       </c>
     </row>
-    <row r="644" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A644">
         <v>42306.245336891603</v>
       </c>
@@ -5568,7 +5539,7 @@
         <v>11.413075900688501</v>
       </c>
     </row>
-    <row r="645" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A645">
         <v>42306.2713761782</v>
       </c>
@@ -5576,7 +5547,7 @@
         <v>11.697901698910499</v>
       </c>
     </row>
-    <row r="646" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A646">
         <v>42306.281883387797</v>
       </c>
@@ -5584,7 +5555,7 @@
         <v>31.190372487148998</v>
       </c>
     </row>
-    <row r="647" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A647">
         <v>42306.298639553301</v>
       </c>
@@ -5592,7 +5563,7 @@
         <v>20.6394495509347</v>
       </c>
     </row>
-    <row r="648" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A648">
         <v>42306.3209509511</v>
       </c>
@@ -5600,7 +5571,7 @@
         <v>18.345175180276801</v>
       </c>
     </row>
-    <row r="649" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A649">
         <v>42306.3247371826</v>
       </c>
@@ -5608,7 +5579,7 @@
         <v>13.468383795028799</v>
       </c>
     </row>
-    <row r="650" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A650">
         <v>42306.325906639802</v>
       </c>
@@ -5616,7 +5587,7 @@
         <v>23.132392478293401</v>
       </c>
     </row>
-    <row r="651" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A651">
         <v>42306.3309958475</v>
       </c>
@@ -5624,7 +5595,7 @@
         <v>25.347281924690598</v>
       </c>
     </row>
-    <row r="652" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A652">
         <v>42306.335753169202</v>
       </c>
@@ -5632,7 +5603,7 @@
         <v>9.1598526102432398</v>
       </c>
     </row>
-    <row r="653" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A653">
         <v>42306.342871072302</v>
       </c>
@@ -5640,7 +5611,7 @@
         <v>20.831257547557801</v>
       </c>
     </row>
-    <row r="654" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A654">
         <v>42306.368197342999</v>
       </c>
@@ -5648,7 +5619,7 @@
         <v>20.813046940187501</v>
       </c>
     </row>
-    <row r="655" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A655">
         <v>42306.369617135002</v>
       </c>
@@ -5656,7 +5627,7 @@
         <v>11.684935266719901</v>
       </c>
     </row>
-    <row r="656" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A656">
         <v>42306.370049669204</v>
       </c>
@@ -5664,7 +5635,7 @@
         <v>16.810542023226699</v>
       </c>
     </row>
-    <row r="657" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A657">
         <v>42306.375608743103</v>
       </c>
@@ -5672,7 +5643,7 @@
         <v>20.0831826622926</v>
       </c>
     </row>
-    <row r="658" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A658">
         <v>42306.379943207001</v>
       </c>
@@ -5680,7 +5651,7 @@
         <v>9.5002119185021208</v>
       </c>
     </row>
-    <row r="659" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A659">
         <v>42306.3850885875</v>
       </c>
@@ -5688,7 +5659,7 @@
         <v>22.865691475376401</v>
       </c>
     </row>
-    <row r="660" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A660">
         <v>42306.390280515501</v>
       </c>
@@ -5696,7 +5667,7 @@
         <v>11.3150271967879</v>
       </c>
     </row>
-    <row r="661" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A661">
         <v>42306.393969256198</v>
       </c>
@@ -5704,7 +5675,7 @@
         <v>10.9337673007372</v>
       </c>
     </row>
-    <row r="662" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A662">
         <v>42306.412820003497</v>
       </c>
@@ -5712,7 +5683,7 @@
         <v>12.687895436990599</v>
       </c>
     </row>
-    <row r="663" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A663">
         <v>42306.418839867998</v>
       </c>
@@ -5720,7 +5691,7 @@
         <v>12.946124989735299</v>
       </c>
     </row>
-    <row r="664" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A664">
         <v>42306.434216311602</v>
       </c>
@@ -5728,7 +5699,7 @@
         <v>8.4933174689914992</v>
       </c>
     </row>
-    <row r="665" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A665">
         <v>42306.438540433199</v>
       </c>
@@ -5736,7 +5707,7 @@
         <v>14.026298090925099</v>
       </c>
     </row>
-    <row r="666" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A666">
         <v>42306.442129503703</v>
       </c>
@@ -5744,7 +5715,7 @@
         <v>17.014097378681502</v>
       </c>
     </row>
-    <row r="667" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A667">
         <v>42306.468832022401</v>
       </c>
@@ -5752,7 +5723,7 @@
         <v>36.140929820006299</v>
       </c>
     </row>
-    <row r="668" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A668">
         <v>42306.469182311499</v>
       </c>
@@ -5760,7 +5731,7 @@
         <v>26.7173427208206</v>
       </c>
     </row>
-    <row r="669" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A669">
         <v>42306.4867411374</v>
       </c>
@@ -5768,7 +5739,7 @@
         <v>13.078062847086899</v>
       </c>
     </row>
-    <row r="670" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A670">
         <v>42306.487810044302</v>
       </c>
@@ -5776,7 +5747,7 @@
         <v>19.879270759289199</v>
       </c>
     </row>
-    <row r="671" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A671">
         <v>42306.489170445901</v>
       </c>
@@ -5784,7 +5755,7 @@
         <v>22.017663703999201</v>
       </c>
     </row>
-    <row r="672" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A672">
         <v>42306.490710951301</v>
       </c>
@@ -5792,7 +5763,7 @@
         <v>15.966344250896601</v>
       </c>
     </row>
-    <row r="673" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A673">
         <v>42306.517226367199</v>
       </c>
@@ -5800,7 +5771,7 @@
         <v>26.322878439652101</v>
       </c>
     </row>
-    <row r="674" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A674">
         <v>42306.5255324471</v>
       </c>
@@ -5808,7 +5779,7 @@
         <v>10.881309297360101</v>
       </c>
     </row>
-    <row r="675" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A675">
         <v>42306.538042507898</v>
       </c>
@@ -5816,7 +5787,7 @@
         <v>36.767167460736502</v>
       </c>
     </row>
-    <row r="676" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A676">
         <v>42306.539833110699</v>
       </c>
@@ -5824,7 +5795,7 @@
         <v>18.178580824834899</v>
       </c>
     </row>
-    <row r="677" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A677">
         <v>42306.540702588798</v>
       </c>
@@ -5832,7 +5803,7 @@
         <v>22.243434363367001</v>
       </c>
     </row>
-    <row r="678" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A678">
         <v>42306.561645245099</v>
       </c>
@@ -5840,7 +5811,7 @@
         <v>27.4435010890931</v>
       </c>
     </row>
-    <row r="679" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A679">
         <v>42306.574646904497</v>
       </c>
@@ -5848,7 +5819,7 @@
         <v>7.4164177153238597</v>
       </c>
     </row>
-    <row r="680" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A680">
         <v>42306.588120670101</v>
       </c>
@@ -5856,7 +5827,7 @@
         <v>35.314749992337902</v>
       </c>
     </row>
-    <row r="681" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A681">
         <v>42306.591464523401</v>
       </c>
@@ -5864,7 +5835,7 @@
         <v>26.102493311610001</v>
       </c>
     </row>
-    <row r="682" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A682">
         <v>42306.597124631902</v>
       </c>
@@ -5872,7 +5843,7 @@
         <v>26.995711901521101</v>
       </c>
     </row>
-    <row r="683" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A683">
         <v>42306.6069984071</v>
       </c>
@@ -5880,7 +5851,7 @@
         <v>26.171102535232802</v>
       </c>
     </row>
-    <row r="684" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A684">
         <v>42306.622774937598</v>
       </c>
@@ -5888,7 +5859,7 @@
         <v>26.393209706723098</v>
       </c>
     </row>
-    <row r="685" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A685">
         <v>42306.628810168899</v>
       </c>
@@ -5896,7 +5867,7 @@
         <v>6.11327871662969</v>
       </c>
     </row>
-    <row r="686" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A686">
         <v>42306.630607872998</v>
       </c>
@@ -5904,7 +5875,7 @@
         <v>33.321112474563797</v>
       </c>
     </row>
-    <row r="687" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A687">
         <v>42306.6424869767</v>
       </c>
@@ -5912,7 +5883,7 @@
         <v>3.4372769445965701</v>
       </c>
     </row>
-    <row r="688" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A688">
         <v>42306.650870598503</v>
       </c>
@@ -5920,7 +5891,7 @@
         <v>15.568659633088901</v>
       </c>
     </row>
-    <row r="689" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A689">
         <v>42306.683994176899</v>
       </c>
@@ -5928,7 +5899,7 @@
         <v>12.626890248286401</v>
       </c>
     </row>
-    <row r="690" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A690">
         <v>42306.684725400199</v>
       </c>
@@ -5936,7 +5907,7 @@
         <v>23.726235840809601</v>
       </c>
     </row>
-    <row r="691" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A691">
         <v>42306.684970053902</v>
       </c>
@@ -5944,7 +5915,7 @@
         <v>8.2208243844891307</v>
       </c>
     </row>
-    <row r="692" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A692">
         <v>42306.689066327403</v>
       </c>
@@ -5952,7 +5923,7 @@
         <v>33.722738319278101</v>
       </c>
     </row>
-    <row r="693" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A693">
         <v>42306.726421728599</v>
       </c>
@@ -5960,7 +5931,7 @@
         <v>17.737117813739498</v>
       </c>
     </row>
-    <row r="694" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A694">
         <v>42306.744412841901</v>
       </c>
@@ -5968,7 +5939,7 @@
         <v>27.5866049737024</v>
       </c>
     </row>
-    <row r="695" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A695">
         <v>42306.748225192401</v>
       </c>
@@ -5976,7 +5947,7 @@
         <v>28.581946608361498</v>
       </c>
     </row>
-    <row r="696" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A696">
         <v>42306.755086828103</v>
       </c>
@@ -5984,7 +5955,7 @@
         <v>33.395728635898301</v>
       </c>
     </row>
-    <row r="697" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A697">
         <v>42306.757985001597</v>
       </c>
@@ -5992,7 +5963,7 @@
         <v>15.354500834426201</v>
       </c>
     </row>
-    <row r="698" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A698">
         <v>42306.760493756599</v>
       </c>
@@ -6000,7 +5971,7 @@
         <v>23.9293355466768</v>
       </c>
     </row>
-    <row r="699" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A699">
         <v>42306.7641567928</v>
       </c>
@@ -6008,7 +5979,7 @@
         <v>5.7717800748540604</v>
       </c>
     </row>
-    <row r="700" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A700">
         <v>42306.783869264902</v>
       </c>
@@ -6016,7 +5987,7 @@
         <v>4.21008438703472</v>
       </c>
     </row>
-    <row r="701" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A701">
         <v>42306.791947524704</v>
       </c>
@@ -6024,7 +5995,7 @@
         <v>34.201755117228799</v>
       </c>
     </row>
-    <row r="702" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A702">
         <v>42306.792482932702</v>
       </c>
@@ -6032,7 +6003,7 @@
         <v>18.118718406227899</v>
       </c>
     </row>
-    <row r="703" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A703">
         <v>42306.808112081497</v>
       </c>
@@ -6040,7 +6011,7 @@
         <v>11.8382017716054</v>
       </c>
     </row>
-    <row r="704" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A704">
         <v>42306.813243538701</v>
       </c>
@@ -6048,7 +6019,7 @@
         <v>28.0550379514127</v>
       </c>
     </row>
-    <row r="705" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A705">
         <v>42306.815160708204</v>
       </c>
@@ -6056,7 +6027,7 @@
         <v>38.824233906371497</v>
       </c>
     </row>
-    <row r="706" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A706">
         <v>42306.849557912101</v>
       </c>
@@ -6064,7 +6035,7 @@
         <v>20.183617209832899</v>
       </c>
     </row>
-    <row r="707" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A707">
         <v>42306.855338771202</v>
       </c>
@@ -6072,7 +6043,7 @@
         <v>20.2529199800911</v>
       </c>
     </row>
-    <row r="708" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A708">
         <v>42306.872891985899</v>
       </c>
@@ -6080,7 +6051,7 @@
         <v>24.079135715368501</v>
       </c>
     </row>
-    <row r="709" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A709">
         <v>42306.884894713403</v>
       </c>
@@ -6088,7 +6059,7 @@
         <v>20.675881140609199</v>
       </c>
     </row>
-    <row r="710" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A710">
         <v>42306.899362661199</v>
       </c>
@@ -6096,7 +6067,7 @@
         <v>18.581834165126001</v>
       </c>
     </row>
-    <row r="711" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A711">
         <v>42306.900050014498</v>
       </c>
@@ -6104,7 +6075,7 @@
         <v>3.0055615284818802</v>
       </c>
     </row>
-    <row r="712" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A712">
         <v>42306.908013660999</v>
       </c>
@@ -6112,7 +6083,7 @@
         <v>17.446179577580299</v>
       </c>
     </row>
-    <row r="713" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A713">
         <v>42306.916632991197</v>
       </c>
@@ -6120,7 +6091,7 @@
         <v>17.692749148180599</v>
       </c>
     </row>
-    <row r="714" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A714">
         <v>42306.923782256701</v>
       </c>
@@ -6128,7 +6099,7 @@
         <v>20.881250963968402</v>
       </c>
     </row>
-    <row r="715" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A715">
         <v>42306.950303213998</v>
       </c>
@@ -6136,7 +6107,7 @@
         <v>21.112932970095098</v>
       </c>
     </row>
-    <row r="716" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A716">
         <v>42306.971553961099</v>
       </c>
@@ -6144,7 +6115,7 @@
         <v>22.7731555028438</v>
       </c>
     </row>
-    <row r="717" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A717">
         <v>42306.993583028401</v>
       </c>
@@ -6152,7 +6123,7 @@
         <v>10.6712862230182</v>
       </c>
     </row>
-    <row r="718" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A718">
         <v>42306.9952339421</v>
       </c>
@@ -6160,7 +6131,7 @@
         <v>27.385016143194601</v>
       </c>
     </row>
-    <row r="719" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A719">
         <v>42307.003839065001</v>
       </c>
@@ -6168,7 +6139,7 @@
         <v>21.0393980091199</v>
       </c>
     </row>
-    <row r="720" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A720">
         <v>42307.009426222998</v>
       </c>
@@ -6176,7 +6147,7 @@
         <v>29.351821790870702</v>
       </c>
     </row>
-    <row r="721" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A721">
         <v>42307.022652126303</v>
       </c>
@@ -6184,7 +6155,7 @@
         <v>26.714346125125601</v>
       </c>
     </row>
-    <row r="722" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A722">
         <v>42307.036315965503</v>
       </c>
@@ -6192,7 +6163,7 @@
         <v>33.4610798043161</v>
       </c>
     </row>
-    <row r="723" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A723">
         <v>42307.055826741198</v>
       </c>
@@ -6200,7 +6171,7 @@
         <v>15.7639207597511</v>
       </c>
     </row>
-    <row r="724" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A724">
         <v>42307.069501830701</v>
       </c>
@@ -6208,7 +6179,7 @@
         <v>22.893474952292301</v>
       </c>
     </row>
-    <row r="725" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A725">
         <v>42307.096576468597</v>
       </c>
@@ -6216,7 +6187,7 @@
         <v>14.913339059629401</v>
       </c>
     </row>
-    <row r="726" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A726">
         <v>42307.097003829302</v>
       </c>
@@ -6224,7 +6195,7 @@
         <v>16.881444945429799</v>
       </c>
     </row>
-    <row r="727" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A727">
         <v>42307.097742703401</v>
       </c>
@@ -6232,7 +6203,7 @@
         <v>21.3061195011345</v>
       </c>
     </row>
-    <row r="728" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A728">
         <v>42307.104111511202</v>
       </c>
@@ -6240,7 +6211,7 @@
         <v>11.0685786422478</v>
       </c>
     </row>
-    <row r="729" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A729">
         <v>42307.113399689399</v>
       </c>
@@ -6248,7 +6219,7 @@
         <v>23.510959967240499</v>
       </c>
     </row>
-    <row r="730" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A730">
         <v>42307.1180509892</v>
       </c>
@@ -6256,7 +6227,7 @@
         <v>12.426566936195901</v>
       </c>
     </row>
-    <row r="731" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A731">
         <v>42307.122105530201</v>
       </c>
@@ -6264,7 +6235,7 @@
         <v>9.8036705671399798</v>
       </c>
     </row>
-    <row r="732" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A732">
         <v>42307.122783323503</v>
       </c>
@@ -6272,7 +6243,7 @@
         <v>13.6019794997611</v>
       </c>
     </row>
-    <row r="733" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A733">
         <v>42307.130896572999</v>
       </c>
@@ -6280,7 +6251,7 @@
         <v>15.3081222256601</v>
       </c>
     </row>
-    <row r="734" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A734">
         <v>42307.143307969498</v>
       </c>
@@ -6288,7 +6259,7 @@
         <v>12.293308277116701</v>
       </c>
     </row>
-    <row r="735" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A735">
         <v>42307.146686435401</v>
       </c>
@@ -6296,7 +6267,7 @@
         <v>25.187775539681699</v>
       </c>
     </row>
-    <row r="736" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A736">
         <v>42307.1613332204</v>
       </c>
@@ -6304,7 +6275,7 @@
         <v>25.200360558010001</v>
       </c>
     </row>
-    <row r="737" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A737">
         <v>42307.167543410003</v>
       </c>
@@ -6312,7 +6283,7 @@
         <v>26.0509065698493</v>
       </c>
     </row>
-    <row r="738" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A738">
         <v>42307.173872096399</v>
       </c>
@@ -6320,7 +6291,7 @@
         <v>16.041491862166101</v>
       </c>
     </row>
-    <row r="739" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A739">
         <v>42307.175115947597</v>
       </c>
@@ -6328,7 +6299,7 @@
         <v>9.7160737243789494</v>
       </c>
     </row>
-    <row r="740" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A740">
         <v>42307.182299620697</v>
       </c>
@@ -6336,7 +6307,7 @@
         <v>22.0324464853657</v>
       </c>
     </row>
-    <row r="741" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A741">
         <v>42307.188154538599</v>
       </c>
@@ -6344,7 +6315,7 @@
         <v>32.175465912984002</v>
       </c>
     </row>
-    <row r="742" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A742">
         <v>42307.200628124199</v>
       </c>
@@ -6352,7 +6323,7 @@
         <v>8.8242205372353695</v>
       </c>
     </row>
-    <row r="743" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A743">
         <v>42307.209466250097</v>
       </c>
@@ -6360,7 +6331,7 @@
         <v>16.416995579118201</v>
       </c>
     </row>
-    <row r="744" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A744">
         <v>42307.229381452496</v>
       </c>
@@ -6368,7 +6339,7 @@
         <v>26.741801832361698</v>
       </c>
     </row>
-    <row r="745" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A745">
         <v>42307.274431459802</v>
       </c>
@@ -6376,7 +6347,7 @@
         <v>28.653171153515402</v>
       </c>
     </row>
-    <row r="746" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A746">
         <v>42307.296929201199</v>
       </c>
@@ -6384,7 +6355,7 @@
         <v>17.6168908725659</v>
       </c>
     </row>
-    <row r="747" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A747">
         <v>42307.298041810398</v>
       </c>
@@ -6392,7 +6363,7 @@
         <v>32.165878952527301</v>
       </c>
     </row>
-    <row r="748" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A748">
         <v>42307.298421669002</v>
       </c>
@@ -6400,7 +6371,7 @@
         <v>15.814351013032599</v>
       </c>
     </row>
-    <row r="749" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A749">
         <v>42307.3109613505</v>
       </c>
@@ -6408,7 +6379,7 @@
         <v>13.982873879626499</v>
       </c>
     </row>
-    <row r="750" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A750">
         <v>42307.313646493298</v>
       </c>
@@ -6416,7 +6387,7 @@
         <v>13.229002069898501</v>
       </c>
     </row>
-    <row r="751" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A751">
         <v>42307.350038869699</v>
       </c>
@@ -6424,7 +6395,7 @@
         <v>25.8217065850483</v>
       </c>
     </row>
-    <row r="752" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A752">
         <v>42307.352248227697</v>
       </c>
@@ -6432,7 +6403,7 @@
         <v>20.1039471052752</v>
       </c>
     </row>
-    <row r="753" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A753">
         <v>42307.355320944996</v>
       </c>
@@ -6440,7 +6411,7 @@
         <v>19.8409044865877</v>
       </c>
     </row>
-    <row r="754" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A754">
         <v>42307.364110078597</v>
       </c>
@@ -6448,7 +6419,7 @@
         <v>15.154232749766599</v>
       </c>
     </row>
-    <row r="755" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A755">
         <v>42307.364268100799</v>
       </c>
@@ -6456,7 +6427,7 @@
         <v>15.319994456227599</v>
       </c>
     </row>
-    <row r="756" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A756">
         <v>42307.369643718201</v>
       </c>
@@ -6464,7 +6435,7 @@
         <v>12.4520350892204</v>
       </c>
     </row>
-    <row r="757" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A757">
         <v>42307.375576480699</v>
       </c>
@@ -6472,7 +6443,7 @@
         <v>21.674977774905599</v>
       </c>
     </row>
-    <row r="758" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A758">
         <v>42307.376640456299</v>
       </c>
@@ -6480,7 +6451,7 @@
         <v>16.542822078866799</v>
       </c>
     </row>
-    <row r="759" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A759">
         <v>42307.387972594202</v>
       </c>
@@ -6488,7 +6459,7 @@
         <v>15.016617978183801</v>
       </c>
     </row>
-    <row r="760" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A760">
         <v>42307.393237076903</v>
       </c>
@@ -6496,7 +6467,7 @@
         <v>21.003799031173301</v>
       </c>
     </row>
-    <row r="761" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A761">
         <v>42307.393570075998</v>
       </c>
@@ -6504,7 +6475,7 @@
         <v>27.280290079687099</v>
       </c>
     </row>
-    <row r="762" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A762">
         <v>42307.400552061903</v>
       </c>
@@ -6512,7 +6483,7 @@
         <v>15.816812871223799</v>
       </c>
     </row>
-    <row r="763" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A763">
         <v>42307.403783937603</v>
       </c>
@@ -6520,7 +6491,7 @@
         <v>14.185396333112701</v>
       </c>
     </row>
-    <row r="764" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A764">
         <v>42307.409201557603</v>
       </c>
@@ -6528,7 +6499,7 @@
         <v>20.210829096809199</v>
       </c>
     </row>
-    <row r="765" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A765">
         <v>42307.413519881702</v>
       </c>
@@ -6536,7 +6507,7 @@
         <v>18.266200606071902</v>
       </c>
     </row>
-    <row r="766" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A766">
         <v>42307.414567899097</v>
       </c>
@@ -6544,7 +6515,7 @@
         <v>7.5729454419111697</v>
       </c>
     </row>
-    <row r="767" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A767">
         <v>42307.423883057701</v>
       </c>
@@ -6552,7 +6523,7 @@
         <v>24.242162956196701</v>
       </c>
     </row>
-    <row r="768" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A768">
         <v>42307.426720089898</v>
       </c>
@@ -6560,7 +6531,7 @@
         <v>30.221902117534398</v>
       </c>
     </row>
-    <row r="769" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A769">
         <v>42307.427319531002</v>
       </c>
@@ -6568,7 +6539,7 @@
         <v>1.0673026883605501</v>
       </c>
     </row>
-    <row r="770" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A770">
         <v>42307.435212271303</v>
       </c>
@@ -6576,7 +6547,7 @@
         <v>24.1814801355013</v>
       </c>
     </row>
-    <row r="771" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A771">
         <v>42307.440007367397</v>
       </c>
@@ -6584,7 +6555,7 @@
         <v>12.3436183990946</v>
       </c>
     </row>
-    <row r="772" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A772">
         <v>42307.440620349902</v>
       </c>
@@ -6592,7 +6563,7 @@
         <v>21.241147157502098</v>
       </c>
     </row>
-    <row r="773" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A773">
         <v>42307.445107262</v>
       </c>
@@ -6600,7 +6571,7 @@
         <v>23.494209869302701</v>
       </c>
     </row>
-    <row r="774" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A774">
         <v>42307.464377085897</v>
       </c>
@@ -6608,7 +6579,7 @@
         <v>17.914191876867001</v>
       </c>
     </row>
-    <row r="775" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A775">
         <v>42307.464866356197</v>
       </c>
@@ -6616,7 +6587,7 @@
         <v>9.7129913631846492</v>
       </c>
     </row>
-    <row r="776" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A776">
         <v>42307.467919934898</v>
       </c>
@@ -6624,7 +6595,7 @@
         <v>36.8351515154298</v>
       </c>
     </row>
-    <row r="777" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A777">
         <v>42307.468857865199</v>
       </c>
@@ -6632,7 +6603,7 @@
         <v>5.6560425836423498</v>
       </c>
     </row>
-    <row r="778" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A778">
         <v>42307.476411683303</v>
       </c>
@@ -6640,7 +6611,7 @@
         <v>7.6249412019364504</v>
       </c>
     </row>
-    <row r="779" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A779">
         <v>42307.479666343803</v>
       </c>
@@ -6648,7 +6619,7 @@
         <v>22.0439258002367</v>
       </c>
     </row>
-    <row r="780" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A780">
         <v>42307.480588902603</v>
       </c>
@@ -6656,7 +6627,7 @@
         <v>34.0584786305999</v>
       </c>
     </row>
-    <row r="781" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A781">
         <v>42307.492982035903</v>
       </c>
@@ -6664,7 +6635,7 @@
         <v>21.4776000499707</v>
       </c>
     </row>
-    <row r="782" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A782">
         <v>42307.4985043739</v>
       </c>
@@ -6672,7 +6643,7 @@
         <v>37.726762195478599</v>
       </c>
     </row>
-    <row r="783" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A783">
         <v>42307.513068704196</v>
       </c>
@@ -6680,7 +6651,7 @@
         <v>25.376942044608299</v>
       </c>
     </row>
-    <row r="784" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A784">
         <v>42307.515825754403</v>
       </c>
@@ -6688,7 +6659,7 @@
         <v>31.8330412012564</v>
       </c>
     </row>
-    <row r="785" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A785">
         <v>42307.516270381799</v>
       </c>
@@ -6696,7 +6667,7 @@
         <v>8.4918105983193506</v>
       </c>
     </row>
-    <row r="786" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A786">
         <v>42307.518541509802</v>
       </c>
@@ -6704,7 +6675,7 @@
         <v>27.5840472917277</v>
       </c>
     </row>
-    <row r="787" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A787">
         <v>42307.532437024798</v>
       </c>
@@ -6712,7 +6683,7 @@
         <v>7.7590690737221699</v>
       </c>
     </row>
-    <row r="788" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A788">
         <v>42307.579771761899</v>
       </c>
@@ -6720,7 +6691,7 @@
         <v>30.206206695888</v>
       </c>
     </row>
-    <row r="789" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A789">
         <v>42307.5864249351</v>
       </c>
@@ -6728,7 +6699,7 @@
         <v>29.868823168263798</v>
       </c>
     </row>
-    <row r="790" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A790">
         <v>42307.592505475201</v>
       </c>
@@ -6736,7 +6707,7 @@
         <v>28.068978519115198</v>
       </c>
     </row>
-    <row r="791" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A791">
         <v>42307.604242244903</v>
       </c>
@@ -6744,7 +6715,7 @@
         <v>15.586651314452901</v>
       </c>
     </row>
-    <row r="792" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A792">
         <v>42307.613289913701</v>
       </c>
@@ -6752,7 +6723,7 @@
         <v>19.258296832887101</v>
       </c>
     </row>
-    <row r="793" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A793">
         <v>42307.618533143599</v>
       </c>
@@ -6760,7 +6731,7 @@
         <v>27.053774874457599</v>
       </c>
     </row>
-    <row r="794" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A794">
         <v>42307.623663953498</v>
       </c>
@@ -6768,7 +6739,7 @@
         <v>17.235404665120601</v>
       </c>
     </row>
-    <row r="795" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A795">
         <v>42307.631197659597</v>
       </c>
@@ -6776,7 +6747,7 @@
         <v>31.068870230044201</v>
       </c>
     </row>
-    <row r="796" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A796">
         <v>42307.669827692203</v>
       </c>
@@ -6784,7 +6755,7 @@
         <v>38.387732143959603</v>
       </c>
     </row>
-    <row r="797" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A797">
         <v>42307.675528504202</v>
       </c>
@@ -6792,7 +6763,7 @@
         <v>16.2873052360587</v>
       </c>
     </row>
-    <row r="798" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A798">
         <v>42307.680375740303</v>
       </c>
@@ -6800,7 +6771,7 @@
         <v>33.737379856257398</v>
       </c>
     </row>
-    <row r="799" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A799">
         <v>42307.6879851583</v>
       </c>
@@ -6808,7 +6779,7 @@
         <v>12.794018205018499</v>
       </c>
     </row>
-    <row r="800" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A800">
         <v>42307.711160883999</v>
       </c>
@@ -6816,7 +6787,7 @@
         <v>21.554266462154999</v>
       </c>
     </row>
-    <row r="801" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A801">
         <v>42307.711244227998</v>
       </c>
@@ -6824,7 +6795,7 @@
         <v>31.123453958655499</v>
       </c>
     </row>
-    <row r="802" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A802">
         <v>42307.711882617099</v>
       </c>
@@ -6832,7 +6803,7 @@
         <v>22.472866405823101</v>
       </c>
     </row>
-    <row r="803" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A803">
         <v>42307.738020866098</v>
       </c>
@@ -6840,7 +6811,7 @@
         <v>19.1091892888216</v>
       </c>
     </row>
-    <row r="804" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A804">
         <v>42307.752640530904</v>
       </c>
@@ -6848,7 +6819,7 @@
         <v>8.9655141076393008</v>
       </c>
     </row>
-    <row r="805" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A805">
         <v>42307.763508493001</v>
       </c>
@@ -6856,7 +6827,7 @@
         <v>14.538760229849499</v>
       </c>
     </row>
-    <row r="806" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A806">
         <v>42307.764272238099</v>
       </c>
@@ -6864,7 +6835,7 @@
         <v>6.6187844530663797</v>
       </c>
     </row>
-    <row r="807" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A807">
         <v>42307.776600700301</v>
       </c>
@@ -6872,7 +6843,7 @@
         <v>19.410505262153698</v>
       </c>
     </row>
-    <row r="808" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A808">
         <v>42307.780433907799</v>
       </c>
@@ -6880,7 +6851,7 @@
         <v>24.581237160323699</v>
       </c>
     </row>
-    <row r="809" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A809">
         <v>42307.804567256702</v>
       </c>
@@ -6888,7 +6859,7 @@
         <v>19.9134522735344</v>
       </c>
     </row>
-    <row r="810" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A810">
         <v>42307.807958225603</v>
       </c>
@@ -6896,7 +6867,7 @@
         <v>14.319364874226</v>
       </c>
     </row>
-    <row r="811" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A811">
         <v>42307.820661591701</v>
       </c>
@@ -6904,7 +6875,7 @@
         <v>21.950000462005899</v>
       </c>
     </row>
-    <row r="812" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A812">
         <v>42307.821770405797</v>
       </c>
@@ -6912,7 +6883,7 @@
         <v>29.379711112601399</v>
       </c>
     </row>
-    <row r="813" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A813">
         <v>42307.825221514897</v>
       </c>
@@ -6920,7 +6891,7 @@
         <v>9.7501243319178794</v>
       </c>
     </row>
-    <row r="814" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A814">
         <v>42307.8326100743</v>
       </c>
@@ -6928,7 +6899,7 @@
         <v>19.0041121446293</v>
       </c>
     </row>
-    <row r="815" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A815">
         <v>42307.845874352803</v>
       </c>
@@ -6936,7 +6907,7 @@
         <v>37.591036202031198</v>
       </c>
     </row>
-    <row r="816" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A816">
         <v>42307.863458035703</v>
       </c>
@@ -6944,7 +6915,7 @@
         <v>28.4643284322079</v>
       </c>
     </row>
-    <row r="817" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A817">
         <v>42307.867495696402</v>
       </c>
@@ -6952,7 +6923,7 @@
         <v>15.015707479945901</v>
       </c>
     </row>
-    <row r="818" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A818">
         <v>42307.869927393702</v>
       </c>
@@ -6960,7 +6931,7 @@
         <v>22.333341482251001</v>
       </c>
     </row>
-    <row r="819" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A819">
         <v>42307.881934987403</v>
       </c>
@@ -6968,7 +6939,7 @@
         <v>27.741250013004201</v>
       </c>
     </row>
-    <row r="820" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A820">
         <v>42307.882442567497</v>
       </c>
@@ -6976,7 +6947,7 @@
         <v>11.640426008699601</v>
       </c>
     </row>
-    <row r="821" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A821">
         <v>42307.886753883402</v>
       </c>
@@ -6984,7 +6955,7 @@
         <v>15.1357839286987</v>
       </c>
     </row>
-    <row r="822" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A822">
         <v>42307.890036399796</v>
       </c>
@@ -6992,7 +6963,7 @@
         <v>22.123493980847801</v>
       </c>
     </row>
-    <row r="823" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A823">
         <v>42307.893024017503</v>
       </c>
@@ -7000,7 +6971,7 @@
         <v>17.915620870342401</v>
       </c>
     </row>
-    <row r="824" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A824">
         <v>42307.909254092898</v>
       </c>
@@ -7008,7 +6979,7 @@
         <v>23.954026427162901</v>
       </c>
     </row>
-    <row r="825" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A825">
         <v>42307.930326230897</v>
       </c>
@@ -7016,7 +6987,7 @@
         <v>4.0217461259329799</v>
       </c>
     </row>
-    <row r="826" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A826">
         <v>42307.933462143097</v>
       </c>
@@ -7024,7 +6995,7 @@
         <v>9.6134149083589495</v>
       </c>
     </row>
-    <row r="827" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A827">
         <v>42307.956903016398</v>
       </c>
@@ -7032,7 +7003,7 @@
         <v>13.133138863517299</v>
       </c>
     </row>
-    <row r="828" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A828">
         <v>42307.963718216401</v>
       </c>
@@ -7040,7 +7011,7 @@
         <v>4.9526369948750997</v>
       </c>
     </row>
-    <row r="829" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A829">
         <v>42307.970009198201</v>
       </c>
@@ -7048,7 +7019,7 @@
         <v>26.474204738767501</v>
       </c>
     </row>
-    <row r="830" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A830">
         <v>42308.009020463003</v>
       </c>
@@ -7056,7 +7027,7 @@
         <v>4.4218786134662498</v>
       </c>
     </row>
-    <row r="831" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A831">
         <v>42308.0090491757</v>
       </c>
@@ -7064,7 +7035,7 @@
         <v>18.253691099381001</v>
       </c>
     </row>
-    <row r="832" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A832">
         <v>42308.032129436098</v>
       </c>
@@ -7072,7 +7043,7 @@
         <v>14.486118569653501</v>
       </c>
     </row>
-    <row r="833" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A833">
         <v>42308.035920855102</v>
       </c>
@@ -7080,7 +7051,7 @@
         <v>31.484787723145899</v>
       </c>
     </row>
-    <row r="834" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A834">
         <v>42308.053725498998</v>
       </c>
@@ -7088,7 +7059,7 @@
         <v>12.7723369680572</v>
       </c>
     </row>
-    <row r="835" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A835">
         <v>42308.065236292598</v>
       </c>
@@ -7096,7 +7067,7 @@
         <v>16.364104138197799</v>
       </c>
     </row>
-    <row r="836" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A836">
         <v>42308.073381439899</v>
       </c>
@@ -7104,7 +7075,7 @@
         <v>35.450026566745798</v>
       </c>
     </row>
-    <row r="837" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A837">
         <v>42308.075537260796</v>
       </c>
@@ -7112,7 +7083,7 @@
         <v>38.479671073505699</v>
       </c>
     </row>
-    <row r="838" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A838">
         <v>42308.075723176102</v>
       </c>
@@ -7120,7 +7091,7 @@
         <v>27.3251731892301</v>
       </c>
     </row>
-    <row r="839" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A839">
         <v>42308.079442417598</v>
       </c>
@@ -7128,7 +7099,7 @@
         <v>12.8402847197951</v>
       </c>
     </row>
-    <row r="840" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A840">
         <v>42308.084843874502</v>
       </c>
@@ -7136,7 +7107,7 @@
         <v>20.807145037039799</v>
       </c>
     </row>
-    <row r="841" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A841">
         <v>42308.1158128147</v>
       </c>
@@ -7144,7 +7115,7 @@
         <v>16.369698146090101</v>
       </c>
     </row>
-    <row r="842" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A842">
         <v>42308.118308447301</v>
       </c>
@@ -7152,7 +7123,7 @@
         <v>28.855673993347299</v>
       </c>
     </row>
-    <row r="843" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A843">
         <v>42308.140746723802</v>
       </c>
@@ -7160,7 +7131,7 @@
         <v>27.944653562873398</v>
       </c>
     </row>
-    <row r="844" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A844">
         <v>42308.153906060899</v>
       </c>
@@ -7168,7 +7139,7 @@
         <v>27.4464496471678</v>
       </c>
     </row>
-    <row r="845" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A845">
         <v>42308.184151610199</v>
       </c>
@@ -7176,7 +7147,7 @@
         <v>21.081973832085598</v>
       </c>
     </row>
-    <row r="846" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A846">
         <v>42308.188264126002</v>
       </c>
@@ -7184,7 +7155,7 @@
         <v>24.238055199493999</v>
       </c>
     </row>
-    <row r="847" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A847">
         <v>42308.211292400003</v>
       </c>
@@ -7192,7 +7163,7 @@
         <v>14.049404149036601</v>
       </c>
     </row>
-    <row r="848" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A848">
         <v>42308.249378530898</v>
       </c>
@@ -7200,7 +7171,7 @@
         <v>26.5591836709206</v>
       </c>
     </row>
-    <row r="849" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A849">
         <v>42308.250545859897</v>
       </c>
@@ -7208,7 +7179,7 @@
         <v>25.242968306714801</v>
       </c>
     </row>
-    <row r="850" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A850">
         <v>42308.2511527284</v>
       </c>
@@ -7216,7 +7187,7 @@
         <v>34.891026423190397</v>
       </c>
     </row>
-    <row r="851" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A851">
         <v>42308.264448993097</v>
       </c>
@@ -7224,7 +7195,7 @@
         <v>30.599199934365199</v>
       </c>
     </row>
-    <row r="852" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A852">
         <v>42308.266628106401</v>
       </c>
@@ -7232,7 +7203,7 @@
         <v>17.366745498112099</v>
       </c>
     </row>
-    <row r="853" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A853">
         <v>42308.279461126702</v>
       </c>
@@ -7240,7 +7211,7 @@
         <v>23.821348978585899</v>
       </c>
     </row>
-    <row r="854" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A854">
         <v>42308.289091365703</v>
       </c>
@@ -7248,7 +7219,7 @@
         <v>11.2519341504268</v>
       </c>
     </row>
-    <row r="855" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A855">
         <v>42308.300511997899</v>
       </c>
@@ -7256,7 +7227,7 @@
         <v>25.670210924915899</v>
       </c>
     </row>
-    <row r="856" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A856">
         <v>42308.307544028503</v>
       </c>
@@ -7264,7 +7235,7 @@
         <v>33.436930385483002</v>
       </c>
     </row>
-    <row r="857" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A857">
         <v>42308.326705548803</v>
       </c>
@@ -7272,7 +7243,7 @@
         <v>36.082648042135403</v>
       </c>
     </row>
-    <row r="858" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A858">
         <v>42308.354628565801</v>
       </c>
@@ -7280,7 +7251,7 @@
         <v>10.9271926567011</v>
       </c>
     </row>
-    <row r="859" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A859">
         <v>42308.358296416904</v>
       </c>
@@ -7288,7 +7259,7 @@
         <v>8.2772693333997793</v>
       </c>
     </row>
-    <row r="860" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A860">
         <v>42308.374343212599</v>
       </c>
@@ -7296,7 +7267,7 @@
         <v>15.415537976809199</v>
       </c>
     </row>
-    <row r="861" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A861">
         <v>42308.389625997799</v>
       </c>
@@ -7304,7 +7275,7 @@
         <v>32.181582765390402</v>
       </c>
     </row>
-    <row r="862" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A862">
         <v>42308.4096246095</v>
       </c>
@@ -7312,7 +7283,7 @@
         <v>2.7191538694911102</v>
       </c>
     </row>
-    <row r="863" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A863">
         <v>42308.410757405203</v>
       </c>
@@ -7320,7 +7291,7 @@
         <v>21.1709749510199</v>
       </c>
     </row>
-    <row r="864" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A864">
         <v>42308.417110231501</v>
       </c>
@@ -7328,7 +7299,7 @@
         <v>19.8350435988878</v>
       </c>
     </row>
-    <row r="865" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A865">
         <v>42308.442893786203</v>
       </c>
@@ -7336,7 +7307,7 @@
         <v>35.782244709083301</v>
       </c>
     </row>
-    <row r="866" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A866">
         <v>42308.4500338176</v>
       </c>
@@ -7344,7 +7315,7 @@
         <v>20.585977048523699</v>
       </c>
     </row>
-    <row r="867" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A867">
         <v>42308.460547648901</v>
       </c>
@@ -7352,7 +7323,7 @@
         <v>18.806352894073299</v>
       </c>
     </row>
-    <row r="868" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A868">
         <v>42308.467665989803</v>
       </c>
@@ -7360,7 +7331,7 @@
         <v>24.836634179164601</v>
       </c>
     </row>
-    <row r="869" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A869">
         <v>42308.473024396299</v>
       </c>
@@ -7368,7 +7339,7 @@
         <v>19.8062781074707</v>
       </c>
     </row>
-    <row r="870" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A870">
         <v>42308.490728434001</v>
       </c>
@@ -7376,7 +7347,7 @@
         <v>30.785157446162</v>
       </c>
     </row>
-    <row r="871" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A871">
         <v>42308.493558416099</v>
       </c>
@@ -7384,7 +7355,7 @@
         <v>8.2824939321782391</v>
       </c>
     </row>
-    <row r="872" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A872">
         <v>42308.521117700402</v>
       </c>
@@ -7392,7 +7363,7 @@
         <v>19.724971287242401</v>
       </c>
     </row>
-    <row r="873" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A873">
         <v>42308.540230447397</v>
       </c>
@@ -7400,7 +7371,7 @@
         <v>20.268650065565101</v>
       </c>
     </row>
-    <row r="874" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A874">
         <v>42308.542816092297</v>
       </c>
@@ -7408,7 +7379,7 @@
         <v>22.278925279951</v>
       </c>
     </row>
-    <row r="875" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A875">
         <v>42308.543919080999</v>
       </c>
@@ -7416,7 +7387,7 @@
         <v>12.3676462523872</v>
       </c>
     </row>
-    <row r="876" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A876">
         <v>42308.551974835304</v>
       </c>
@@ -7424,7 +7395,7 @@
         <v>24.372004275964699</v>
       </c>
     </row>
-    <row r="877" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A877">
         <v>42308.576313480298</v>
       </c>
@@ -7432,7 +7403,7 @@
         <v>20.621253127607801</v>
       </c>
     </row>
-    <row r="878" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A878">
         <v>42308.583069671702</v>
       </c>
@@ -7440,7 +7411,7 @@
         <v>14.7511916392722</v>
       </c>
     </row>
-    <row r="879" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A879">
         <v>42308.5834568551</v>
       </c>
@@ -7448,7 +7419,7 @@
         <v>10.408624319701</v>
       </c>
     </row>
-    <row r="880" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A880">
         <v>42308.597719800098</v>
       </c>
@@ -7456,7 +7427,7 @@
         <v>31.9451194607351</v>
       </c>
     </row>
-    <row r="881" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A881">
         <v>42308.626453221397</v>
       </c>
@@ -7464,7 +7435,7 @@
         <v>8.0379408612963594</v>
       </c>
     </row>
-    <row r="882" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A882">
         <v>42308.630339076502</v>
       </c>
@@ -7472,7 +7443,7 @@
         <v>26.541515344767301</v>
       </c>
     </row>
-    <row r="883" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A883">
         <v>42308.648349253999</v>
       </c>
@@ -7480,7 +7451,7 @@
         <v>13.908973039250199</v>
       </c>
     </row>
-    <row r="884" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A884">
         <v>42308.6615928385</v>
       </c>
@@ -7488,7 +7459,7 @@
         <v>14.7370022407943</v>
       </c>
     </row>
-    <row r="885" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A885">
         <v>42308.663525863703</v>
       </c>
@@ -7496,7 +7467,7 @@
         <v>28.771563975877601</v>
       </c>
     </row>
-    <row r="886" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A886">
         <v>42308.684744214697</v>
       </c>
@@ -7504,7 +7475,7 @@
         <v>24.5549830641474</v>
       </c>
     </row>
-    <row r="887" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A887">
         <v>42308.691523498303</v>
       </c>
@@ -7512,7 +7483,7 @@
         <v>15.011015877098</v>
       </c>
     </row>
-    <row r="888" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A888">
         <v>42308.704011058398</v>
       </c>
@@ -7520,7 +7491,7 @@
         <v>24.000615663850802</v>
       </c>
     </row>
-    <row r="889" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A889">
         <v>42308.728840715201</v>
       </c>
@@ -7528,7 +7499,7 @@
         <v>27.589842260413199</v>
       </c>
     </row>
-    <row r="890" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A890">
         <v>42308.729914329997</v>
       </c>
@@ -7536,7 +7507,7 @@
         <v>35.713118536218602</v>
       </c>
     </row>
-    <row r="891" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A891">
         <v>42308.734387914803</v>
       </c>
@@ -7544,7 +7515,7 @@
         <v>19.495046342294199</v>
       </c>
     </row>
-    <row r="892" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A892">
         <v>42308.7425196185</v>
       </c>
@@ -7552,7 +7523,7 @@
         <v>21.303043929282001</v>
       </c>
     </row>
-    <row r="893" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A893">
         <v>42308.745858340197</v>
       </c>
@@ -7560,7 +7531,7 @@
         <v>21.031095444989901</v>
       </c>
     </row>
-    <row r="894" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A894">
         <v>42308.776517215199</v>
       </c>
@@ -7568,7 +7539,7 @@
         <v>12.594886538835899</v>
       </c>
     </row>
-    <row r="895" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A895">
         <v>42308.777779371499</v>
       </c>
@@ -7576,7 +7547,7 @@
         <v>15.8076719118525</v>
       </c>
     </row>
-    <row r="896" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A896">
         <v>42308.785106663898</v>
       </c>
@@ -7584,7 +7555,7 @@
         <v>9.2592087979581006</v>
       </c>
     </row>
-    <row r="897" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A897">
         <v>42308.786675290597</v>
       </c>
@@ -7592,7 +7563,7 @@
         <v>16.782744352954101</v>
       </c>
     </row>
-    <row r="898" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A898">
         <v>42308.788746696497</v>
       </c>
@@ -7600,7 +7571,7 @@
         <v>14.8158816245151</v>
       </c>
     </row>
-    <row r="899" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A899">
         <v>42308.7891906859</v>
       </c>
@@ -7608,7 +7579,7 @@
         <v>11.6362502933858</v>
       </c>
     </row>
-    <row r="900" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A900">
         <v>42308.802614918997</v>
       </c>
@@ -7616,7 +7587,7 @@
         <v>24.2134348201295</v>
       </c>
     </row>
-    <row r="901" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A901">
         <v>42308.806873135502</v>
       </c>
@@ -7624,7 +7595,7 @@
         <v>14.4869158935677</v>
       </c>
     </row>
-    <row r="902" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A902">
         <v>42308.808503932698</v>
       </c>
@@ -7632,7 +7603,7 @@
         <v>32.728819391666697</v>
       </c>
     </row>
-    <row r="903" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A903">
         <v>42308.810115213899</v>
       </c>
@@ -7640,7 +7611,7 @@
         <v>15.302233714931599</v>
       </c>
     </row>
-    <row r="904" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A904">
         <v>42308.811514433</v>
       </c>
@@ -7648,7 +7619,7 @@
         <v>7.9592369760084596</v>
       </c>
     </row>
-    <row r="905" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A905">
         <v>42308.820830206299</v>
       </c>
@@ -7656,7 +7627,7 @@
         <v>31.369263001897998</v>
       </c>
     </row>
-    <row r="906" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A906">
         <v>42308.8415152866</v>
       </c>
@@ -7664,7 +7635,7 @@
         <v>7.3497451025658904</v>
       </c>
     </row>
-    <row r="907" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A907">
         <v>42308.849614906198</v>
       </c>
@@ -7672,7 +7643,7 @@
         <v>15.0107100773185</v>
       </c>
     </row>
-    <row r="908" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A908">
         <v>42308.853287679398</v>
       </c>
@@ -7680,7 +7651,7 @@
         <v>27.262566414344199</v>
       </c>
     </row>
-    <row r="909" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A909">
         <v>42308.854774917803</v>
       </c>
@@ -7688,7 +7659,7 @@
         <v>20.517551835622601</v>
       </c>
     </row>
-    <row r="910" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A910">
         <v>42308.864309938399</v>
       </c>
@@ -7696,7 +7667,7 @@
         <v>20.452720186897199</v>
       </c>
     </row>
-    <row r="911" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A911">
         <v>42308.880411095401</v>
       </c>
@@ -7704,7 +7675,7 @@
         <v>27.389650926049999</v>
       </c>
     </row>
-    <row r="912" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A912">
         <v>42308.919673053599</v>
       </c>
@@ -7712,7 +7683,7 @@
         <v>11.4004978486534</v>
       </c>
     </row>
-    <row r="913" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A913">
         <v>42308.929949905301</v>
       </c>
@@ -7720,7 +7691,7 @@
         <v>12.3966290865622</v>
       </c>
     </row>
-    <row r="914" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A914">
         <v>42308.931626146303</v>
       </c>
@@ -7728,7 +7699,7 @@
         <v>11.7743021439834</v>
       </c>
     </row>
-    <row r="915" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A915">
         <v>42308.958123499302</v>
       </c>
@@ -7736,7 +7707,7 @@
         <v>27.606284733179098</v>
       </c>
     </row>
-    <row r="916" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A916">
         <v>42308.971835878998</v>
       </c>
@@ -7744,7 +7715,7 @@
         <v>28.467732760942202</v>
       </c>
     </row>
-    <row r="917" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A917">
         <v>42308.975740113703</v>
       </c>
@@ -7752,7 +7723,7 @@
         <v>31.244254846014901</v>
       </c>
     </row>
-    <row r="918" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A918">
         <v>42308.990134305401</v>
       </c>
@@ -7760,7 +7731,7 @@
         <v>14.2371959472828</v>
       </c>
     </row>
-    <row r="919" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A919">
         <v>42308.990851367897</v>
       </c>
@@ -7768,7 +7739,7 @@
         <v>11.719532709643399</v>
       </c>
     </row>
-    <row r="920" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A920">
         <v>42308.999738271799</v>
       </c>
@@ -7776,7 +7747,7 @@
         <v>15.847017330581499</v>
       </c>
     </row>
-    <row r="921" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A921">
         <v>42309.004507002101</v>
       </c>
@@ -7784,7 +7755,7 @@
         <v>7.0768311254357199</v>
       </c>
     </row>
-    <row r="922" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A922">
         <v>42309.020307393097</v>
       </c>
@@ -7792,7 +7763,7 @@
         <v>23.650243259161101</v>
       </c>
     </row>
-    <row r="923" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A923">
         <v>42309.032377907002</v>
       </c>
@@ -7800,7 +7771,7 @@
         <v>30.891522386008599</v>
       </c>
     </row>
-    <row r="924" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A924">
         <v>42309.0337625928</v>
       </c>
@@ -7808,7 +7779,7 @@
         <v>23.0703429323524</v>
       </c>
     </row>
-    <row r="925" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A925">
         <v>42309.050805167899</v>
       </c>
@@ -7816,7 +7787,7 @@
         <v>16.9258152966827</v>
       </c>
     </row>
-    <row r="926" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A926">
         <v>42309.059383077598</v>
       </c>
@@ -7824,7 +7795,7 @@
         <v>26.975275749759</v>
       </c>
     </row>
-    <row r="927" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A927">
         <v>42309.063202408302</v>
       </c>
@@ -7832,7 +7803,7 @@
         <v>10.376044875925301</v>
       </c>
     </row>
-    <row r="928" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A928">
         <v>42309.069101163601</v>
       </c>
@@ -7840,7 +7811,7 @@
         <v>25.214664602301301</v>
       </c>
     </row>
-    <row r="929" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A929">
         <v>42309.085456832399</v>
       </c>
@@ -7848,7 +7819,7 @@
         <v>14.0227209273406</v>
       </c>
     </row>
-    <row r="930" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A930">
         <v>42309.110522407304</v>
       </c>
@@ -7856,7 +7827,7 @@
         <v>29.029274167254702</v>
       </c>
     </row>
-    <row r="931" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A931">
         <v>42309.1411012444</v>
       </c>
@@ -7864,7 +7835,7 @@
         <v>12.817852669170801</v>
       </c>
     </row>
-    <row r="932" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A932">
         <v>42309.1536571123</v>
       </c>
@@ -7872,7 +7843,7 @@
         <v>27.1370675073242</v>
       </c>
     </row>
-    <row r="933" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A933">
         <v>42309.163794409898</v>
       </c>
@@ -7880,7 +7851,7 @@
         <v>13.7155167040503</v>
       </c>
     </row>
-    <row r="934" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A934">
         <v>42309.169215690097</v>
       </c>
@@ -7888,7 +7859,7 @@
         <v>11.1330349027682</v>
       </c>
     </row>
-    <row r="935" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A935">
         <v>42309.206468259203</v>
       </c>
@@ -7896,7 +7867,7 @@
         <v>22.610984520024498</v>
       </c>
     </row>
-    <row r="936" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A936">
         <v>42309.250061943298</v>
       </c>
@@ -7904,7 +7875,7 @@
         <v>24.388115039556201</v>
       </c>
     </row>
-    <row r="937" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A937">
         <v>42309.259716205801</v>
       </c>
@@ -7912,7 +7883,7 @@
         <v>21.6840165588732</v>
       </c>
     </row>
-    <row r="938" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A938">
         <v>42309.261632723399</v>
       </c>
@@ -7920,7 +7891,7 @@
         <v>4.2943918076452396</v>
       </c>
     </row>
-    <row r="939" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A939">
         <v>42309.300008947299</v>
       </c>
@@ -7928,7 +7899,7 @@
         <v>29.9187298412863</v>
       </c>
     </row>
-    <row r="940" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A940">
         <v>42309.323736211503</v>
       </c>
@@ -7936,7 +7907,7 @@
         <v>19.281997708123999</v>
       </c>
     </row>
-    <row r="941" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A941">
         <v>42309.325359199502</v>
       </c>
@@ -7944,7 +7915,7 @@
         <v>19.495424123998301</v>
       </c>
     </row>
-    <row r="942" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A942">
         <v>42309.337489243502</v>
       </c>
@@ -7952,7 +7923,7 @@
         <v>1.33599149694633</v>
       </c>
     </row>
-    <row r="943" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A943">
         <v>42309.339409756401</v>
       </c>
@@ -7960,7 +7931,7 @@
         <v>10.920037072246499</v>
       </c>
     </row>
-    <row r="944" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A944">
         <v>42309.3410922978</v>
       </c>
@@ -7968,7 +7939,7 @@
         <v>19.6645009384875</v>
       </c>
     </row>
-    <row r="945" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A945">
         <v>42309.372521078498</v>
       </c>
@@ -7976,7 +7947,7 @@
         <v>28.5503031531236</v>
       </c>
     </row>
-    <row r="946" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A946">
         <v>42309.428332588403</v>
       </c>
@@ -7984,7 +7955,7 @@
         <v>18.3995401412067</v>
       </c>
     </row>
-    <row r="947" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A947">
         <v>42309.450367685997</v>
       </c>
@@ -7992,7 +7963,7 @@
         <v>12.924725170527401</v>
       </c>
     </row>
-    <row r="948" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A948">
         <v>42309.462268564101</v>
       </c>
@@ -8000,7 +7971,7 @@
         <v>17.521240277823701</v>
       </c>
     </row>
-    <row r="949" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A949">
         <v>42309.463118721898</v>
       </c>
@@ -8008,7 +7979,7 @@
         <v>26.317389652588499</v>
       </c>
     </row>
-    <row r="950" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A950">
         <v>42309.475906633503</v>
       </c>
@@ -8016,7 +7987,7 @@
         <v>26.056817320561699</v>
       </c>
     </row>
-    <row r="951" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A951">
         <v>42309.480008923398</v>
       </c>
@@ -8024,7 +7995,7 @@
         <v>29.6160207024597</v>
       </c>
     </row>
-    <row r="952" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A952">
         <v>42309.531161030798</v>
       </c>
@@ -8032,7 +8003,7 @@
         <v>17.746786227671802</v>
       </c>
     </row>
-    <row r="953" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A953">
         <v>42309.5329582087</v>
       </c>
@@ -8040,7 +8011,7 @@
         <v>7.5468540477951001</v>
       </c>
     </row>
-    <row r="954" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A954">
         <v>42309.5335465112</v>
       </c>
@@ -8048,7 +8019,7 @@
         <v>26.363688949920999</v>
       </c>
     </row>
-    <row r="955" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A955">
         <v>42309.538685446998</v>
       </c>
@@ -8056,7 +8027,7 @@
         <v>14.7376445460598</v>
       </c>
     </row>
-    <row r="956" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A956">
         <v>42309.542157077703</v>
       </c>
@@ -8064,7 +8035,7 @@
         <v>29.287755223670601</v>
       </c>
     </row>
-    <row r="957" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A957">
         <v>42309.5430869708</v>
       </c>
@@ -8072,7 +8043,7 @@
         <v>31.996310958492799</v>
       </c>
     </row>
-    <row r="958" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A958">
         <v>42309.5445011888</v>
       </c>
@@ -8080,7 +8051,7 @@
         <v>26.981273346304999</v>
       </c>
     </row>
-    <row r="959" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A959">
         <v>42309.5452352992</v>
       </c>
@@ -8088,7 +8059,7 @@
         <v>16.575895486842398</v>
       </c>
     </row>
-    <row r="960" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A960">
         <v>42309.559945456</v>
       </c>
@@ -8096,7 +8067,7 @@
         <v>16.491862256922001</v>
       </c>
     </row>
-    <row r="961" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A961">
         <v>42309.573657314198</v>
       </c>
@@ -8104,7 +8075,7 @@
         <v>15.7054205029089</v>
       </c>
     </row>
-    <row r="962" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A962">
         <v>42309.595034167003</v>
       </c>
@@ -8112,7 +8083,7 @@
         <v>17.7049462054486</v>
       </c>
     </row>
-    <row r="963" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A963">
         <v>42309.596054039699</v>
       </c>
@@ -8120,7 +8091,7 @@
         <v>26.155265692247799</v>
       </c>
     </row>
-    <row r="964" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A964">
         <v>42309.598688099497</v>
       </c>
@@ -8128,7 +8099,7 @@
         <v>29.6942786704813</v>
       </c>
     </row>
-    <row r="965" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A965">
         <v>42309.603194001298</v>
       </c>
@@ -8136,7 +8107,7 @@
         <v>24.455547108650901</v>
       </c>
     </row>
-    <row r="966" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A966">
         <v>42309.615177357198</v>
       </c>
@@ -8144,7 +8115,7 @@
         <v>22.425872583966299</v>
       </c>
     </row>
-    <row r="967" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A967">
         <v>42309.625309895797</v>
       </c>
@@ -8152,7 +8123,7 @@
         <v>33.004309537525401</v>
       </c>
     </row>
-    <row r="968" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A968">
         <v>42309.626806871202</v>
       </c>
@@ -8160,7 +8131,7 @@
         <v>4.3852753065286203</v>
       </c>
     </row>
-    <row r="969" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A969">
         <v>42309.634144775999</v>
       </c>
@@ -8168,7 +8139,7 @@
         <v>16.915400911965001</v>
       </c>
     </row>
-    <row r="970" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A970">
         <v>42309.641793700699</v>
       </c>
@@ -8176,7 +8147,7 @@
         <v>17.247718771014402</v>
       </c>
     </row>
-    <row r="971" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A971">
         <v>42309.661838599102</v>
       </c>
@@ -8184,7 +8155,7 @@
         <v>25.548663275147</v>
       </c>
     </row>
-    <row r="972" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A972">
         <v>42309.669989953698</v>
       </c>
@@ -8192,7 +8163,7 @@
         <v>19.692654020095102</v>
       </c>
     </row>
-    <row r="973" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A973">
         <v>42309.685556997203</v>
       </c>
@@ -8200,7 +8171,7 @@
         <v>22.548459077542201</v>
       </c>
     </row>
-    <row r="974" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A974">
         <v>42309.688666050097</v>
       </c>
@@ -8208,7 +8179,7 @@
         <v>18.674775207115299</v>
       </c>
     </row>
-    <row r="975" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A975">
         <v>42309.692884256998</v>
       </c>
@@ -8216,7 +8187,7 @@
         <v>16.977700369015601</v>
       </c>
     </row>
-    <row r="976" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A976">
         <v>42309.697745248799</v>
       </c>
@@ -8224,7 +8195,7 @@
         <v>18.870443787420001</v>
       </c>
     </row>
-    <row r="977" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A977">
         <v>42309.707853931497</v>
       </c>
@@ -8232,7 +8203,7 @@
         <v>24.984427152050799</v>
       </c>
     </row>
-    <row r="978" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A978">
         <v>42309.711396035498</v>
       </c>
@@ -8240,7 +8211,7 @@
         <v>26.1918392993074</v>
       </c>
     </row>
-    <row r="979" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A979">
         <v>42309.762222655001</v>
       </c>
@@ -8248,7 +8219,7 @@
         <v>10.336158414638399</v>
       </c>
     </row>
-    <row r="980" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A980">
         <v>42309.766228976703</v>
       </c>
@@ -8256,7 +8227,7 @@
         <v>28.2403424756737</v>
       </c>
     </row>
-    <row r="981" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A981">
         <v>42309.777192003603</v>
       </c>
@@ -8264,7 +8235,7 @@
         <v>21.6307082300122</v>
       </c>
     </row>
-    <row r="982" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A982">
         <v>42309.803357647397</v>
       </c>
@@ -8272,7 +8243,7 @@
         <v>13.690377978460001</v>
       </c>
     </row>
-    <row r="983" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A983">
         <v>42309.808579745601</v>
       </c>
@@ -8280,7 +8251,7 @@
         <v>21.142270936208298</v>
       </c>
     </row>
-    <row r="984" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A984">
         <v>42309.817234629103</v>
       </c>
@@ -8288,7 +8259,7 @@
         <v>20.366755822288901</v>
       </c>
     </row>
-    <row r="985" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A985">
         <v>42309.8244759464</v>
       </c>
@@ -8296,7 +8267,7 @@
         <v>20.311728681669099</v>
       </c>
     </row>
-    <row r="986" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A986">
         <v>42309.8342851903</v>
       </c>
@@ -8304,7 +8275,7 @@
         <v>19.103980466648199</v>
       </c>
     </row>
-    <row r="987" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A987">
         <v>42309.836131826101</v>
       </c>
@@ -8312,7 +8283,7 @@
         <v>5.5371968032148304</v>
       </c>
     </row>
-    <row r="988" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A988">
         <v>42309.840001215402</v>
       </c>
@@ -8320,7 +8291,7 @@
         <v>15.8654470502227</v>
       </c>
     </row>
-    <row r="989" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A989">
         <v>42309.842376805202</v>
       </c>
@@ -8328,7 +8299,7 @@
         <v>10.568376601819001</v>
       </c>
     </row>
-    <row r="990" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A990">
         <v>42309.866905733303</v>
       </c>
@@ -8336,7 +8307,7 @@
         <v>21.558667659986199</v>
       </c>
     </row>
-    <row r="991" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A991">
         <v>42309.867041329198</v>
       </c>
@@ -8344,7 +8315,7 @@
         <v>18.989392087840599</v>
       </c>
     </row>
-    <row r="992" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A992">
         <v>42309.879385186199</v>
       </c>
@@ -8352,7 +8323,7 @@
         <v>10.241452376602</v>
       </c>
     </row>
-    <row r="993" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A993">
         <v>42309.908677112398</v>
       </c>
@@ -8360,7 +8331,7 @@
         <v>28.110783383909901</v>
       </c>
     </row>
-    <row r="994" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A994">
         <v>42309.919544073397</v>
       </c>
@@ -8368,7 +8339,7 @@
         <v>13.848838711693601</v>
       </c>
     </row>
-    <row r="995" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A995">
         <v>42309.920498064399</v>
       </c>
@@ -8376,7 +8347,7 @@
         <v>21.507690180164602</v>
       </c>
     </row>
-    <row r="996" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A996">
         <v>42309.923089730299</v>
       </c>
@@ -8384,7 +8355,7 @@
         <v>15.281429644171901</v>
       </c>
     </row>
-    <row r="997" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A997">
         <v>42309.923128454699</v>
       </c>
@@ -8392,7 +8363,7 @@
         <v>26.3366839562627</v>
       </c>
     </row>
-    <row r="998" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A998">
         <v>42309.934390100803</v>
       </c>
@@ -8400,7 +8371,7 @@
         <v>29.064265969424799</v>
       </c>
     </row>
-    <row r="999" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A999">
         <v>42309.9641231852</v>
       </c>
@@ -8408,7 +8379,7 @@
         <v>22.844103948096201</v>
       </c>
     </row>
-    <row r="1000" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A1000">
         <v>42309.982067280704</v>
       </c>
@@ -8416,7 +8387,7 @@
         <v>16.218704860000798</v>
       </c>
     </row>
-    <row r="1001" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A1001">
         <v>42309.983137901203</v>
       </c>

--- a/DATA624/project_1/Waterflow_Pipe1.xlsx
+++ b/DATA624/project_1/Waterflow_Pipe1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/olivia/Documents/CUNY/CUNY_GITHUB_submissions/DATA624/project_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E2B6CA-F870-274B-B04E-0C6B266F318B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B835723-2D5F-B248-B95C-EA48FAE5E5F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="7640" windowWidth="20500" windowHeight="7680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3000" yWindow="6280" windowWidth="20500" windowHeight="7680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Waterflow_Pipe1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm\ AM/PM"/>
-    <numFmt numFmtId="166" formatCode="m/d/yy\ h:mm;@"/>
+    <numFmt numFmtId="165" formatCode="m/d/yy\ h:mm;@"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -63,7 +63,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -73,8 +73,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -383,7 +386,7 @@
   <dimension ref="A1:B1001"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="17.1640625" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" style="4" customWidth="1"/>
     <col min="2" max="2" width="17.1640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -396,7 +399,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A2">
+      <c r="A2" s="4">
         <v>42300.016741832398</v>
       </c>
       <c r="B2" s="1">
@@ -404,7 +407,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A3">
+      <c r="A3" s="4">
         <v>42300.027811016102</v>
       </c>
       <c r="B3" s="1">
@@ -412,7 +415,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A4">
+      <c r="A4" s="4">
         <v>42300.037400938199</v>
       </c>
       <c r="B4" s="1">
@@ -420,7 +423,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A5">
+      <c r="A5" s="4">
         <v>42300.038663751096</v>
       </c>
       <c r="B5" s="1">
@@ -428,7 +431,7 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A6">
+      <c r="A6" s="4">
         <v>42300.055060123399</v>
       </c>
       <c r="B6" s="1">
@@ -436,7 +439,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A7">
+      <c r="A7" s="4">
         <v>42300.058316777002</v>
       </c>
       <c r="B7" s="1">
@@ -444,7 +447,7 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A8">
+      <c r="A8" s="4">
         <v>42300.076449199798</v>
       </c>
       <c r="B8" s="1">
@@ -452,7 +455,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A9">
+      <c r="A9" s="4">
         <v>42300.080252982101</v>
       </c>
       <c r="B9" s="1">
@@ -460,7 +463,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A10">
+      <c r="A10" s="4">
         <v>42300.082823860903</v>
       </c>
       <c r="B10" s="1">
@@ -468,7 +471,7 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A11">
+      <c r="A11" s="4">
         <v>42300.119344038001</v>
       </c>
       <c r="B11" s="1">
@@ -476,7 +479,7 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A12">
+      <c r="A12" s="4">
         <v>42300.124883340002</v>
       </c>
       <c r="B12" s="1">
@@ -484,7 +487,7 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A13">
+      <c r="A13" s="4">
         <v>42300.135191670401</v>
       </c>
       <c r="B13" s="1">
@@ -492,7 +495,7 @@
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A14">
+      <c r="A14" s="4">
         <v>42300.137605514203</v>
       </c>
       <c r="B14" s="1">
@@ -500,7 +503,7 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A15">
+      <c r="A15" s="4">
         <v>42300.140436003901</v>
       </c>
       <c r="B15" s="1">
@@ -508,7 +511,7 @@
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A16">
+      <c r="A16" s="4">
         <v>42300.157610812901</v>
       </c>
       <c r="B16" s="1">
@@ -516,7 +519,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A17">
+      <c r="A17" s="4">
         <v>42300.166215283898</v>
       </c>
       <c r="B17" s="1">
@@ -524,7 +527,7 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A18">
+      <c r="A18" s="4">
         <v>42300.174891215203</v>
       </c>
       <c r="B18" s="1">
@@ -532,7 +535,7 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A19">
+      <c r="A19" s="4">
         <v>42300.198424494301</v>
       </c>
       <c r="B19" s="1">
@@ -540,7 +543,7 @@
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A20">
+      <c r="A20" s="4">
         <v>42300.212290127798</v>
       </c>
       <c r="B20" s="1">
@@ -548,7 +551,7 @@
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A21">
+      <c r="A21" s="4">
         <v>42300.217931498097</v>
       </c>
       <c r="B21" s="1">
@@ -556,7 +559,7 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A22">
+      <c r="A22" s="4">
         <v>42300.218503488497</v>
       </c>
       <c r="B22" s="1">
@@ -564,7 +567,7 @@
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A23">
+      <c r="A23" s="4">
         <v>42300.219228322901</v>
       </c>
       <c r="B23" s="1">
@@ -572,7 +575,7 @@
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A24">
+      <c r="A24" s="4">
         <v>42300.220111249298</v>
       </c>
       <c r="B24" s="1">
@@ -580,7 +583,7 @@
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A25">
+      <c r="A25" s="4">
         <v>42300.230968645599</v>
       </c>
       <c r="B25" s="1">
@@ -588,7 +591,7 @@
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A26">
+      <c r="A26" s="4">
         <v>42300.2381040576</v>
       </c>
       <c r="B26" s="1">
@@ -596,7 +599,7 @@
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A27">
+      <c r="A27" s="4">
         <v>42300.239242040698</v>
       </c>
       <c r="B27" s="1">
@@ -604,7 +607,7 @@
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A28">
+      <c r="A28" s="4">
         <v>42300.240185819799</v>
       </c>
       <c r="B28" s="1">
@@ -612,7 +615,7 @@
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A29">
+      <c r="A29" s="4">
         <v>42300.252528563797</v>
       </c>
       <c r="B29" s="1">
@@ -620,7 +623,7 @@
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A30">
+      <c r="A30" s="4">
         <v>42300.261991667699</v>
       </c>
       <c r="B30" s="1">
@@ -628,7 +631,7 @@
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A31">
+      <c r="A31" s="4">
         <v>42300.273136446798</v>
       </c>
       <c r="B31" s="1">
@@ -636,7 +639,7 @@
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A32">
+      <c r="A32" s="4">
         <v>42300.273366511399</v>
       </c>
       <c r="B32" s="1">
@@ -644,7 +647,7 @@
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A33">
+      <c r="A33" s="4">
         <v>42300.276743519797</v>
       </c>
       <c r="B33" s="1">
@@ -652,7 +655,7 @@
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A34">
+      <c r="A34" s="4">
         <v>42300.279438362297</v>
       </c>
       <c r="B34" s="1">
@@ -660,7 +663,7 @@
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A35">
+      <c r="A35" s="4">
         <v>42300.289154064201</v>
       </c>
       <c r="B35" s="1">
@@ -668,7 +671,7 @@
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A36">
+      <c r="A36" s="4">
         <v>42300.291314187802</v>
       </c>
       <c r="B36" s="1">
@@ -676,7 +679,7 @@
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A37">
+      <c r="A37" s="4">
         <v>42300.317064540897</v>
       </c>
       <c r="B37" s="1">
@@ -684,7 +687,7 @@
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A38">
+      <c r="A38" s="4">
         <v>42300.330362435503</v>
       </c>
       <c r="B38" s="1">
@@ -692,7 +695,7 @@
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A39">
+      <c r="A39" s="4">
         <v>42300.331045444203</v>
       </c>
       <c r="B39" s="1">
@@ -700,7 +703,7 @@
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A40">
+      <c r="A40" s="4">
         <v>42300.341235273103</v>
       </c>
       <c r="B40" s="1">
@@ -708,7 +711,7 @@
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A41">
+      <c r="A41" s="4">
         <v>42300.351909953097</v>
       </c>
       <c r="B41" s="1">
@@ -716,7 +719,7 @@
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A42">
+      <c r="A42" s="4">
         <v>42300.373947374399</v>
       </c>
       <c r="B42" s="1">
@@ -724,7 +727,7 @@
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A43">
+      <c r="A43" s="4">
         <v>42300.3756878813</v>
       </c>
       <c r="B43" s="1">
@@ -732,7 +735,7 @@
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A44">
+      <c r="A44" s="4">
         <v>42300.382994721898</v>
       </c>
       <c r="B44" s="1">
@@ -740,7 +743,7 @@
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A45">
+      <c r="A45" s="4">
         <v>42300.399831637696</v>
       </c>
       <c r="B45" s="1">
@@ -748,7 +751,7 @@
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A46">
+      <c r="A46" s="4">
         <v>42300.4173896348</v>
       </c>
       <c r="B46" s="1">
@@ -756,7 +759,7 @@
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A47">
+      <c r="A47" s="4">
         <v>42300.420727359997</v>
       </c>
       <c r="B47" s="1">
@@ -764,7 +767,7 @@
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A48">
+      <c r="A48" s="4">
         <v>42300.441386214203</v>
       </c>
       <c r="B48" s="1">
@@ -772,7 +775,7 @@
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A49">
+      <c r="A49" s="4">
         <v>42300.460086911502</v>
       </c>
       <c r="B49" s="1">
@@ -780,7 +783,7 @@
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A50">
+      <c r="A50" s="4">
         <v>42300.460989619198</v>
       </c>
       <c r="B50" s="1">
@@ -788,7 +791,7 @@
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A51">
+      <c r="A51" s="4">
         <v>42300.485019633197</v>
       </c>
       <c r="B51" s="1">
@@ -796,7 +799,7 @@
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A52">
+      <c r="A52" s="4">
         <v>42300.503859521297</v>
       </c>
       <c r="B52" s="1">
@@ -804,7 +807,7 @@
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A53">
+      <c r="A53" s="4">
         <v>42300.524889279397</v>
       </c>
       <c r="B53" s="1">
@@ -812,7 +815,7 @@
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A54">
+      <c r="A54" s="4">
         <v>42300.535590558102</v>
       </c>
       <c r="B54" s="1">
@@ -820,7 +823,7 @@
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A55">
+      <c r="A55" s="4">
         <v>42300.564858339698</v>
       </c>
       <c r="B55" s="1">
@@ -828,7 +831,7 @@
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A56">
+      <c r="A56" s="4">
         <v>42300.568459633898</v>
       </c>
       <c r="B56" s="1">
@@ -836,7 +839,7 @@
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A57">
+      <c r="A57" s="4">
         <v>42300.571550563203</v>
       </c>
       <c r="B57" s="1">
@@ -844,7 +847,7 @@
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A58">
+      <c r="A58" s="4">
         <v>42300.585393872898</v>
       </c>
       <c r="B58" s="1">
@@ -852,7 +855,7 @@
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A59">
+      <c r="A59" s="4">
         <v>42300.589691940797</v>
       </c>
       <c r="B59" s="1">
@@ -860,7 +863,7 @@
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A60">
+      <c r="A60" s="4">
         <v>42300.5908283639</v>
       </c>
       <c r="B60" s="1">
@@ -868,7 +871,7 @@
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A61">
+      <c r="A61" s="4">
         <v>42300.601062989401</v>
       </c>
       <c r="B61" s="1">
@@ -876,7 +879,7 @@
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A62">
+      <c r="A62" s="4">
         <v>42300.6084001165</v>
       </c>
       <c r="B62" s="1">
@@ -884,7 +887,7 @@
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A63">
+      <c r="A63" s="4">
         <v>42300.616552448999</v>
       </c>
       <c r="B63" s="1">
@@ -892,7 +895,7 @@
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A64">
+      <c r="A64" s="4">
         <v>42300.635023095601</v>
       </c>
       <c r="B64" s="1">
@@ -900,7 +903,7 @@
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A65">
+      <c r="A65" s="4">
         <v>42300.650633617901</v>
       </c>
       <c r="B65" s="1">
@@ -908,7 +911,7 @@
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A66">
+      <c r="A66" s="4">
         <v>42300.652286058998</v>
       </c>
       <c r="B66" s="1">
@@ -916,7 +919,7 @@
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A67">
+      <c r="A67" s="4">
         <v>42300.6610955746</v>
       </c>
       <c r="B67" s="1">
@@ -924,7 +927,7 @@
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A68">
+      <c r="A68" s="4">
         <v>42300.669255827997</v>
       </c>
       <c r="B68" s="1">
@@ -932,7 +935,7 @@
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A69">
+      <c r="A69" s="4">
         <v>42300.676789506098</v>
       </c>
       <c r="B69" s="1">
@@ -940,7 +943,7 @@
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A70">
+      <c r="A70" s="4">
         <v>42300.693015837503</v>
       </c>
       <c r="B70" s="1">
@@ -948,7 +951,7 @@
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A71">
+      <c r="A71" s="4">
         <v>42300.693807284799</v>
       </c>
       <c r="B71" s="1">
@@ -956,7 +959,7 @@
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A72">
+      <c r="A72" s="4">
         <v>42300.696284407401</v>
       </c>
       <c r="B72" s="1">
@@ -964,7 +967,7 @@
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A73">
+      <c r="A73" s="4">
         <v>42300.699395485899</v>
       </c>
       <c r="B73" s="1">
@@ -972,7 +975,7 @@
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A74">
+      <c r="A74" s="4">
         <v>42300.7206270803</v>
       </c>
       <c r="B74" s="1">
@@ -980,7 +983,7 @@
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A75">
+      <c r="A75" s="4">
         <v>42300.728828717001</v>
       </c>
       <c r="B75" s="1">
@@ -988,7 +991,7 @@
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A76">
+      <c r="A76" s="4">
         <v>42300.729794680199</v>
       </c>
       <c r="B76" s="1">
@@ -996,7 +999,7 @@
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A77">
+      <c r="A77" s="4">
         <v>42300.756216209498</v>
       </c>
       <c r="B77" s="1">
@@ -1004,7 +1007,7 @@
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A78">
+      <c r="A78" s="4">
         <v>42300.761181835398</v>
       </c>
       <c r="B78" s="1">
@@ -1012,7 +1015,7 @@
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A79">
+      <c r="A79" s="4">
         <v>42300.763305954097</v>
       </c>
       <c r="B79" s="1">
@@ -1020,7 +1023,7 @@
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A80">
+      <c r="A80" s="4">
         <v>42300.789805584202</v>
       </c>
       <c r="B80" s="1">
@@ -1028,7 +1031,7 @@
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A81">
+      <c r="A81" s="4">
         <v>42300.813982952001</v>
       </c>
       <c r="B81" s="1">
@@ -1036,7 +1039,7 @@
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A82">
+      <c r="A82" s="4">
         <v>42300.8323171831</v>
       </c>
       <c r="B82" s="1">
@@ -1044,7 +1047,7 @@
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A83">
+      <c r="A83" s="4">
         <v>42300.832379069499</v>
       </c>
       <c r="B83" s="1">
@@ -1052,7 +1055,7 @@
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A84">
+      <c r="A84" s="4">
         <v>42300.843509455102</v>
       </c>
       <c r="B84" s="1">
@@ -1060,7 +1063,7 @@
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A85">
+      <c r="A85" s="4">
         <v>42300.849725521301</v>
       </c>
       <c r="B85" s="1">
@@ -1068,7 +1071,7 @@
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A86">
+      <c r="A86" s="4">
         <v>42300.852826038601</v>
       </c>
       <c r="B86" s="1">
@@ -1076,7 +1079,7 @@
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A87">
+      <c r="A87" s="4">
         <v>42300.853194237003</v>
       </c>
       <c r="B87" s="1">
@@ -1084,7 +1087,7 @@
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A88">
+      <c r="A88" s="4">
         <v>42300.8584972764</v>
       </c>
       <c r="B88" s="1">
@@ -1092,7 +1095,7 @@
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A89">
+      <c r="A89" s="4">
         <v>42300.862690998903</v>
       </c>
       <c r="B89" s="1">
@@ -1100,7 +1103,7 @@
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A90">
+      <c r="A90" s="4">
         <v>42300.865298338998</v>
       </c>
       <c r="B90" s="1">
@@ -1108,7 +1111,7 @@
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A91">
+      <c r="A91" s="4">
         <v>42300.869391292297</v>
       </c>
       <c r="B91" s="1">
@@ -1116,7 +1119,7 @@
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A92">
+      <c r="A92" s="4">
         <v>42300.910530480302</v>
       </c>
       <c r="B92" s="1">
@@ -1124,7 +1127,7 @@
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A93">
+      <c r="A93" s="4">
         <v>42300.926182041301</v>
       </c>
       <c r="B93" s="1">
@@ -1132,7 +1135,7 @@
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A94">
+      <c r="A94" s="4">
         <v>42300.929378536101</v>
       </c>
       <c r="B94" s="1">
@@ -1140,7 +1143,7 @@
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A95">
+      <c r="A95" s="4">
         <v>42300.960476641398</v>
       </c>
       <c r="B95" s="1">
@@ -1148,7 +1151,7 @@
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A96">
+      <c r="A96" s="4">
         <v>42300.966301198197</v>
       </c>
       <c r="B96" s="1">
@@ -1156,7 +1159,7 @@
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A97">
+      <c r="A97" s="4">
         <v>42300.979175741399</v>
       </c>
       <c r="B97" s="1">
@@ -1164,7 +1167,7 @@
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A98">
+      <c r="A98" s="4">
         <v>42301.001178359198</v>
       </c>
       <c r="B98" s="1">
@@ -1172,7 +1175,7 @@
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A99">
+      <c r="A99" s="4">
         <v>42301.008161001701</v>
       </c>
       <c r="B99" s="1">
@@ -1180,7 +1183,7 @@
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A100">
+      <c r="A100" s="4">
         <v>42301.013578025697</v>
       </c>
       <c r="B100" s="1">
@@ -1188,7 +1191,7 @@
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A101">
+      <c r="A101" s="4">
         <v>42301.027619460299</v>
       </c>
       <c r="B101" s="1">
@@ -1196,7 +1199,7 @@
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A102">
+      <c r="A102" s="4">
         <v>42301.0349295325</v>
       </c>
       <c r="B102" s="1">
@@ -1204,7 +1207,7 @@
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A103">
+      <c r="A103" s="4">
         <v>42301.042470670604</v>
       </c>
       <c r="B103" s="1">
@@ -1212,7 +1215,7 @@
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A104">
+      <c r="A104" s="4">
         <v>42301.044858581801</v>
       </c>
       <c r="B104" s="1">
@@ -1220,7 +1223,7 @@
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A105">
+      <c r="A105" s="4">
         <v>42301.047849747803</v>
       </c>
       <c r="B105" s="1">
@@ -1228,7 +1231,7 @@
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A106">
+      <c r="A106" s="4">
         <v>42301.051026810601</v>
       </c>
       <c r="B106" s="1">
@@ -1236,7 +1239,7 @@
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A107">
+      <c r="A107" s="4">
         <v>42301.0525073155</v>
       </c>
       <c r="B107" s="1">
@@ -1244,7 +1247,7 @@
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A108">
+      <c r="A108" s="4">
         <v>42301.058040424199</v>
       </c>
       <c r="B108" s="1">
@@ -1252,7 +1255,7 @@
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A109">
+      <c r="A109" s="4">
         <v>42301.066442597999</v>
       </c>
       <c r="B109" s="1">
@@ -1260,7 +1263,7 @@
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A110">
+      <c r="A110" s="4">
         <v>42301.068056472897</v>
       </c>
       <c r="B110" s="1">
@@ -1268,7 +1271,7 @@
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A111">
+      <c r="A111" s="4">
         <v>42301.093623104003</v>
       </c>
       <c r="B111" s="1">
@@ -1276,7 +1279,7 @@
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A112">
+      <c r="A112" s="4">
         <v>42301.107989477103</v>
       </c>
       <c r="B112" s="1">
@@ -1284,7 +1287,7 @@
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A113">
+      <c r="A113" s="4">
         <v>42301.122882820397</v>
       </c>
       <c r="B113" s="1">
@@ -1292,7 +1295,7 @@
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A114">
+      <c r="A114" s="4">
         <v>42301.136335300602</v>
       </c>
       <c r="B114" s="1">
@@ -1300,7 +1303,7 @@
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A115">
+      <c r="A115" s="4">
         <v>42301.139095633698</v>
       </c>
       <c r="B115" s="1">
@@ -1308,7 +1311,7 @@
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A116">
+      <c r="A116" s="4">
         <v>42301.1457866977</v>
       </c>
       <c r="B116" s="1">
@@ -1316,7 +1319,7 @@
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A117">
+      <c r="A117" s="4">
         <v>42301.152890076897</v>
       </c>
       <c r="B117" s="1">
@@ -1324,7 +1327,7 @@
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A118">
+      <c r="A118" s="4">
         <v>42301.156465661901</v>
       </c>
       <c r="B118" s="1">
@@ -1332,7 +1335,7 @@
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A119">
+      <c r="A119" s="4">
         <v>42301.168900076002</v>
       </c>
       <c r="B119" s="1">
@@ -1340,7 +1343,7 @@
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A120">
+      <c r="A120" s="4">
         <v>42301.170593932999</v>
       </c>
       <c r="B120" s="1">
@@ -1348,7 +1351,7 @@
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A121">
+      <c r="A121" s="4">
         <v>42301.171652399702</v>
       </c>
       <c r="B121" s="1">
@@ -1356,7 +1359,7 @@
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A122">
+      <c r="A122" s="4">
         <v>42301.172182578397</v>
       </c>
       <c r="B122" s="1">
@@ -1364,7 +1367,7 @@
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A123">
+      <c r="A123" s="4">
         <v>42301.172286574598</v>
       </c>
       <c r="B123" s="1">
@@ -1372,7 +1375,7 @@
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A124">
+      <c r="A124" s="4">
         <v>42301.176402368597</v>
       </c>
       <c r="B124" s="1">
@@ -1380,7 +1383,7 @@
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A125">
+      <c r="A125" s="4">
         <v>42301.187953558299</v>
       </c>
       <c r="B125" s="1">
@@ -1388,7 +1391,7 @@
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A126">
+      <c r="A126" s="4">
         <v>42301.232323523</v>
       </c>
       <c r="B126" s="1">
@@ -1396,7 +1399,7 @@
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A127">
+      <c r="A127" s="4">
         <v>42301.242385164704</v>
       </c>
       <c r="B127" s="1">
@@ -1404,7 +1407,7 @@
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A128">
+      <c r="A128" s="4">
         <v>42301.270011881301</v>
       </c>
       <c r="B128" s="1">
@@ -1412,7 +1415,7 @@
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A129">
+      <c r="A129" s="4">
         <v>42301.280249626798</v>
       </c>
       <c r="B129" s="1">
@@ -1420,7 +1423,7 @@
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A130">
+      <c r="A130" s="4">
         <v>42301.285587250903</v>
       </c>
       <c r="B130" s="1">
@@ -1428,7 +1431,7 @@
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A131">
+      <c r="A131" s="4">
         <v>42301.307260836998</v>
       </c>
       <c r="B131" s="1">
@@ -1436,7 +1439,7 @@
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A132">
+      <c r="A132" s="4">
         <v>42301.321536582996</v>
       </c>
       <c r="B132" s="1">
@@ -1444,7 +1447,7 @@
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A133">
+      <c r="A133" s="4">
         <v>42301.323971046397</v>
       </c>
       <c r="B133" s="1">
@@ -1452,7 +1455,7 @@
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A134">
+      <c r="A134" s="4">
         <v>42301.326454543901</v>
       </c>
       <c r="B134" s="1">
@@ -1460,7 +1463,7 @@
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A135">
+      <c r="A135" s="4">
         <v>42301.330066976603</v>
       </c>
       <c r="B135" s="1">
@@ -1468,7 +1471,7 @@
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A136">
+      <c r="A136" s="4">
         <v>42301.339784708704</v>
       </c>
       <c r="B136" s="1">
@@ -1476,7 +1479,7 @@
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A137">
+      <c r="A137" s="4">
         <v>42301.342727483301</v>
       </c>
       <c r="B137" s="1">
@@ -1484,7 +1487,7 @@
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A138">
+      <c r="A138" s="4">
         <v>42301.348714984299</v>
       </c>
       <c r="B138" s="1">
@@ -1492,7 +1495,7 @@
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A139">
+      <c r="A139" s="4">
         <v>42301.354248814801</v>
       </c>
       <c r="B139" s="1">
@@ -1500,7 +1503,7 @@
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A140">
+      <c r="A140" s="4">
         <v>42301.3586572723</v>
       </c>
       <c r="B140" s="1">
@@ -1508,7 +1511,7 @@
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A141">
+      <c r="A141" s="4">
         <v>42301.372176323399</v>
       </c>
       <c r="B141" s="1">
@@ -1516,7 +1519,7 @@
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A142">
+      <c r="A142" s="4">
         <v>42301.374413500002</v>
       </c>
       <c r="B142" s="1">
@@ -1524,7 +1527,7 @@
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A143">
+      <c r="A143" s="4">
         <v>42301.377684547202</v>
       </c>
       <c r="B143" s="1">
@@ -1532,7 +1535,7 @@
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A144">
+      <c r="A144" s="4">
         <v>42301.385105712201</v>
       </c>
       <c r="B144" s="1">
@@ -1540,7 +1543,7 @@
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A145">
+      <c r="A145" s="4">
         <v>42301.391081674097</v>
       </c>
       <c r="B145" s="1">
@@ -1548,7 +1551,7 @@
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A146">
+      <c r="A146" s="4">
         <v>42301.3972963899</v>
       </c>
       <c r="B146" s="1">
@@ -1556,7 +1559,7 @@
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A147">
+      <c r="A147" s="4">
         <v>42301.405143309101</v>
       </c>
       <c r="B147" s="1">
@@ -1564,7 +1567,7 @@
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A148">
+      <c r="A148" s="4">
         <v>42301.417024736496</v>
       </c>
       <c r="B148" s="1">
@@ -1572,7 +1575,7 @@
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A149">
+      <c r="A149" s="4">
         <v>42301.418724125499</v>
       </c>
       <c r="B149" s="1">
@@ -1580,7 +1583,7 @@
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A150">
+      <c r="A150" s="4">
         <v>42301.425700509499</v>
       </c>
       <c r="B150" s="1">
@@ -1588,7 +1591,7 @@
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A151">
+      <c r="A151" s="4">
         <v>42301.439445071097</v>
       </c>
       <c r="B151" s="1">
@@ -1596,7 +1599,7 @@
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A152">
+      <c r="A152" s="4">
         <v>42301.446862478297</v>
       </c>
       <c r="B152" s="1">
@@ -1604,7 +1607,7 @@
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A153">
+      <c r="A153" s="4">
         <v>42301.491739455101</v>
       </c>
       <c r="B153" s="1">
@@ -1612,7 +1615,7 @@
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A154">
+      <c r="A154" s="4">
         <v>42301.509739695299</v>
       </c>
       <c r="B154" s="1">
@@ -1620,7 +1623,7 @@
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A155">
+      <c r="A155" s="4">
         <v>42301.512394830803</v>
       </c>
       <c r="B155" s="1">
@@ -1628,7 +1631,7 @@
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A156">
+      <c r="A156" s="4">
         <v>42301.517204143602</v>
       </c>
       <c r="B156" s="1">
@@ -1636,7 +1639,7 @@
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A157">
+      <c r="A157" s="4">
         <v>42301.5254818553</v>
       </c>
       <c r="B157" s="1">
@@ -1644,7 +1647,7 @@
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A158">
+      <c r="A158" s="4">
         <v>42301.536688804903</v>
       </c>
       <c r="B158" s="1">
@@ -1652,7 +1655,7 @@
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A159">
+      <c r="A159" s="4">
         <v>42301.541946260797</v>
       </c>
       <c r="B159" s="1">
@@ -1660,7 +1663,7 @@
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A160">
+      <c r="A160" s="4">
         <v>42301.550128353701</v>
       </c>
       <c r="B160" s="1">
@@ -1668,7 +1671,7 @@
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A161">
+      <c r="A161" s="4">
         <v>42301.558282357902</v>
       </c>
       <c r="B161" s="1">
@@ -1676,7 +1679,7 @@
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A162">
+      <c r="A162" s="4">
         <v>42301.576639988503</v>
       </c>
       <c r="B162" s="1">
@@ -1684,7 +1687,7 @@
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A163">
+      <c r="A163" s="4">
         <v>42301.576662684798</v>
       </c>
       <c r="B163" s="1">
@@ -1692,7 +1695,7 @@
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A164">
+      <c r="A164" s="4">
         <v>42301.620166314598</v>
       </c>
       <c r="B164" s="1">
@@ -1700,7 +1703,7 @@
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A165">
+      <c r="A165" s="4">
         <v>42301.654491117501</v>
       </c>
       <c r="B165" s="1">
@@ -1708,7 +1711,7 @@
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A166">
+      <c r="A166" s="4">
         <v>42301.667978075202</v>
       </c>
       <c r="B166" s="1">
@@ -1716,7 +1719,7 @@
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A167">
+      <c r="A167" s="4">
         <v>42301.674929434601</v>
       </c>
       <c r="B167" s="1">
@@ -1724,7 +1727,7 @@
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A168">
+      <c r="A168" s="4">
         <v>42301.686969955197</v>
       </c>
       <c r="B168" s="1">
@@ -1732,7 +1735,7 @@
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A169">
+      <c r="A169" s="4">
         <v>42301.688280340102</v>
       </c>
       <c r="B169" s="1">
@@ -1740,7 +1743,7 @@
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A170">
+      <c r="A170" s="4">
         <v>42301.697050805298</v>
       </c>
       <c r="B170" s="1">
@@ -1748,7 +1751,7 @@
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A171">
+      <c r="A171" s="4">
         <v>42301.698064875898</v>
       </c>
       <c r="B171" s="1">
@@ -1756,7 +1759,7 @@
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A172">
+      <c r="A172" s="4">
         <v>42301.699046457397</v>
       </c>
       <c r="B172" s="1">
@@ -1764,7 +1767,7 @@
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A173">
+      <c r="A173" s="4">
         <v>42301.7046320554</v>
       </c>
       <c r="B173" s="1">
@@ -1772,7 +1775,7 @@
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A174">
+      <c r="A174" s="4">
         <v>42301.719874332703</v>
       </c>
       <c r="B174" s="1">
@@ -1780,7 +1783,7 @@
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A175">
+      <c r="A175" s="4">
         <v>42301.723329269596</v>
       </c>
       <c r="B175" s="1">
@@ -1788,7 +1791,7 @@
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A176">
+      <c r="A176" s="4">
         <v>42301.728958858599</v>
       </c>
       <c r="B176" s="1">
@@ -1796,7 +1799,7 @@
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A177">
+      <c r="A177" s="4">
         <v>42301.7312216094</v>
       </c>
       <c r="B177" s="1">
@@ -1804,7 +1807,7 @@
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A178">
+      <c r="A178" s="4">
         <v>42301.731976334602</v>
       </c>
       <c r="B178" s="1">
@@ -1812,7 +1815,7 @@
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A179">
+      <c r="A179" s="4">
         <v>42301.739477192903</v>
       </c>
       <c r="B179" s="1">
@@ -1820,7 +1823,7 @@
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A180">
+      <c r="A180" s="4">
         <v>42301.751668052202</v>
       </c>
       <c r="B180" s="1">
@@ -1828,7 +1831,7 @@
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A181">
+      <c r="A181" s="4">
         <v>42301.755892918103</v>
       </c>
       <c r="B181" s="1">
@@ -1836,7 +1839,7 @@
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A182">
+      <c r="A182" s="4">
         <v>42301.756309903802</v>
       </c>
       <c r="B182" s="1">
@@ -1844,7 +1847,7 @@
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A183">
+      <c r="A183" s="4">
         <v>42301.780123874203</v>
       </c>
       <c r="B183" s="1">
@@ -1852,7 +1855,7 @@
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A184">
+      <c r="A184" s="4">
         <v>42301.786656366603</v>
       </c>
       <c r="B184" s="1">
@@ -1860,7 +1863,7 @@
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A185">
+      <c r="A185" s="4">
         <v>42301.793796872902</v>
       </c>
       <c r="B185" s="1">
@@ -1868,7 +1871,7 @@
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A186">
+      <c r="A186" s="4">
         <v>42301.803986878796</v>
       </c>
       <c r="B186" s="1">
@@ -1876,7 +1879,7 @@
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A187">
+      <c r="A187" s="4">
         <v>42301.805891698903</v>
       </c>
       <c r="B187" s="1">
@@ -1884,7 +1887,7 @@
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A188">
+      <c r="A188" s="4">
         <v>42301.815930271703</v>
       </c>
       <c r="B188" s="1">
@@ -1892,7 +1895,7 @@
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A189">
+      <c r="A189" s="4">
         <v>42301.837284297799</v>
       </c>
       <c r="B189" s="1">
@@ -1900,7 +1903,7 @@
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A190">
+      <c r="A190" s="4">
         <v>42301.837860204403</v>
       </c>
       <c r="B190" s="1">
@@ -1908,7 +1911,7 @@
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A191">
+      <c r="A191" s="4">
         <v>42301.839318394799</v>
       </c>
       <c r="B191" s="1">
@@ -1916,7 +1919,7 @@
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A192">
+      <c r="A192" s="4">
         <v>42301.8425525895</v>
       </c>
       <c r="B192" s="1">
@@ -1924,7 +1927,7 @@
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A193">
+      <c r="A193" s="4">
         <v>42301.848274528602</v>
       </c>
       <c r="B193" s="1">
@@ -1932,7 +1935,7 @@
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A194">
+      <c r="A194" s="4">
         <v>42301.872009839499</v>
       </c>
       <c r="B194" s="1">
@@ -1940,7 +1943,7 @@
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A195">
+      <c r="A195" s="4">
         <v>42301.8761945281</v>
       </c>
       <c r="B195" s="1">
@@ -1948,7 +1951,7 @@
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A196">
+      <c r="A196" s="4">
         <v>42301.882629534201</v>
       </c>
       <c r="B196" s="1">
@@ -1956,7 +1959,7 @@
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A197">
+      <c r="A197" s="4">
         <v>42301.904854244502</v>
       </c>
       <c r="B197" s="1">
@@ -1964,7 +1967,7 @@
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A198">
+      <c r="A198" s="4">
         <v>42301.9094553088</v>
       </c>
       <c r="B198" s="1">
@@ -1972,7 +1975,7 @@
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A199">
+      <c r="A199" s="4">
         <v>42301.932480579402</v>
       </c>
       <c r="B199" s="1">
@@ -1980,7 +1983,7 @@
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A200">
+      <c r="A200" s="4">
         <v>42301.934221412201</v>
       </c>
       <c r="B200" s="1">
@@ -1988,7 +1991,7 @@
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A201">
+      <c r="A201" s="4">
         <v>42301.947355263597</v>
       </c>
       <c r="B201" s="1">
@@ -1996,7 +1999,7 @@
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A202">
+      <c r="A202" s="4">
         <v>42301.9492976068</v>
       </c>
       <c r="B202" s="1">
@@ -2004,7 +2007,7 @@
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A203">
+      <c r="A203" s="4">
         <v>42301.9493007454</v>
       </c>
       <c r="B203" s="1">
@@ -2012,7 +2015,7 @@
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A204">
+      <c r="A204" s="4">
         <v>42301.956310722198</v>
       </c>
       <c r="B204" s="1">
@@ -2020,7 +2023,7 @@
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A205">
+      <c r="A205" s="4">
         <v>42301.969759179003</v>
       </c>
       <c r="B205" s="1">
@@ -2028,7 +2031,7 @@
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A206">
+      <c r="A206" s="4">
         <v>42301.970181743403</v>
       </c>
       <c r="B206" s="1">
@@ -2036,7 +2039,7 @@
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A207">
+      <c r="A207" s="4">
         <v>42302.000802541203</v>
       </c>
       <c r="B207" s="1">
@@ -2044,7 +2047,7 @@
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A208">
+      <c r="A208" s="4">
         <v>42302.010737774399</v>
       </c>
       <c r="B208" s="1">
@@ -2052,7 +2055,7 @@
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A209">
+      <c r="A209" s="4">
         <v>42302.0122786383</v>
       </c>
       <c r="B209" s="1">
@@ -2060,7 +2063,7 @@
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A210">
+      <c r="A210" s="4">
         <v>42302.016896042704</v>
       </c>
       <c r="B210" s="1">
@@ -2068,7 +2071,7 @@
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A211">
+      <c r="A211" s="4">
         <v>42302.027792987603</v>
       </c>
       <c r="B211" s="1">
@@ -2076,7 +2079,7 @@
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A212">
+      <c r="A212" s="4">
         <v>42302.035861929398</v>
       </c>
       <c r="B212" s="1">
@@ -2084,7 +2087,7 @@
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A213">
+      <c r="A213" s="4">
         <v>42302.039449304997</v>
       </c>
       <c r="B213" s="1">
@@ -2092,7 +2095,7 @@
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A214">
+      <c r="A214" s="4">
         <v>42302.0437620784</v>
       </c>
       <c r="B214" s="1">
@@ -2100,7 +2103,7 @@
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A215">
+      <c r="A215" s="4">
         <v>42302.048027745499</v>
       </c>
       <c r="B215" s="1">
@@ -2108,7 +2111,7 @@
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A216">
+      <c r="A216" s="4">
         <v>42302.058649815102</v>
       </c>
       <c r="B216" s="1">
@@ -2116,7 +2119,7 @@
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A217">
+      <c r="A217" s="4">
         <v>42302.062726763703</v>
       </c>
       <c r="B217" s="1">
@@ -2124,7 +2127,7 @@
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A218">
+      <c r="A218" s="4">
         <v>42302.067207058797</v>
       </c>
       <c r="B218" s="1">
@@ -2132,7 +2135,7 @@
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A219">
+      <c r="A219" s="4">
         <v>42302.079083629302</v>
       </c>
       <c r="B219" s="1">
@@ -2140,7 +2143,7 @@
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A220">
+      <c r="A220" s="4">
         <v>42302.081732632098</v>
       </c>
       <c r="B220" s="1">
@@ -2148,7 +2151,7 @@
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A221">
+      <c r="A221" s="4">
         <v>42302.084316228102</v>
       </c>
       <c r="B221" s="1">
@@ -2156,7 +2159,7 @@
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A222">
+      <c r="A222" s="4">
         <v>42302.090049142796</v>
       </c>
       <c r="B222" s="1">
@@ -2164,7 +2167,7 @@
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A223">
+      <c r="A223" s="4">
         <v>42302.123171738604</v>
       </c>
       <c r="B223" s="1">
@@ -2172,7 +2175,7 @@
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A224">
+      <c r="A224" s="4">
         <v>42302.125986833496</v>
       </c>
       <c r="B224" s="1">
@@ -2180,7 +2183,7 @@
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A225">
+      <c r="A225" s="4">
         <v>42302.159335126002</v>
       </c>
       <c r="B225" s="1">
@@ -2188,7 +2191,7 @@
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A226">
+      <c r="A226" s="4">
         <v>42302.181094086402</v>
       </c>
       <c r="B226" s="1">
@@ -2196,7 +2199,7 @@
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A227">
+      <c r="A227" s="4">
         <v>42302.186250996703</v>
       </c>
       <c r="B227" s="1">
@@ -2204,7 +2207,7 @@
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A228">
+      <c r="A228" s="4">
         <v>42302.202120370799</v>
       </c>
       <c r="B228" s="1">
@@ -2212,7 +2215,7 @@
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A229">
+      <c r="A229" s="4">
         <v>42302.219628220701</v>
       </c>
       <c r="B229" s="1">
@@ -2220,7 +2223,7 @@
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A230">
+      <c r="A230" s="4">
         <v>42302.233012812103</v>
       </c>
       <c r="B230" s="1">
@@ -2228,7 +2231,7 @@
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A231">
+      <c r="A231" s="4">
         <v>42302.244335478499</v>
       </c>
       <c r="B231" s="1">
@@ -2236,7 +2239,7 @@
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A232">
+      <c r="A232" s="4">
         <v>42302.247649306002</v>
       </c>
       <c r="B232" s="1">
@@ -2244,7 +2247,7 @@
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A233">
+      <c r="A233" s="4">
         <v>42302.254241039802</v>
       </c>
       <c r="B233" s="1">
@@ -2252,7 +2255,7 @@
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A234">
+      <c r="A234" s="4">
         <v>42302.255047630402</v>
       </c>
       <c r="B234" s="1">
@@ -2260,7 +2263,7 @@
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A235">
+      <c r="A235" s="4">
         <v>42302.262005886201</v>
       </c>
       <c r="B235" s="1">
@@ -2268,7 +2271,7 @@
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A236">
+      <c r="A236" s="4">
         <v>42302.268809868401</v>
       </c>
       <c r="B236" s="1">
@@ -2276,7 +2279,7 @@
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A237">
+      <c r="A237" s="4">
         <v>42302.272688803801</v>
       </c>
       <c r="B237" s="1">
@@ -2284,7 +2287,7 @@
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A238">
+      <c r="A238" s="4">
         <v>42302.293482346002</v>
       </c>
       <c r="B238" s="1">
@@ -2292,7 +2295,7 @@
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A239">
+      <c r="A239" s="4">
         <v>42302.300083043803</v>
       </c>
       <c r="B239" s="1">
@@ -2300,7 +2303,7 @@
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A240">
+      <c r="A240" s="4">
         <v>42302.329725096002</v>
       </c>
       <c r="B240" s="1">
@@ -2308,7 +2311,7 @@
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A241">
+      <c r="A241" s="4">
         <v>42302.331406477897</v>
       </c>
       <c r="B241" s="1">
@@ -2316,7 +2319,7 @@
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A242">
+      <c r="A242" s="4">
         <v>42302.337014339202</v>
       </c>
       <c r="B242" s="1">
@@ -2324,7 +2327,7 @@
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A243">
+      <c r="A243" s="4">
         <v>42302.342201233398</v>
       </c>
       <c r="B243" s="1">
@@ -2332,7 +2335,7 @@
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A244">
+      <c r="A244" s="4">
         <v>42302.351659424603</v>
       </c>
       <c r="B244" s="1">
@@ -2340,7 +2343,7 @@
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A245">
+      <c r="A245" s="4">
         <v>42302.3814157222</v>
       </c>
       <c r="B245" s="1">
@@ -2348,7 +2351,7 @@
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A246">
+      <c r="A246" s="4">
         <v>42302.420830715302</v>
       </c>
       <c r="B246" s="1">
@@ -2356,7 +2359,7 @@
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A247">
+      <c r="A247" s="4">
         <v>42302.4464611234</v>
       </c>
       <c r="B247" s="1">
@@ -2364,7 +2367,7 @@
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A248">
+      <c r="A248" s="4">
         <v>42302.454347861298</v>
       </c>
       <c r="B248" s="1">
@@ -2372,7 +2375,7 @@
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A249">
+      <c r="A249" s="4">
         <v>42302.456704126103</v>
       </c>
       <c r="B249" s="1">
@@ -2380,7 +2383,7 @@
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A250">
+      <c r="A250" s="4">
         <v>42302.463648509904</v>
       </c>
       <c r="B250" s="1">
@@ -2388,7 +2391,7 @@
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A251">
+      <c r="A251" s="4">
         <v>42302.465409915698</v>
       </c>
       <c r="B251" s="1">
@@ -2396,7 +2399,7 @@
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A252">
+      <c r="A252" s="4">
         <v>42302.475966639096</v>
       </c>
       <c r="B252" s="1">
@@ -2404,7 +2407,7 @@
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A253">
+      <c r="A253" s="4">
         <v>42302.484792601899</v>
       </c>
       <c r="B253" s="1">
@@ -2412,7 +2415,7 @@
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A254">
+      <c r="A254" s="4">
         <v>42302.5233738471</v>
       </c>
       <c r="B254" s="1">
@@ -2420,7 +2423,7 @@
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A255">
+      <c r="A255" s="4">
         <v>42302.538831115598</v>
       </c>
       <c r="B255" s="1">
@@ -2428,7 +2431,7 @@
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A256">
+      <c r="A256" s="4">
         <v>42302.539420819798</v>
       </c>
       <c r="B256" s="1">
@@ -2436,7 +2439,7 @@
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A257">
+      <c r="A257" s="4">
         <v>42302.5409588478</v>
       </c>
       <c r="B257" s="1">
@@ -2444,7 +2447,7 @@
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A258">
+      <c r="A258" s="4">
         <v>42302.545714930799</v>
       </c>
       <c r="B258" s="1">
@@ -2452,7 +2455,7 @@
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A259">
+      <c r="A259" s="4">
         <v>42302.548838014103</v>
       </c>
       <c r="B259" s="1">
@@ -2460,7 +2463,7 @@
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A260">
+      <c r="A260" s="4">
         <v>42302.564006889203</v>
       </c>
       <c r="B260" s="1">
@@ -2468,7 +2471,7 @@
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A261">
+      <c r="A261" s="4">
         <v>42302.564982491604</v>
       </c>
       <c r="B261" s="1">
@@ -2476,7 +2479,7 @@
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A262">
+      <c r="A262" s="4">
         <v>42302.572222025403</v>
       </c>
       <c r="B262" s="1">
@@ -2484,7 +2487,7 @@
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A263">
+      <c r="A263" s="4">
         <v>42302.587173441403</v>
       </c>
       <c r="B263" s="1">
@@ -2492,7 +2495,7 @@
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A264">
+      <c r="A264" s="4">
         <v>42302.587844515198</v>
       </c>
       <c r="B264" s="1">
@@ -2500,7 +2503,7 @@
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A265">
+      <c r="A265" s="4">
         <v>42302.597425394102</v>
       </c>
       <c r="B265" s="1">
@@ -2508,7 +2511,7 @@
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A266">
+      <c r="A266" s="4">
         <v>42302.5992527329</v>
       </c>
       <c r="B266" s="1">
@@ -2516,7 +2519,7 @@
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A267">
+      <c r="A267" s="4">
         <v>42302.604844510301</v>
       </c>
       <c r="B267" s="1">
@@ -2524,7 +2527,7 @@
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A268">
+      <c r="A268" s="4">
         <v>42302.605319857299</v>
       </c>
       <c r="B268" s="1">
@@ -2532,7 +2535,7 @@
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A269">
+      <c r="A269" s="4">
         <v>42302.611429352299</v>
       </c>
       <c r="B269" s="1">
@@ -2540,7 +2543,7 @@
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A270">
+      <c r="A270" s="4">
         <v>42302.619361659803</v>
       </c>
       <c r="B270" s="1">
@@ -2548,7 +2551,7 @@
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A271">
+      <c r="A271" s="4">
         <v>42302.619996114001</v>
       </c>
       <c r="B271" s="1">
@@ -2556,7 +2559,7 @@
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A272">
+      <c r="A272" s="4">
         <v>42302.625277197498</v>
       </c>
       <c r="B272" s="1">
@@ -2564,7 +2567,7 @@
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A273">
+      <c r="A273" s="4">
         <v>42302.627623720698</v>
       </c>
       <c r="B273" s="1">
@@ -2572,7 +2575,7 @@
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A274">
+      <c r="A274" s="4">
         <v>42302.639459327002</v>
       </c>
       <c r="B274" s="1">
@@ -2580,7 +2583,7 @@
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A275">
+      <c r="A275" s="4">
         <v>42302.657140561299</v>
       </c>
       <c r="B275" s="1">
@@ -2588,7 +2591,7 @@
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A276">
+      <c r="A276" s="4">
         <v>42302.662130625104</v>
       </c>
       <c r="B276" s="1">
@@ -2596,7 +2599,7 @@
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A277">
+      <c r="A277" s="4">
         <v>42302.671260357398</v>
       </c>
       <c r="B277" s="1">
@@ -2604,7 +2607,7 @@
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A278">
+      <c r="A278" s="4">
         <v>42302.705501657903</v>
       </c>
       <c r="B278" s="1">
@@ -2612,7 +2615,7 @@
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A279">
+      <c r="A279" s="4">
         <v>42302.714487323901</v>
       </c>
       <c r="B279" s="1">
@@ -2620,7 +2623,7 @@
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A280">
+      <c r="A280" s="4">
         <v>42302.759133621403</v>
       </c>
       <c r="B280" s="1">
@@ -2628,7 +2631,7 @@
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A281">
+      <c r="A281" s="4">
         <v>42302.764228845503</v>
       </c>
       <c r="B281" s="1">
@@ -2636,7 +2639,7 @@
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A282">
+      <c r="A282" s="4">
         <v>42302.7668571822</v>
       </c>
       <c r="B282" s="1">
@@ -2644,7 +2647,7 @@
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A283">
+      <c r="A283" s="4">
         <v>42302.791063225501</v>
       </c>
       <c r="B283" s="1">
@@ -2652,7 +2655,7 @@
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A284">
+      <c r="A284" s="4">
         <v>42302.821427201801</v>
       </c>
       <c r="B284" s="1">
@@ -2660,7 +2663,7 @@
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A285">
+      <c r="A285" s="4">
         <v>42302.821574280897</v>
       </c>
       <c r="B285" s="1">
@@ -2668,7 +2671,7 @@
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A286">
+      <c r="A286" s="4">
         <v>42302.823542240098</v>
       </c>
       <c r="B286" s="1">
@@ -2676,7 +2679,7 @@
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A287">
+      <c r="A287" s="4">
         <v>42302.828398579899</v>
       </c>
       <c r="B287" s="1">
@@ -2684,7 +2687,7 @@
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A288">
+      <c r="A288" s="4">
         <v>42302.832951685799</v>
       </c>
       <c r="B288" s="1">
@@ -2692,7 +2695,7 @@
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A289">
+      <c r="A289" s="4">
         <v>42302.847649241798</v>
       </c>
       <c r="B289" s="1">
@@ -2700,7 +2703,7 @@
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A290">
+      <c r="A290" s="4">
         <v>42302.864787910803</v>
       </c>
       <c r="B290" s="1">
@@ -2708,7 +2711,7 @@
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A291">
+      <c r="A291" s="4">
         <v>42302.880027138097</v>
       </c>
       <c r="B291" s="1">
@@ -2716,7 +2719,7 @@
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A292">
+      <c r="A292" s="4">
         <v>42302.889052711202</v>
       </c>
       <c r="B292" s="1">
@@ -2724,7 +2727,7 @@
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A293">
+      <c r="A293" s="4">
         <v>42302.898932390999</v>
       </c>
       <c r="B293" s="1">
@@ -2732,7 +2735,7 @@
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A294">
+      <c r="A294" s="4">
         <v>42302.899134553198</v>
       </c>
       <c r="B294" s="1">
@@ -2740,7 +2743,7 @@
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A295">
+      <c r="A295" s="4">
         <v>42302.906976694801</v>
       </c>
       <c r="B295" s="1">
@@ -2748,7 +2751,7 @@
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A296">
+      <c r="A296" s="4">
         <v>42302.9156554527</v>
       </c>
       <c r="B296" s="1">
@@ -2756,7 +2759,7 @@
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A297">
+      <c r="A297" s="4">
         <v>42302.920545771798</v>
       </c>
       <c r="B297" s="1">
@@ -2764,7 +2767,7 @@
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A298">
+      <c r="A298" s="4">
         <v>42302.932487022699</v>
       </c>
       <c r="B298" s="1">
@@ -2772,7 +2775,7 @@
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A299">
+      <c r="A299" s="4">
         <v>42302.945034695003</v>
       </c>
       <c r="B299" s="1">
@@ -2780,7 +2783,7 @@
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A300">
+      <c r="A300" s="4">
         <v>42302.987985514999</v>
       </c>
       <c r="B300" s="1">
@@ -2788,7 +2791,7 @@
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A301">
+      <c r="A301" s="4">
         <v>42302.992877422097</v>
       </c>
       <c r="B301" s="1">
@@ -2796,7 +2799,7 @@
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A302">
+      <c r="A302" s="4">
         <v>42303.010564844997</v>
       </c>
       <c r="B302" s="1">
@@ -2804,7 +2807,7 @@
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A303">
+      <c r="A303" s="4">
         <v>42303.014479343001</v>
       </c>
       <c r="B303" s="1">
@@ -2812,7 +2815,7 @@
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A304">
+      <c r="A304" s="4">
         <v>42303.015581726198</v>
       </c>
       <c r="B304" s="1">
@@ -2820,7 +2823,7 @@
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A305">
+      <c r="A305" s="4">
         <v>42303.0386238258</v>
       </c>
       <c r="B305" s="1">
@@ -2828,7 +2831,7 @@
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A306">
+      <c r="A306" s="4">
         <v>42303.043435597203</v>
       </c>
       <c r="B306" s="1">
@@ -2836,7 +2839,7 @@
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A307">
+      <c r="A307" s="4">
         <v>42303.049371768298</v>
       </c>
       <c r="B307" s="1">
@@ -2844,7 +2847,7 @@
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A308">
+      <c r="A308" s="4">
         <v>42303.049689083899</v>
       </c>
       <c r="B308" s="1">
@@ -2852,7 +2855,7 @@
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A309">
+      <c r="A309" s="4">
         <v>42303.0557106294</v>
       </c>
       <c r="B309" s="1">
@@ -2860,7 +2863,7 @@
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A310">
+      <c r="A310" s="4">
         <v>42303.062369232197</v>
       </c>
       <c r="B310" s="1">
@@ -2868,7 +2871,7 @@
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A311">
+      <c r="A311" s="4">
         <v>42303.062614836002</v>
       </c>
       <c r="B311" s="1">
@@ -2876,7 +2879,7 @@
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A312">
+      <c r="A312" s="4">
         <v>42303.065552585998</v>
       </c>
       <c r="B312" s="1">
@@ -2884,7 +2887,7 @@
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A313">
+      <c r="A313" s="4">
         <v>42303.065746547902</v>
       </c>
       <c r="B313" s="1">
@@ -2892,7 +2895,7 @@
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A314">
+      <c r="A314" s="4">
         <v>42303.076384645698</v>
       </c>
       <c r="B314" s="1">
@@ -2900,7 +2903,7 @@
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A315">
+      <c r="A315" s="4">
         <v>42303.083747798599</v>
       </c>
       <c r="B315" s="1">
@@ -2908,7 +2911,7 @@
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A316">
+      <c r="A316" s="4">
         <v>42303.087497969398</v>
       </c>
       <c r="B316" s="1">
@@ -2916,7 +2919,7 @@
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A317">
+      <c r="A317" s="4">
         <v>42303.092264375999</v>
       </c>
       <c r="B317" s="1">
@@ -2924,7 +2927,7 @@
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A318">
+      <c r="A318" s="4">
         <v>42303.1010574678</v>
       </c>
       <c r="B318" s="1">
@@ -2932,7 +2935,7 @@
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A319">
+      <c r="A319" s="4">
         <v>42303.105959121101</v>
       </c>
       <c r="B319" s="1">
@@ -2940,7 +2943,7 @@
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A320">
+      <c r="A320" s="4">
         <v>42303.110437097203</v>
       </c>
       <c r="B320" s="1">
@@ -2948,7 +2951,7 @@
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A321">
+      <c r="A321" s="4">
         <v>42303.126733813297</v>
       </c>
       <c r="B321" s="1">
@@ -2956,7 +2959,7 @@
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A322">
+      <c r="A322" s="4">
         <v>42303.128304051199</v>
       </c>
       <c r="B322" s="1">
@@ -2964,7 +2967,7 @@
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A323">
+      <c r="A323" s="4">
         <v>42303.129904077403</v>
       </c>
       <c r="B323" s="1">
@@ -2972,7 +2975,7 @@
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A324">
+      <c r="A324" s="4">
         <v>42303.130557623699</v>
       </c>
       <c r="B324" s="1">
@@ -2980,7 +2983,7 @@
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A325">
+      <c r="A325" s="4">
         <v>42303.132897488002</v>
       </c>
       <c r="B325" s="1">
@@ -2988,7 +2991,7 @@
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A326">
+      <c r="A326" s="4">
         <v>42303.148231463303</v>
       </c>
       <c r="B326" s="1">
@@ -2996,7 +2999,7 @@
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A327">
+      <c r="A327" s="4">
         <v>42303.154937544903</v>
       </c>
       <c r="B327" s="1">
@@ -3004,7 +3007,7 @@
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A328">
+      <c r="A328" s="4">
         <v>42303.155080433098</v>
       </c>
       <c r="B328" s="1">
@@ -3012,7 +3015,7 @@
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A329">
+      <c r="A329" s="4">
         <v>42303.156579759998</v>
       </c>
       <c r="B329" s="1">
@@ -3020,7 +3023,7 @@
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A330">
+      <c r="A330" s="4">
         <v>42303.171099899097</v>
       </c>
       <c r="B330" s="1">
@@ -3028,7 +3031,7 @@
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A331">
+      <c r="A331" s="4">
         <v>42303.1886021705</v>
       </c>
       <c r="B331" s="1">
@@ -3036,7 +3039,7 @@
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A332">
+      <c r="A332" s="4">
         <v>42303.190285671102</v>
       </c>
       <c r="B332" s="1">
@@ -3044,7 +3047,7 @@
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A333">
+      <c r="A333" s="4">
         <v>42303.192669670701</v>
       </c>
       <c r="B333" s="1">
@@ -3052,7 +3055,7 @@
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A334">
+      <c r="A334" s="4">
         <v>42303.194669457902</v>
       </c>
       <c r="B334" s="1">
@@ -3060,7 +3063,7 @@
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A335">
+      <c r="A335" s="4">
         <v>42303.200306204199</v>
       </c>
       <c r="B335" s="1">
@@ -3068,7 +3071,7 @@
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A336">
+      <c r="A336" s="4">
         <v>42303.229674792201</v>
       </c>
       <c r="B336" s="1">
@@ -3076,7 +3079,7 @@
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A337">
+      <c r="A337" s="4">
         <v>42303.246311659903</v>
       </c>
       <c r="B337" s="1">
@@ -3084,7 +3087,7 @@
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A338">
+      <c r="A338" s="4">
         <v>42303.251120520901</v>
       </c>
       <c r="B338" s="1">
@@ -3092,7 +3095,7 @@
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A339">
+      <c r="A339" s="4">
         <v>42303.2569726449</v>
       </c>
       <c r="B339" s="1">
@@ -3100,7 +3103,7 @@
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A340">
+      <c r="A340" s="4">
         <v>42303.263790615601</v>
       </c>
       <c r="B340" s="1">
@@ -3108,7 +3111,7 @@
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A341">
+      <c r="A341" s="4">
         <v>42303.267108582797</v>
       </c>
       <c r="B341" s="1">
@@ -3116,7 +3119,7 @@
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A342">
+      <c r="A342" s="4">
         <v>42303.269129385197</v>
       </c>
       <c r="B342" s="1">
@@ -3124,7 +3127,7 @@
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A343">
+      <c r="A343" s="4">
         <v>42303.2743431294</v>
       </c>
       <c r="B343" s="1">
@@ -3132,7 +3135,7 @@
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A344">
+      <c r="A344" s="4">
         <v>42303.280787011099</v>
       </c>
       <c r="B344" s="1">
@@ -3140,7 +3143,7 @@
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A345">
+      <c r="A345" s="4">
         <v>42303.282211566802</v>
       </c>
       <c r="B345" s="1">
@@ -3148,7 +3151,7 @@
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A346">
+      <c r="A346" s="4">
         <v>42303.287643957599</v>
       </c>
       <c r="B346" s="1">
@@ -3156,7 +3159,7 @@
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A347">
+      <c r="A347" s="4">
         <v>42303.300491604299</v>
       </c>
       <c r="B347" s="1">
@@ -3164,7 +3167,7 @@
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A348">
+      <c r="A348" s="4">
         <v>42303.304692870399</v>
       </c>
       <c r="B348" s="1">
@@ -3172,7 +3175,7 @@
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A349">
+      <c r="A349" s="4">
         <v>42303.311006981603</v>
       </c>
       <c r="B349" s="1">
@@ -3180,7 +3183,7 @@
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A350">
+      <c r="A350" s="4">
         <v>42303.311522287098</v>
       </c>
       <c r="B350" s="1">
@@ -3188,7 +3191,7 @@
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A351">
+      <c r="A351" s="4">
         <v>42303.312788871903</v>
       </c>
       <c r="B351" s="1">
@@ -3196,7 +3199,7 @@
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A352">
+      <c r="A352" s="4">
         <v>42303.337275056903</v>
       </c>
       <c r="B352" s="1">
@@ -3204,7 +3207,7 @@
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A353">
+      <c r="A353" s="4">
         <v>42303.338753359298</v>
       </c>
       <c r="B353" s="1">
@@ -3212,7 +3215,7 @@
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A354">
+      <c r="A354" s="4">
         <v>42303.351216853996</v>
       </c>
       <c r="B354" s="1">
@@ -3220,7 +3223,7 @@
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A355">
+      <c r="A355" s="4">
         <v>42303.366944662397</v>
       </c>
       <c r="B355" s="1">
@@ -3228,7 +3231,7 @@
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A356">
+      <c r="A356" s="4">
         <v>42303.375654475298</v>
       </c>
       <c r="B356" s="1">
@@ -3236,7 +3239,7 @@
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A357">
+      <c r="A357" s="4">
         <v>42303.390558566098</v>
       </c>
       <c r="B357" s="1">
@@ -3244,7 +3247,7 @@
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A358">
+      <c r="A358" s="4">
         <v>42303.391029708197</v>
       </c>
       <c r="B358" s="1">
@@ -3252,7 +3255,7 @@
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A359">
+      <c r="A359" s="4">
         <v>42303.391858175499</v>
       </c>
       <c r="B359" s="1">
@@ -3260,7 +3263,7 @@
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A360">
+      <c r="A360" s="4">
         <v>42303.409407161998</v>
       </c>
       <c r="B360" s="1">
@@ -3268,7 +3271,7 @@
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A361">
+      <c r="A361" s="4">
         <v>42303.411354688003</v>
       </c>
       <c r="B361" s="1">
@@ -3276,7 +3279,7 @@
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A362">
+      <c r="A362" s="4">
         <v>42303.420463279203</v>
       </c>
       <c r="B362" s="1">
@@ -3284,7 +3287,7 @@
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A363">
+      <c r="A363" s="4">
         <v>42303.4212107727</v>
       </c>
       <c r="B363" s="1">
@@ -3292,7 +3295,7 @@
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A364">
+      <c r="A364" s="4">
         <v>42303.423062838097</v>
       </c>
       <c r="B364" s="1">
@@ -3300,7 +3303,7 @@
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A365">
+      <c r="A365" s="4">
         <v>42303.425285243997</v>
       </c>
       <c r="B365" s="1">
@@ -3308,7 +3311,7 @@
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A366">
+      <c r="A366" s="4">
         <v>42303.434939613602</v>
       </c>
       <c r="B366" s="1">
@@ -3316,7 +3319,7 @@
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A367">
+      <c r="A367" s="4">
         <v>42303.4482169119</v>
       </c>
       <c r="B367" s="1">
@@ -3324,7 +3327,7 @@
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A368">
+      <c r="A368" s="4">
         <v>42303.450921654403</v>
       </c>
       <c r="B368" s="1">
@@ -3332,7 +3335,7 @@
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A369">
+      <c r="A369" s="4">
         <v>42303.482942914598</v>
       </c>
       <c r="B369" s="1">
@@ -3340,7 +3343,7 @@
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A370">
+      <c r="A370" s="4">
         <v>42303.498350399197</v>
       </c>
       <c r="B370" s="1">
@@ -3348,7 +3351,7 @@
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A371">
+      <c r="A371" s="4">
         <v>42303.503609503503</v>
       </c>
       <c r="B371" s="1">
@@ -3356,7 +3359,7 @@
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A372">
+      <c r="A372" s="4">
         <v>42303.539764159803</v>
       </c>
       <c r="B372" s="1">
@@ -3364,7 +3367,7 @@
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A373">
+      <c r="A373" s="4">
         <v>42303.544690130002</v>
       </c>
       <c r="B373" s="1">
@@ -3372,7 +3375,7 @@
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A374">
+      <c r="A374" s="4">
         <v>42303.5497364736</v>
       </c>
       <c r="B374" s="1">
@@ -3380,7 +3383,7 @@
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A375">
+      <c r="A375" s="4">
         <v>42303.553400636702</v>
       </c>
       <c r="B375" s="1">
@@ -3388,7 +3391,7 @@
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A376">
+      <c r="A376" s="4">
         <v>42303.556913501699</v>
       </c>
       <c r="B376" s="1">
@@ -3396,7 +3399,7 @@
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A377">
+      <c r="A377" s="4">
         <v>42303.578220505296</v>
       </c>
       <c r="B377" s="1">
@@ -3404,7 +3407,7 @@
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A378">
+      <c r="A378" s="4">
         <v>42303.584728345602</v>
       </c>
       <c r="B378" s="1">
@@ -3412,7 +3415,7 @@
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A379">
+      <c r="A379" s="4">
         <v>42303.585966753199</v>
       </c>
       <c r="B379" s="1">
@@ -3420,7 +3423,7 @@
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A380">
+      <c r="A380" s="4">
         <v>42303.587316123303</v>
       </c>
       <c r="B380" s="1">
@@ -3428,7 +3431,7 @@
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A381">
+      <c r="A381" s="4">
         <v>42303.593902203902</v>
       </c>
       <c r="B381" s="1">
@@ -3436,7 +3439,7 @@
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A382">
+      <c r="A382" s="4">
         <v>42303.603427738999</v>
       </c>
       <c r="B382" s="1">
@@ -3444,7 +3447,7 @@
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A383">
+      <c r="A383" s="4">
         <v>42303.626517927398</v>
       </c>
       <c r="B383" s="1">
@@ -3452,7 +3455,7 @@
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A384">
+      <c r="A384" s="4">
         <v>42303.633904861701</v>
       </c>
       <c r="B384" s="1">
@@ -3460,7 +3463,7 @@
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A385">
+      <c r="A385" s="4">
         <v>42303.644315274301</v>
       </c>
       <c r="B385" s="1">
@@ -3468,7 +3471,7 @@
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A386">
+      <c r="A386" s="4">
         <v>42303.6514126232</v>
       </c>
       <c r="B386" s="1">
@@ -3476,7 +3479,7 @@
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A387">
+      <c r="A387" s="4">
         <v>42303.654645653703</v>
       </c>
       <c r="B387" s="1">
@@ -3484,7 +3487,7 @@
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A388">
+      <c r="A388" s="4">
         <v>42303.6777637911</v>
       </c>
       <c r="B388" s="1">
@@ -3492,7 +3495,7 @@
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A389">
+      <c r="A389" s="4">
         <v>42303.686905309303</v>
       </c>
       <c r="B389" s="1">
@@ -3500,7 +3503,7 @@
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A390">
+      <c r="A390" s="4">
         <v>42303.699093728501</v>
       </c>
       <c r="B390" s="1">
@@ -3508,7 +3511,7 @@
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A391">
+      <c r="A391" s="4">
         <v>42303.738680369097</v>
       </c>
       <c r="B391" s="1">
@@ -3516,7 +3519,7 @@
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A392">
+      <c r="A392" s="4">
         <v>42303.757844567001</v>
       </c>
       <c r="B392" s="1">
@@ -3524,7 +3527,7 @@
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A393">
+      <c r="A393" s="4">
         <v>42303.761214711601</v>
       </c>
       <c r="B393" s="1">
@@ -3532,7 +3535,7 @@
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A394">
+      <c r="A394" s="4">
         <v>42303.763456279397</v>
       </c>
       <c r="B394" s="1">
@@ -3540,7 +3543,7 @@
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A395">
+      <c r="A395" s="4">
         <v>42303.769827587697</v>
       </c>
       <c r="B395" s="1">
@@ -3548,7 +3551,7 @@
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A396">
+      <c r="A396" s="4">
         <v>42303.770837276497</v>
       </c>
       <c r="B396" s="1">
@@ -3556,7 +3559,7 @@
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A397">
+      <c r="A397" s="4">
         <v>42303.782220115601</v>
       </c>
       <c r="B397" s="1">
@@ -3564,7 +3567,7 @@
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A398">
+      <c r="A398" s="4">
         <v>42303.78620979</v>
       </c>
       <c r="B398" s="1">
@@ -3572,7 +3575,7 @@
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A399">
+      <c r="A399" s="4">
         <v>42303.786562197798</v>
       </c>
       <c r="B399" s="1">
@@ -3580,7 +3583,7 @@
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A400">
+      <c r="A400" s="4">
         <v>42303.793450008401</v>
       </c>
       <c r="B400" s="1">
@@ -3588,7 +3591,7 @@
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A401">
+      <c r="A401" s="4">
         <v>42303.7943363062</v>
       </c>
       <c r="B401" s="1">
@@ -3596,7 +3599,7 @@
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A402">
+      <c r="A402" s="4">
         <v>42303.802183090302</v>
       </c>
       <c r="B402" s="1">
@@ -3604,7 +3607,7 @@
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A403">
+      <c r="A403" s="4">
         <v>42303.802801772603</v>
       </c>
       <c r="B403" s="1">
@@ -3612,7 +3615,7 @@
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A404">
+      <c r="A404" s="4">
         <v>42303.807435260896</v>
       </c>
       <c r="B404" s="1">
@@ -3620,7 +3623,7 @@
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A405">
+      <c r="A405" s="4">
         <v>42303.810470008197</v>
       </c>
       <c r="B405" s="1">
@@ -3628,7 +3631,7 @@
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A406">
+      <c r="A406" s="4">
         <v>42303.825040825199</v>
       </c>
       <c r="B406" s="1">
@@ -3636,7 +3639,7 @@
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A407">
+      <c r="A407" s="4">
         <v>42303.828789328902</v>
       </c>
       <c r="B407" s="1">
@@ -3644,7 +3647,7 @@
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A408">
+      <c r="A408" s="4">
         <v>42303.871269621501</v>
       </c>
       <c r="B408" s="1">
@@ -3652,7 +3655,7 @@
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A409">
+      <c r="A409" s="4">
         <v>42303.903611889997</v>
       </c>
       <c r="B409" s="1">
@@ -3660,7 +3663,7 @@
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A410">
+      <c r="A410" s="4">
         <v>42303.9100965775</v>
       </c>
       <c r="B410" s="1">
@@ -3668,7 +3671,7 @@
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A411">
+      <c r="A411" s="4">
         <v>42303.918772969897</v>
       </c>
       <c r="B411" s="1">
@@ -3676,7 +3679,7 @@
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A412">
+      <c r="A412" s="4">
         <v>42303.923508908403</v>
       </c>
       <c r="B412" s="1">
@@ -3684,7 +3687,7 @@
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A413">
+      <c r="A413" s="4">
         <v>42303.927877640301</v>
       </c>
       <c r="B413" s="1">
@@ -3692,7 +3695,7 @@
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A414">
+      <c r="A414" s="4">
         <v>42303.937411543302</v>
       </c>
       <c r="B414" s="1">
@@ -3700,7 +3703,7 @@
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A415">
+      <c r="A415" s="4">
         <v>42303.9480587168</v>
       </c>
       <c r="B415" s="1">
@@ -3708,7 +3711,7 @@
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A416">
+      <c r="A416" s="4">
         <v>42303.9609325243</v>
       </c>
       <c r="B416" s="1">
@@ -3716,7 +3719,7 @@
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A417">
+      <c r="A417" s="4">
         <v>42303.967620095798</v>
       </c>
       <c r="B417" s="1">
@@ -3724,7 +3727,7 @@
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A418">
+      <c r="A418" s="4">
         <v>42303.998332153897</v>
       </c>
       <c r="B418" s="1">
@@ -3732,7 +3735,7 @@
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A419">
+      <c r="A419" s="4">
         <v>42303.9993143826</v>
       </c>
       <c r="B419" s="1">
@@ -3740,7 +3743,7 @@
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A420">
+      <c r="A420" s="4">
         <v>42304.008887368604</v>
       </c>
       <c r="B420" s="1">
@@ -3748,7 +3751,7 @@
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A421">
+      <c r="A421" s="4">
         <v>42304.015017697297</v>
       </c>
       <c r="B421" s="1">
@@ -3756,7 +3759,7 @@
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A422">
+      <c r="A422" s="4">
         <v>42304.016076471402</v>
       </c>
       <c r="B422" s="1">
@@ -3764,7 +3767,7 @@
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A423">
+      <c r="A423" s="4">
         <v>42304.028783991198</v>
       </c>
       <c r="B423" s="1">
@@ -3772,7 +3775,7 @@
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A424">
+      <c r="A424" s="4">
         <v>42304.047627390399</v>
       </c>
       <c r="B424" s="1">
@@ -3780,7 +3783,7 @@
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A425">
+      <c r="A425" s="4">
         <v>42304.051217373599</v>
       </c>
       <c r="B425" s="1">
@@ -3788,7 +3791,7 @@
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A426">
+      <c r="A426" s="4">
         <v>42304.079436406799</v>
       </c>
       <c r="B426" s="1">
@@ -3796,7 +3799,7 @@
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A427">
+      <c r="A427" s="4">
         <v>42304.087892178199</v>
       </c>
       <c r="B427" s="1">
@@ -3804,7 +3807,7 @@
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A428">
+      <c r="A428" s="4">
         <v>42304.102978384501</v>
       </c>
       <c r="B428" s="1">
@@ -3812,7 +3815,7 @@
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A429">
+      <c r="A429" s="4">
         <v>42304.118570089398</v>
       </c>
       <c r="B429" s="1">
@@ -3820,7 +3823,7 @@
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A430">
+      <c r="A430" s="4">
         <v>42304.133302532799</v>
       </c>
       <c r="B430" s="1">
@@ -3828,7 +3831,7 @@
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A431">
+      <c r="A431" s="4">
         <v>42304.137248150902</v>
       </c>
       <c r="B431" s="1">
@@ -3836,7 +3839,7 @@
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A432">
+      <c r="A432" s="4">
         <v>42304.1448122972</v>
       </c>
       <c r="B432" s="1">
@@ -3844,7 +3847,7 @@
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A433">
+      <c r="A433" s="4">
         <v>42304.148999048703</v>
       </c>
       <c r="B433" s="1">
@@ -3852,7 +3855,7 @@
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A434">
+      <c r="A434" s="4">
         <v>42304.149754374601</v>
       </c>
       <c r="B434" s="1">
@@ -3860,7 +3863,7 @@
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A435">
+      <c r="A435" s="4">
         <v>42304.154436976198</v>
       </c>
       <c r="B435" s="1">
@@ -3868,7 +3871,7 @@
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A436">
+      <c r="A436" s="4">
         <v>42304.162846037099</v>
       </c>
       <c r="B436" s="1">
@@ -3876,7 +3879,7 @@
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A437">
+      <c r="A437" s="4">
         <v>42304.166551183102</v>
       </c>
       <c r="B437" s="1">
@@ -3884,7 +3887,7 @@
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A438">
+      <c r="A438" s="4">
         <v>42304.168988882702</v>
       </c>
       <c r="B438" s="1">
@@ -3892,7 +3895,7 @@
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A439">
+      <c r="A439" s="4">
         <v>42304.181929680301</v>
       </c>
       <c r="B439" s="1">
@@ -3900,7 +3903,7 @@
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A440">
+      <c r="A440" s="4">
         <v>42304.182994270501</v>
       </c>
       <c r="B440" s="1">
@@ -3908,7 +3911,7 @@
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A441">
+      <c r="A441" s="4">
         <v>42304.198666008597</v>
       </c>
       <c r="B441" s="1">
@@ -3916,7 +3919,7 @@
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A442">
+      <c r="A442" s="4">
         <v>42304.2148838883</v>
       </c>
       <c r="B442" s="1">
@@ -3924,7 +3927,7 @@
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A443">
+      <c r="A443" s="4">
         <v>42304.222303693597</v>
       </c>
       <c r="B443" s="1">
@@ -3932,7 +3935,7 @@
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A444">
+      <c r="A444" s="4">
         <v>42304.230087823002</v>
       </c>
       <c r="B444" s="1">
@@ -3940,7 +3943,7 @@
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A445">
+      <c r="A445" s="4">
         <v>42304.231744315301</v>
       </c>
       <c r="B445" s="1">
@@ -3948,7 +3951,7 @@
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A446">
+      <c r="A446" s="4">
         <v>42304.239058043</v>
       </c>
       <c r="B446" s="1">
@@ -3956,7 +3959,7 @@
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A447">
+      <c r="A447" s="4">
         <v>42304.239996662604</v>
       </c>
       <c r="B447" s="1">
@@ -3964,7 +3967,7 @@
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A448">
+      <c r="A448" s="4">
         <v>42304.244216797299</v>
       </c>
       <c r="B448" s="1">
@@ -3972,7 +3975,7 @@
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A449">
+      <c r="A449" s="4">
         <v>42304.256402962703</v>
       </c>
       <c r="B449" s="1">
@@ -3980,7 +3983,7 @@
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A450">
+      <c r="A450" s="4">
         <v>42304.264429394403</v>
       </c>
       <c r="B450" s="1">
@@ -3988,7 +3991,7 @@
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A451">
+      <c r="A451" s="4">
         <v>42304.285652062099</v>
       </c>
       <c r="B451" s="1">
@@ -3996,7 +3999,7 @@
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A452">
+      <c r="A452" s="4">
         <v>42304.287700394401</v>
       </c>
       <c r="B452" s="1">
@@ -4004,7 +4007,7 @@
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A453">
+      <c r="A453" s="4">
         <v>42304.287869182597</v>
       </c>
       <c r="B453" s="1">
@@ -4012,7 +4015,7 @@
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A454">
+      <c r="A454" s="4">
         <v>42304.294058328996</v>
       </c>
       <c r="B454" s="1">
@@ -4020,7 +4023,7 @@
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A455">
+      <c r="A455" s="4">
         <v>42304.299707065999</v>
       </c>
       <c r="B455" s="1">
@@ -4028,7 +4031,7 @@
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A456">
+      <c r="A456" s="4">
         <v>42304.300901384799</v>
       </c>
       <c r="B456" s="1">
@@ -4036,7 +4039,7 @@
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A457">
+      <c r="A457" s="4">
         <v>42304.302405251998</v>
       </c>
       <c r="B457" s="1">
@@ -4044,7 +4047,7 @@
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A458">
+      <c r="A458" s="4">
         <v>42304.3102187041</v>
       </c>
       <c r="B458" s="1">
@@ -4052,7 +4055,7 @@
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A459">
+      <c r="A459" s="4">
         <v>42304.311774003603</v>
       </c>
       <c r="B459" s="1">
@@ -4060,7 +4063,7 @@
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A460">
+      <c r="A460" s="4">
         <v>42304.321905000797</v>
       </c>
       <c r="B460" s="1">
@@ -4068,7 +4071,7 @@
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A461">
+      <c r="A461" s="4">
         <v>42304.322638859703</v>
       </c>
       <c r="B461" s="1">
@@ -4076,7 +4079,7 @@
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A462">
+      <c r="A462" s="4">
         <v>42304.323106667704</v>
       </c>
       <c r="B462" s="1">
@@ -4084,7 +4087,7 @@
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A463">
+      <c r="A463" s="4">
         <v>42304.325171479803</v>
       </c>
       <c r="B463" s="1">
@@ -4092,7 +4095,7 @@
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A464">
+      <c r="A464" s="4">
         <v>42304.339669025001</v>
       </c>
       <c r="B464" s="1">
@@ -4100,7 +4103,7 @@
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A465">
+      <c r="A465" s="4">
         <v>42304.350254991899</v>
       </c>
       <c r="B465" s="1">
@@ -4108,7 +4111,7 @@
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A466">
+      <c r="A466" s="4">
         <v>42304.360579382897</v>
       </c>
       <c r="B466" s="1">
@@ -4116,7 +4119,7 @@
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A467">
+      <c r="A467" s="4">
         <v>42304.360624519497</v>
       </c>
       <c r="B467" s="1">
@@ -4124,7 +4127,7 @@
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A468">
+      <c r="A468" s="4">
         <v>42304.373714542802</v>
       </c>
       <c r="B468" s="1">
@@ -4132,7 +4135,7 @@
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A469">
+      <c r="A469" s="4">
         <v>42304.407466759301</v>
       </c>
       <c r="B469" s="1">
@@ -4140,7 +4143,7 @@
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A470">
+      <c r="A470" s="4">
         <v>42304.433044859601</v>
       </c>
       <c r="B470" s="1">
@@ -4148,7 +4151,7 @@
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A471">
+      <c r="A471" s="4">
         <v>42304.439843612403</v>
       </c>
       <c r="B471" s="1">
@@ -4156,7 +4159,7 @@
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A472">
+      <c r="A472" s="4">
         <v>42304.447062941297</v>
       </c>
       <c r="B472" s="1">
@@ -4164,7 +4167,7 @@
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A473">
+      <c r="A473" s="4">
         <v>42304.498973028902</v>
       </c>
       <c r="B473" s="1">
@@ -4172,7 +4175,7 @@
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A474">
+      <c r="A474" s="4">
         <v>42304.528314249997</v>
       </c>
       <c r="B474" s="1">
@@ -4180,7 +4183,7 @@
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A475">
+      <c r="A475" s="4">
         <v>42304.530841813001</v>
       </c>
       <c r="B475" s="1">
@@ -4188,7 +4191,7 @@
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A476">
+      <c r="A476" s="4">
         <v>42304.535764816901</v>
       </c>
       <c r="B476" s="1">
@@ -4196,7 +4199,7 @@
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A477">
+      <c r="A477" s="4">
         <v>42304.538164313803</v>
       </c>
       <c r="B477" s="1">
@@ -4204,7 +4207,7 @@
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A478">
+      <c r="A478" s="4">
         <v>42304.538790465202</v>
       </c>
       <c r="B478" s="1">
@@ -4212,7 +4215,7 @@
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A479">
+      <c r="A479" s="4">
         <v>42304.545280331004</v>
       </c>
       <c r="B479" s="1">
@@ -4220,7 +4223,7 @@
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A480">
+      <c r="A480" s="4">
         <v>42304.5459031297</v>
       </c>
       <c r="B480" s="1">
@@ -4228,7 +4231,7 @@
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A481">
+      <c r="A481" s="4">
         <v>42304.5491353779</v>
       </c>
       <c r="B481" s="1">
@@ -4236,7 +4239,7 @@
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A482">
+      <c r="A482" s="4">
         <v>42304.558664452001</v>
       </c>
       <c r="B482" s="1">
@@ -4244,7 +4247,7 @@
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A483">
+      <c r="A483" s="4">
         <v>42304.568380968798</v>
       </c>
       <c r="B483" s="1">
@@ -4252,7 +4255,7 @@
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A484">
+      <c r="A484" s="4">
         <v>42304.572320142099</v>
       </c>
       <c r="B484" s="1">
@@ -4260,7 +4263,7 @@
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A485">
+      <c r="A485" s="4">
         <v>42304.588032532498</v>
       </c>
       <c r="B485" s="1">
@@ -4268,7 +4271,7 @@
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A486">
+      <c r="A486" s="4">
         <v>42304.6022466902</v>
       </c>
       <c r="B486" s="1">
@@ -4276,7 +4279,7 @@
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A487">
+      <c r="A487" s="4">
         <v>42304.643692856102</v>
       </c>
       <c r="B487" s="1">
@@ -4284,7 +4287,7 @@
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A488">
+      <c r="A488" s="4">
         <v>42304.645150469099</v>
       </c>
       <c r="B488" s="1">
@@ -4292,7 +4295,7 @@
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A489">
+      <c r="A489" s="4">
         <v>42304.648847987497</v>
       </c>
       <c r="B489" s="1">
@@ -4300,7 +4303,7 @@
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A490">
+      <c r="A490" s="4">
         <v>42304.664165231603</v>
       </c>
       <c r="B490" s="1">
@@ -4308,7 +4311,7 @@
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A491">
+      <c r="A491" s="4">
         <v>42304.688659114101</v>
       </c>
       <c r="B491" s="1">
@@ -4316,7 +4319,7 @@
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A492">
+      <c r="A492" s="4">
         <v>42304.693184252297</v>
       </c>
       <c r="B492" s="1">
@@ -4324,7 +4327,7 @@
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A493">
+      <c r="A493" s="4">
         <v>42304.693395182898</v>
       </c>
       <c r="B493" s="1">
@@ -4332,7 +4335,7 @@
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A494">
+      <c r="A494" s="4">
         <v>42304.750409127999</v>
       </c>
       <c r="B494" s="1">
@@ -4340,7 +4343,7 @@
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A495">
+      <c r="A495" s="4">
         <v>42304.765161580901</v>
       </c>
       <c r="B495" s="1">
@@ -4348,7 +4351,7 @@
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A496">
+      <c r="A496" s="4">
         <v>42304.773487078797</v>
       </c>
       <c r="B496" s="1">
@@ -4356,7 +4359,7 @@
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A497">
+      <c r="A497" s="4">
         <v>42304.7746500586</v>
       </c>
       <c r="B497" s="1">
@@ -4364,7 +4367,7 @@
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A498">
+      <c r="A498" s="4">
         <v>42304.815969438903</v>
       </c>
       <c r="B498" s="1">
@@ -4372,7 +4375,7 @@
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A499">
+      <c r="A499" s="4">
         <v>42304.8248499213</v>
       </c>
       <c r="B499" s="1">
@@ -4380,7 +4383,7 @@
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A500">
+      <c r="A500" s="4">
         <v>42304.834169280199</v>
       </c>
       <c r="B500" s="1">
@@ -4388,7 +4391,7 @@
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A501">
+      <c r="A501" s="4">
         <v>42304.834350897399</v>
       </c>
       <c r="B501" s="1">
@@ -4396,7 +4399,7 @@
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A502">
+      <c r="A502" s="4">
         <v>42304.842752922203</v>
       </c>
       <c r="B502" s="1">
@@ -4404,7 +4407,7 @@
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A503">
+      <c r="A503" s="4">
         <v>42304.851141773303</v>
       </c>
       <c r="B503" s="1">
@@ -4412,7 +4415,7 @@
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A504">
+      <c r="A504" s="4">
         <v>42304.854932847702</v>
       </c>
       <c r="B504" s="1">
@@ -4420,7 +4423,7 @@
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A505">
+      <c r="A505" s="4">
         <v>42304.8614359848</v>
       </c>
       <c r="B505" s="1">
@@ -4428,7 +4431,7 @@
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A506">
+      <c r="A506" s="4">
         <v>42304.863231574796</v>
       </c>
       <c r="B506" s="1">
@@ -4436,7 +4439,7 @@
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A507">
+      <c r="A507" s="4">
         <v>42304.864494709102</v>
       </c>
       <c r="B507" s="1">
@@ -4444,7 +4447,7 @@
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A508">
+      <c r="A508" s="4">
         <v>42304.867487723801</v>
       </c>
       <c r="B508" s="1">
@@ -4452,7 +4455,7 @@
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A509">
+      <c r="A509" s="4">
         <v>42304.870824149803</v>
       </c>
       <c r="B509" s="1">
@@ -4460,7 +4463,7 @@
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A510">
+      <c r="A510" s="4">
         <v>42304.884790873701</v>
       </c>
       <c r="B510" s="1">
@@ -4468,7 +4471,7 @@
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A511">
+      <c r="A511" s="4">
         <v>42304.891510925198</v>
       </c>
       <c r="B511" s="1">
@@ -4476,7 +4479,7 @@
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A512">
+      <c r="A512" s="4">
         <v>42304.902589803904</v>
       </c>
       <c r="B512" s="1">
@@ -4484,7 +4487,7 @@
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A513">
+      <c r="A513" s="4">
         <v>42304.913456280497</v>
       </c>
       <c r="B513" s="1">
@@ -4492,7 +4495,7 @@
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A514">
+      <c r="A514" s="4">
         <v>42304.955492742003</v>
       </c>
       <c r="B514" s="1">
@@ -4500,7 +4503,7 @@
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A515">
+      <c r="A515" s="4">
         <v>42304.966221476003</v>
       </c>
       <c r="B515" s="1">
@@ -4508,7 +4511,7 @@
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A516">
+      <c r="A516" s="4">
         <v>42304.984136849504</v>
       </c>
       <c r="B516" s="1">
@@ -4516,7 +4519,7 @@
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A517">
+      <c r="A517" s="4">
         <v>42304.993570136998</v>
       </c>
       <c r="B517" s="1">
@@ -4524,7 +4527,7 @@
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A518">
+      <c r="A518" s="4">
         <v>42304.998489639198</v>
       </c>
       <c r="B518" s="1">
@@ -4532,7 +4535,7 @@
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A519">
+      <c r="A519" s="4">
         <v>42305.049318046898</v>
       </c>
       <c r="B519" s="1">
@@ -4540,7 +4543,7 @@
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A520">
+      <c r="A520" s="4">
         <v>42305.059065884001</v>
       </c>
       <c r="B520" s="1">
@@ -4548,7 +4551,7 @@
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A521">
+      <c r="A521" s="4">
         <v>42305.064060106102</v>
       </c>
       <c r="B521" s="1">
@@ -4556,7 +4559,7 @@
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A522">
+      <c r="A522" s="4">
         <v>42305.064092525499</v>
       </c>
       <c r="B522" s="1">
@@ -4564,7 +4567,7 @@
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A523">
+      <c r="A523" s="4">
         <v>42305.075581181503</v>
       </c>
       <c r="B523" s="1">
@@ -4572,7 +4575,7 @@
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A524">
+      <c r="A524" s="4">
         <v>42305.096773623103</v>
       </c>
       <c r="B524" s="1">
@@ -4580,7 +4583,7 @@
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A525">
+      <c r="A525" s="4">
         <v>42305.099189627697</v>
       </c>
       <c r="B525" s="1">
@@ -4588,7 +4591,7 @@
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A526">
+      <c r="A526" s="4">
         <v>42305.120116209197</v>
       </c>
       <c r="B526" s="1">
@@ -4596,7 +4599,7 @@
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A527">
+      <c r="A527" s="4">
         <v>42305.124773078402</v>
       </c>
       <c r="B527" s="1">
@@ -4604,7 +4607,7 @@
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A528">
+      <c r="A528" s="4">
         <v>42305.135791453802</v>
       </c>
       <c r="B528" s="1">
@@ -4612,7 +4615,7 @@
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A529">
+      <c r="A529" s="4">
         <v>42305.155918136399</v>
       </c>
       <c r="B529" s="1">
@@ -4620,7 +4623,7 @@
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A530">
+      <c r="A530" s="4">
         <v>42305.161512204802</v>
       </c>
       <c r="B530" s="1">
@@ -4628,7 +4631,7 @@
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A531">
+      <c r="A531" s="4">
         <v>42305.170450564197</v>
       </c>
       <c r="B531" s="1">
@@ -4636,7 +4639,7 @@
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A532">
+      <c r="A532" s="4">
         <v>42305.171007634897</v>
       </c>
       <c r="B532" s="1">
@@ -4644,7 +4647,7 @@
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A533">
+      <c r="A533" s="4">
         <v>42305.186657370497</v>
       </c>
       <c r="B533" s="1">
@@ -4652,7 +4655,7 @@
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A534">
+      <c r="A534" s="4">
         <v>42305.194461174098</v>
       </c>
       <c r="B534" s="1">
@@ -4660,7 +4663,7 @@
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A535">
+      <c r="A535" s="4">
         <v>42305.204293626499</v>
       </c>
       <c r="B535" s="1">
@@ -4668,7 +4671,7 @@
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A536">
+      <c r="A536" s="4">
         <v>42305.207392486103</v>
       </c>
       <c r="B536" s="1">
@@ -4676,7 +4679,7 @@
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A537">
+      <c r="A537" s="4">
         <v>42305.207919013999</v>
       </c>
       <c r="B537" s="1">
@@ -4684,7 +4687,7 @@
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A538">
+      <c r="A538" s="4">
         <v>42305.220133454401</v>
       </c>
       <c r="B538" s="1">
@@ -4692,7 +4695,7 @@
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A539">
+      <c r="A539" s="4">
         <v>42305.2234179964</v>
       </c>
       <c r="B539" s="1">
@@ -4700,7 +4703,7 @@
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A540">
+      <c r="A540" s="4">
         <v>42305.228194493997</v>
       </c>
       <c r="B540" s="1">
@@ -4708,7 +4711,7 @@
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A541">
+      <c r="A541" s="4">
         <v>42305.244677949602</v>
       </c>
       <c r="B541" s="1">
@@ -4716,7 +4719,7 @@
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A542">
+      <c r="A542" s="4">
         <v>42305.245633500599</v>
       </c>
       <c r="B542" s="1">
@@ -4724,7 +4727,7 @@
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A543">
+      <c r="A543" s="4">
         <v>42305.248378429598</v>
       </c>
       <c r="B543" s="1">
@@ -4732,7 +4735,7 @@
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A544">
+      <c r="A544" s="4">
         <v>42305.248400683602</v>
       </c>
       <c r="B544" s="1">
@@ -4740,7 +4743,7 @@
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A545">
+      <c r="A545" s="4">
         <v>42305.257707288001</v>
       </c>
       <c r="B545" s="1">
@@ -4748,7 +4751,7 @@
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A546">
+      <c r="A546" s="4">
         <v>42305.262762688697</v>
       </c>
       <c r="B546" s="1">
@@ -4756,7 +4759,7 @@
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A547">
+      <c r="A547" s="4">
         <v>42305.277654895799</v>
       </c>
       <c r="B547" s="1">
@@ -4764,7 +4767,7 @@
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A548">
+      <c r="A548" s="4">
         <v>42305.278908321001</v>
       </c>
       <c r="B548" s="1">
@@ -4772,7 +4775,7 @@
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A549">
+      <c r="A549" s="4">
         <v>42305.280027160799</v>
       </c>
       <c r="B549" s="1">
@@ -4780,7 +4783,7 @@
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A550">
+      <c r="A550" s="4">
         <v>42305.286121060803</v>
       </c>
       <c r="B550" s="1">
@@ -4788,7 +4791,7 @@
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A551">
+      <c r="A551" s="4">
         <v>42305.311721666498</v>
       </c>
       <c r="B551" s="1">
@@ -4796,7 +4799,7 @@
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A552">
+      <c r="A552" s="4">
         <v>42305.319251675202</v>
       </c>
       <c r="B552" s="1">
@@ -4804,7 +4807,7 @@
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A553">
+      <c r="A553" s="4">
         <v>42305.327992738603</v>
       </c>
       <c r="B553" s="1">
@@ -4812,7 +4815,7 @@
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A554">
+      <c r="A554" s="4">
         <v>42305.331653078603</v>
       </c>
       <c r="B554" s="1">
@@ -4820,7 +4823,7 @@
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A555">
+      <c r="A555" s="4">
         <v>42305.337157795999</v>
       </c>
       <c r="B555" s="1">
@@ -4828,7 +4831,7 @@
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A556">
+      <c r="A556" s="4">
         <v>42305.348567028799</v>
       </c>
       <c r="B556" s="1">
@@ -4836,7 +4839,7 @@
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A557">
+      <c r="A557" s="4">
         <v>42305.354123243596</v>
       </c>
       <c r="B557" s="1">
@@ -4844,7 +4847,7 @@
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A558">
+      <c r="A558" s="4">
         <v>42305.363635069603</v>
       </c>
       <c r="B558" s="1">
@@ -4852,7 +4855,7 @@
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A559">
+      <c r="A559" s="4">
         <v>42305.393593734298</v>
       </c>
       <c r="B559" s="1">
@@ -4860,7 +4863,7 @@
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A560">
+      <c r="A560" s="4">
         <v>42305.416598492498</v>
       </c>
       <c r="B560" s="1">
@@ -4868,7 +4871,7 @@
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A561">
+      <c r="A561" s="4">
         <v>42305.4206714131</v>
       </c>
       <c r="B561" s="1">
@@ -4876,7 +4879,7 @@
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A562">
+      <c r="A562" s="4">
         <v>42305.431550974798</v>
       </c>
       <c r="B562" s="1">
@@ -4884,7 +4887,7 @@
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A563">
+      <c r="A563" s="4">
         <v>42305.432277350599</v>
       </c>
       <c r="B563" s="1">
@@ -4892,7 +4895,7 @@
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A564">
+      <c r="A564" s="4">
         <v>42305.441476387197</v>
       </c>
       <c r="B564" s="1">
@@ -4900,7 +4903,7 @@
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A565">
+      <c r="A565" s="4">
         <v>42305.458673496702</v>
       </c>
       <c r="B565" s="1">
@@ -4908,7 +4911,7 @@
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A566">
+      <c r="A566" s="4">
         <v>42305.480588882201</v>
       </c>
       <c r="B566" s="1">
@@ -4916,7 +4919,7 @@
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A567">
+      <c r="A567" s="4">
         <v>42305.4944585064</v>
       </c>
       <c r="B567" s="1">
@@ -4924,7 +4927,7 @@
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A568">
+      <c r="A568" s="4">
         <v>42305.498591823198</v>
       </c>
       <c r="B568" s="1">
@@ -4932,7 +4935,7 @@
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A569">
+      <c r="A569" s="4">
         <v>42305.510704781998</v>
       </c>
       <c r="B569" s="1">
@@ -4940,7 +4943,7 @@
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A570">
+      <c r="A570" s="4">
         <v>42305.511272539603</v>
       </c>
       <c r="B570" s="1">
@@ -4948,7 +4951,7 @@
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A571">
+      <c r="A571" s="4">
         <v>42305.531566799698</v>
       </c>
       <c r="B571" s="1">
@@ -4956,7 +4959,7 @@
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A572">
+      <c r="A572" s="4">
         <v>42305.538014183199</v>
       </c>
       <c r="B572" s="1">
@@ -4964,7 +4967,7 @@
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A573">
+      <c r="A573" s="4">
         <v>42305.540894200501</v>
       </c>
       <c r="B573" s="1">
@@ -4972,7 +4975,7 @@
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A574">
+      <c r="A574" s="4">
         <v>42305.5498950564</v>
       </c>
       <c r="B574" s="1">
@@ -4980,7 +4983,7 @@
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A575">
+      <c r="A575" s="4">
         <v>42305.559021859699</v>
       </c>
       <c r="B575" s="1">
@@ -4988,7 +4991,7 @@
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A576">
+      <c r="A576" s="4">
         <v>42305.568012862102</v>
       </c>
       <c r="B576" s="1">
@@ -4996,7 +4999,7 @@
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A577">
+      <c r="A577" s="4">
         <v>42305.571609383303</v>
       </c>
       <c r="B577" s="1">
@@ -5004,7 +5007,7 @@
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A578">
+      <c r="A578" s="4">
         <v>42305.5737406685</v>
       </c>
       <c r="B578" s="1">
@@ -5012,7 +5015,7 @@
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A579">
+      <c r="A579" s="4">
         <v>42305.581061804798</v>
       </c>
       <c r="B579" s="1">
@@ -5020,7 +5023,7 @@
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A580">
+      <c r="A580" s="4">
         <v>42305.581798355299</v>
       </c>
       <c r="B580" s="1">
@@ -5028,7 +5031,7 @@
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A581">
+      <c r="A581" s="4">
         <v>42305.589009134601</v>
       </c>
       <c r="B581" s="1">
@@ -5036,7 +5039,7 @@
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A582">
+      <c r="A582" s="4">
         <v>42305.598325070903</v>
       </c>
       <c r="B582" s="1">
@@ -5044,7 +5047,7 @@
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A583">
+      <c r="A583" s="4">
         <v>42305.600818174898</v>
       </c>
       <c r="B583" s="1">
@@ -5052,7 +5055,7 @@
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A584">
+      <c r="A584" s="4">
         <v>42305.620478674602</v>
       </c>
       <c r="B584" s="1">
@@ -5060,7 +5063,7 @@
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A585">
+      <c r="A585" s="4">
         <v>42305.6240216773</v>
       </c>
       <c r="B585" s="1">
@@ -5068,7 +5071,7 @@
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A586">
+      <c r="A586" s="4">
         <v>42305.636945217397</v>
       </c>
       <c r="B586" s="1">
@@ -5076,7 +5079,7 @@
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A587">
+      <c r="A587" s="4">
         <v>42305.662208535403</v>
       </c>
       <c r="B587" s="1">
@@ -5084,7 +5087,7 @@
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A588">
+      <c r="A588" s="4">
         <v>42305.665569962701</v>
       </c>
       <c r="B588" s="1">
@@ -5092,7 +5095,7 @@
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A589">
+      <c r="A589" s="4">
         <v>42305.679576570503</v>
       </c>
       <c r="B589" s="1">
@@ -5100,7 +5103,7 @@
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A590">
+      <c r="A590" s="4">
         <v>42305.692697960803</v>
       </c>
       <c r="B590" s="1">
@@ -5108,7 +5111,7 @@
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A591">
+      <c r="A591" s="4">
         <v>42305.699586297596</v>
       </c>
       <c r="B591" s="1">
@@ -5116,7 +5119,7 @@
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A592">
+      <c r="A592" s="4">
         <v>42305.706151213999</v>
       </c>
       <c r="B592" s="1">
@@ -5124,7 +5127,7 @@
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A593">
+      <c r="A593" s="4">
         <v>42305.711734730503</v>
       </c>
       <c r="B593" s="1">
@@ -5132,7 +5135,7 @@
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A594">
+      <c r="A594" s="4">
         <v>42305.726563156</v>
       </c>
       <c r="B594" s="1">
@@ -5140,7 +5143,7 @@
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A595">
+      <c r="A595" s="4">
         <v>42305.728134199497</v>
       </c>
       <c r="B595" s="1">
@@ -5148,7 +5151,7 @@
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A596">
+      <c r="A596" s="4">
         <v>42305.753293907801</v>
       </c>
       <c r="B596" s="1">
@@ -5156,7 +5159,7 @@
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A597">
+      <c r="A597" s="4">
         <v>42305.753685831602</v>
       </c>
       <c r="B597" s="1">
@@ -5164,7 +5167,7 @@
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A598">
+      <c r="A598" s="4">
         <v>42305.754828853103</v>
       </c>
       <c r="B598" s="1">
@@ -5172,7 +5175,7 @@
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A599">
+      <c r="A599" s="4">
         <v>42305.769457356299</v>
       </c>
       <c r="B599" s="1">
@@ -5180,7 +5183,7 @@
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A600">
+      <c r="A600" s="4">
         <v>42305.777714686097</v>
       </c>
       <c r="B600" s="1">
@@ -5188,7 +5191,7 @@
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A601">
+      <c r="A601" s="4">
         <v>42305.7839209128</v>
       </c>
       <c r="B601" s="1">
@@ -5196,7 +5199,7 @@
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A602">
+      <c r="A602" s="4">
         <v>42305.785772554504</v>
       </c>
       <c r="B602" s="1">
@@ -5204,7 +5207,7 @@
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A603">
+      <c r="A603" s="4">
         <v>42305.800143342</v>
       </c>
       <c r="B603" s="1">
@@ -5212,7 +5215,7 @@
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A604">
+      <c r="A604" s="4">
         <v>42305.810385669502</v>
       </c>
       <c r="B604" s="1">
@@ -5220,7 +5223,7 @@
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A605">
+      <c r="A605" s="4">
         <v>42305.815530277003</v>
       </c>
       <c r="B605" s="1">
@@ -5228,7 +5231,7 @@
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A606">
+      <c r="A606" s="4">
         <v>42305.8197106769</v>
       </c>
       <c r="B606" s="1">
@@ -5236,7 +5239,7 @@
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A607">
+      <c r="A607" s="4">
         <v>42305.829539641498</v>
       </c>
       <c r="B607" s="1">
@@ -5244,7 +5247,7 @@
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A608">
+      <c r="A608" s="4">
         <v>42305.8569717071</v>
       </c>
       <c r="B608" s="1">
@@ -5252,7 +5255,7 @@
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A609">
+      <c r="A609" s="4">
         <v>42305.889508342698</v>
       </c>
       <c r="B609" s="1">
@@ -5260,7 +5263,7 @@
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A610">
+      <c r="A610" s="4">
         <v>42305.908016940703</v>
       </c>
       <c r="B610" s="1">
@@ -5268,7 +5271,7 @@
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A611">
+      <c r="A611" s="4">
         <v>42305.913112765498</v>
       </c>
       <c r="B611" s="1">
@@ -5276,7 +5279,7 @@
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A612">
+      <c r="A612" s="4">
         <v>42305.922682105302</v>
       </c>
       <c r="B612" s="1">
@@ -5284,7 +5287,7 @@
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A613">
+      <c r="A613" s="4">
         <v>42305.931413692502</v>
       </c>
       <c r="B613" s="1">
@@ -5292,7 +5295,7 @@
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A614">
+      <c r="A614" s="4">
         <v>42305.9341326004</v>
       </c>
       <c r="B614" s="1">
@@ -5300,7 +5303,7 @@
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A615">
+      <c r="A615" s="4">
         <v>42305.942466610599</v>
       </c>
       <c r="B615" s="1">
@@ -5308,7 +5311,7 @@
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A616">
+      <c r="A616" s="4">
         <v>42305.954972811101</v>
       </c>
       <c r="B616" s="1">
@@ -5316,7 +5319,7 @@
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A617">
+      <c r="A617" s="4">
         <v>42305.960420349897</v>
       </c>
       <c r="B617" s="1">
@@ -5324,7 +5327,7 @@
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A618">
+      <c r="A618" s="4">
         <v>42305.9827614569</v>
       </c>
       <c r="B618" s="1">
@@ -5332,7 +5335,7 @@
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A619">
+      <c r="A619" s="4">
         <v>42305.983602022097</v>
       </c>
       <c r="B619" s="1">
@@ -5340,7 +5343,7 @@
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A620">
+      <c r="A620" s="4">
         <v>42305.985548518998</v>
       </c>
       <c r="B620" s="1">
@@ -5348,7 +5351,7 @@
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A621">
+      <c r="A621" s="4">
         <v>42305.988715914602</v>
       </c>
       <c r="B621" s="1">
@@ -5356,7 +5359,7 @@
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A622">
+      <c r="A622" s="4">
         <v>42305.992234730802</v>
       </c>
       <c r="B622" s="1">
@@ -5364,7 +5367,7 @@
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A623">
+      <c r="A623" s="4">
         <v>42306.005903813297</v>
       </c>
       <c r="B623" s="1">
@@ -5372,7 +5375,7 @@
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A624">
+      <c r="A624" s="4">
         <v>42306.0080184744</v>
       </c>
       <c r="B624" s="1">
@@ -5380,7 +5383,7 @@
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A625">
+      <c r="A625" s="4">
         <v>42306.008908483498</v>
       </c>
       <c r="B625" s="1">
@@ -5388,7 +5391,7 @@
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A626">
+      <c r="A626" s="4">
         <v>42306.021846757198</v>
       </c>
       <c r="B626" s="1">
@@ -5396,7 +5399,7 @@
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A627">
+      <c r="A627" s="4">
         <v>42306.039234843702</v>
       </c>
       <c r="B627" s="1">
@@ -5404,7 +5407,7 @@
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A628">
+      <c r="A628" s="4">
         <v>42306.054808322602</v>
       </c>
       <c r="B628" s="1">
@@ -5412,7 +5415,7 @@
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A629">
+      <c r="A629" s="4">
         <v>42306.062403686898</v>
       </c>
       <c r="B629" s="1">
@@ -5420,7 +5423,7 @@
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A630">
+      <c r="A630" s="4">
         <v>42306.067252343397</v>
       </c>
       <c r="B630" s="1">
@@ -5428,7 +5431,7 @@
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A631">
+      <c r="A631" s="4">
         <v>42306.077069242703</v>
       </c>
       <c r="B631" s="1">
@@ -5436,7 +5439,7 @@
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A632">
+      <c r="A632" s="4">
         <v>42306.098946853701</v>
       </c>
       <c r="B632" s="1">
@@ -5444,7 +5447,7 @@
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A633">
+      <c r="A633" s="4">
         <v>42306.128756395003</v>
       </c>
       <c r="B633" s="1">
@@ -5452,7 +5455,7 @@
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A634">
+      <c r="A634" s="4">
         <v>42306.131565985801</v>
       </c>
       <c r="B634" s="1">
@@ -5460,7 +5463,7 @@
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A635">
+      <c r="A635" s="4">
         <v>42306.1379815041</v>
       </c>
       <c r="B635" s="1">
@@ -5468,7 +5471,7 @@
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A636">
+      <c r="A636" s="4">
         <v>42306.162048430997</v>
       </c>
       <c r="B636" s="1">
@@ -5476,7 +5479,7 @@
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A637">
+      <c r="A637" s="4">
         <v>42306.184441463898</v>
       </c>
       <c r="B637" s="1">
@@ -5484,7 +5487,7 @@
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A638">
+      <c r="A638" s="4">
         <v>42306.191120187897</v>
       </c>
       <c r="B638" s="1">
@@ -5492,7 +5495,7 @@
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A639">
+      <c r="A639" s="4">
         <v>42306.193160715702</v>
       </c>
       <c r="B639" s="1">
@@ -5500,7 +5503,7 @@
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A640">
+      <c r="A640" s="4">
         <v>42306.207331818398</v>
       </c>
       <c r="B640" s="1">
@@ -5508,7 +5511,7 @@
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A641">
+      <c r="A641" s="4">
         <v>42306.210884716304</v>
       </c>
       <c r="B641" s="1">
@@ -5516,7 +5519,7 @@
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A642">
+      <c r="A642" s="4">
         <v>42306.232989732998</v>
       </c>
       <c r="B642" s="1">
@@ -5524,7 +5527,7 @@
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A643">
+      <c r="A643" s="4">
         <v>42306.233238219203</v>
       </c>
       <c r="B643" s="1">
@@ -5532,7 +5535,7 @@
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A644">
+      <c r="A644" s="4">
         <v>42306.245336891603</v>
       </c>
       <c r="B644" s="1">
@@ -5540,7 +5543,7 @@
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A645">
+      <c r="A645" s="4">
         <v>42306.2713761782</v>
       </c>
       <c r="B645" s="1">
@@ -5548,7 +5551,7 @@
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A646">
+      <c r="A646" s="4">
         <v>42306.281883387797</v>
       </c>
       <c r="B646" s="1">
@@ -5556,7 +5559,7 @@
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A647">
+      <c r="A647" s="4">
         <v>42306.298639553301</v>
       </c>
       <c r="B647" s="1">
@@ -5564,7 +5567,7 @@
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A648">
+      <c r="A648" s="4">
         <v>42306.3209509511</v>
       </c>
       <c r="B648" s="1">
@@ -5572,7 +5575,7 @@
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A649">
+      <c r="A649" s="4">
         <v>42306.3247371826</v>
       </c>
       <c r="B649" s="1">
@@ -5580,7 +5583,7 @@
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A650">
+      <c r="A650" s="4">
         <v>42306.325906639802</v>
       </c>
       <c r="B650" s="1">
@@ -5588,7 +5591,7 @@
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A651">
+      <c r="A651" s="4">
         <v>42306.3309958475</v>
       </c>
       <c r="B651" s="1">
@@ -5596,7 +5599,7 @@
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A652">
+      <c r="A652" s="4">
         <v>42306.335753169202</v>
       </c>
       <c r="B652" s="1">
@@ -5604,7 +5607,7 @@
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A653">
+      <c r="A653" s="4">
         <v>42306.342871072302</v>
       </c>
       <c r="B653" s="1">
@@ -5612,7 +5615,7 @@
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A654">
+      <c r="A654" s="4">
         <v>42306.368197342999</v>
       </c>
       <c r="B654" s="1">
@@ -5620,7 +5623,7 @@
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A655">
+      <c r="A655" s="4">
         <v>42306.369617135002</v>
       </c>
       <c r="B655" s="1">
@@ -5628,7 +5631,7 @@
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A656">
+      <c r="A656" s="4">
         <v>42306.370049669204</v>
       </c>
       <c r="B656" s="1">
@@ -5636,7 +5639,7 @@
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A657">
+      <c r="A657" s="4">
         <v>42306.375608743103</v>
       </c>
       <c r="B657" s="1">
@@ -5644,7 +5647,7 @@
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A658">
+      <c r="A658" s="4">
         <v>42306.379943207001</v>
       </c>
       <c r="B658" s="1">
@@ -5652,7 +5655,7 @@
       </c>
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A659">
+      <c r="A659" s="4">
         <v>42306.3850885875</v>
       </c>
       <c r="B659" s="1">
@@ -5660,7 +5663,7 @@
       </c>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A660">
+      <c r="A660" s="4">
         <v>42306.390280515501</v>
       </c>
       <c r="B660" s="1">
@@ -5668,7 +5671,7 @@
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A661">
+      <c r="A661" s="4">
         <v>42306.393969256198</v>
       </c>
       <c r="B661" s="1">
@@ -5676,7 +5679,7 @@
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A662">
+      <c r="A662" s="4">
         <v>42306.412820003497</v>
       </c>
       <c r="B662" s="1">
@@ -5684,7 +5687,7 @@
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A663">
+      <c r="A663" s="4">
         <v>42306.418839867998</v>
       </c>
       <c r="B663" s="1">
@@ -5692,7 +5695,7 @@
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A664">
+      <c r="A664" s="4">
         <v>42306.434216311602</v>
       </c>
       <c r="B664" s="1">
@@ -5700,7 +5703,7 @@
       </c>
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A665">
+      <c r="A665" s="4">
         <v>42306.438540433199</v>
       </c>
       <c r="B665" s="1">
@@ -5708,7 +5711,7 @@
       </c>
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A666">
+      <c r="A666" s="4">
         <v>42306.442129503703</v>
       </c>
       <c r="B666" s="1">
@@ -5716,7 +5719,7 @@
       </c>
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A667">
+      <c r="A667" s="4">
         <v>42306.468832022401</v>
       </c>
       <c r="B667" s="1">
@@ -5724,7 +5727,7 @@
       </c>
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A668">
+      <c r="A668" s="4">
         <v>42306.469182311499</v>
       </c>
       <c r="B668" s="1">
@@ -5732,7 +5735,7 @@
       </c>
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A669">
+      <c r="A669" s="4">
         <v>42306.4867411374</v>
       </c>
       <c r="B669" s="1">
@@ -5740,7 +5743,7 @@
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A670">
+      <c r="A670" s="4">
         <v>42306.487810044302</v>
       </c>
       <c r="B670" s="1">
@@ -5748,7 +5751,7 @@
       </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A671">
+      <c r="A671" s="4">
         <v>42306.489170445901</v>
       </c>
       <c r="B671" s="1">
@@ -5756,7 +5759,7 @@
       </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A672">
+      <c r="A672" s="4">
         <v>42306.490710951301</v>
       </c>
       <c r="B672" s="1">
@@ -5764,7 +5767,7 @@
       </c>
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A673">
+      <c r="A673" s="4">
         <v>42306.517226367199</v>
       </c>
       <c r="B673" s="1">
@@ -5772,7 +5775,7 @@
       </c>
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A674">
+      <c r="A674" s="4">
         <v>42306.5255324471</v>
       </c>
       <c r="B674" s="1">
@@ -5780,7 +5783,7 @@
       </c>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A675">
+      <c r="A675" s="4">
         <v>42306.538042507898</v>
       </c>
       <c r="B675" s="1">
@@ -5788,7 +5791,7 @@
       </c>
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A676">
+      <c r="A676" s="4">
         <v>42306.539833110699</v>
       </c>
       <c r="B676" s="1">
@@ -5796,7 +5799,7 @@
       </c>
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A677">
+      <c r="A677" s="4">
         <v>42306.540702588798</v>
       </c>
       <c r="B677" s="1">
@@ -5804,7 +5807,7 @@
       </c>
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A678">
+      <c r="A678" s="4">
         <v>42306.561645245099</v>
       </c>
       <c r="B678" s="1">
@@ -5812,7 +5815,7 @@
       </c>
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A679">
+      <c r="A679" s="4">
         <v>42306.574646904497</v>
       </c>
       <c r="B679" s="1">
@@ -5820,7 +5823,7 @@
       </c>
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A680">
+      <c r="A680" s="4">
         <v>42306.588120670101</v>
       </c>
       <c r="B680" s="1">
@@ -5828,7 +5831,7 @@
       </c>
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A681">
+      <c r="A681" s="4">
         <v>42306.591464523401</v>
       </c>
       <c r="B681" s="1">
@@ -5836,7 +5839,7 @@
       </c>
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A682">
+      <c r="A682" s="4">
         <v>42306.597124631902</v>
       </c>
       <c r="B682" s="1">
@@ -5844,7 +5847,7 @@
       </c>
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A683">
+      <c r="A683" s="4">
         <v>42306.6069984071</v>
       </c>
       <c r="B683" s="1">
@@ -5852,7 +5855,7 @@
       </c>
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A684">
+      <c r="A684" s="4">
         <v>42306.622774937598</v>
       </c>
       <c r="B684" s="1">
@@ -5860,7 +5863,7 @@
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A685">
+      <c r="A685" s="4">
         <v>42306.628810168899</v>
       </c>
       <c r="B685" s="1">
@@ -5868,7 +5871,7 @@
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A686">
+      <c r="A686" s="4">
         <v>42306.630607872998</v>
       </c>
       <c r="B686" s="1">
@@ -5876,7 +5879,7 @@
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A687">
+      <c r="A687" s="4">
         <v>42306.6424869767</v>
       </c>
       <c r="B687" s="1">
@@ -5884,7 +5887,7 @@
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A688">
+      <c r="A688" s="4">
         <v>42306.650870598503</v>
       </c>
       <c r="B688" s="1">
@@ -5892,7 +5895,7 @@
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A689">
+      <c r="A689" s="4">
         <v>42306.683994176899</v>
       </c>
       <c r="B689" s="1">
@@ -5900,7 +5903,7 @@
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A690">
+      <c r="A690" s="4">
         <v>42306.684725400199</v>
       </c>
       <c r="B690" s="1">
@@ -5908,7 +5911,7 @@
       </c>
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A691">
+      <c r="A691" s="4">
         <v>42306.684970053902</v>
       </c>
       <c r="B691" s="1">
@@ -5916,7 +5919,7 @@
       </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A692">
+      <c r="A692" s="4">
         <v>42306.689066327403</v>
       </c>
       <c r="B692" s="1">
@@ -5924,7 +5927,7 @@
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A693">
+      <c r="A693" s="4">
         <v>42306.726421728599</v>
       </c>
       <c r="B693" s="1">
@@ -5932,7 +5935,7 @@
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A694">
+      <c r="A694" s="4">
         <v>42306.744412841901</v>
       </c>
       <c r="B694" s="1">
@@ -5940,7 +5943,7 @@
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A695">
+      <c r="A695" s="4">
         <v>42306.748225192401</v>
       </c>
       <c r="B695" s="1">
@@ -5948,7 +5951,7 @@
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A696">
+      <c r="A696" s="4">
         <v>42306.755086828103</v>
       </c>
       <c r="B696" s="1">
@@ -5956,7 +5959,7 @@
       </c>
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A697">
+      <c r="A697" s="4">
         <v>42306.757985001597</v>
       </c>
       <c r="B697" s="1">
@@ -5964,7 +5967,7 @@
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A698">
+      <c r="A698" s="4">
         <v>42306.760493756599</v>
       </c>
       <c r="B698" s="1">
@@ -5972,7 +5975,7 @@
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A699">
+      <c r="A699" s="4">
         <v>42306.7641567928</v>
       </c>
       <c r="B699" s="1">
@@ -5980,7 +5983,7 @@
       </c>
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A700">
+      <c r="A700" s="4">
         <v>42306.783869264902</v>
       </c>
       <c r="B700" s="1">
@@ -5988,7 +5991,7 @@
       </c>
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A701">
+      <c r="A701" s="4">
         <v>42306.791947524704</v>
       </c>
       <c r="B701" s="1">
@@ -5996,7 +5999,7 @@
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A702">
+      <c r="A702" s="4">
         <v>42306.792482932702</v>
       </c>
       <c r="B702" s="1">
@@ -6004,7 +6007,7 @@
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A703">
+      <c r="A703" s="4">
         <v>42306.808112081497</v>
       </c>
       <c r="B703" s="1">
@@ -6012,7 +6015,7 @@
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A704">
+      <c r="A704" s="4">
         <v>42306.813243538701</v>
       </c>
       <c r="B704" s="1">
@@ -6020,7 +6023,7 @@
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A705">
+      <c r="A705" s="4">
         <v>42306.815160708204</v>
       </c>
       <c r="B705" s="1">
@@ -6028,7 +6031,7 @@
       </c>
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A706">
+      <c r="A706" s="4">
         <v>42306.849557912101</v>
       </c>
       <c r="B706" s="1">
@@ -6036,7 +6039,7 @@
       </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A707">
+      <c r="A707" s="4">
         <v>42306.855338771202</v>
       </c>
       <c r="B707" s="1">
@@ -6044,7 +6047,7 @@
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A708">
+      <c r="A708" s="4">
         <v>42306.872891985899</v>
       </c>
       <c r="B708" s="1">
@@ -6052,7 +6055,7 @@
       </c>
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A709">
+      <c r="A709" s="4">
         <v>42306.884894713403</v>
       </c>
       <c r="B709" s="1">
@@ -6060,7 +6063,7 @@
       </c>
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A710">
+      <c r="A710" s="4">
         <v>42306.899362661199</v>
       </c>
       <c r="B710" s="1">
@@ -6068,7 +6071,7 @@
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A711">
+      <c r="A711" s="4">
         <v>42306.900050014498</v>
       </c>
       <c r="B711" s="1">
@@ -6076,7 +6079,7 @@
       </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A712">
+      <c r="A712" s="4">
         <v>42306.908013660999</v>
       </c>
       <c r="B712" s="1">
@@ -6084,7 +6087,7 @@
       </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A713">
+      <c r="A713" s="4">
         <v>42306.916632991197</v>
       </c>
       <c r="B713" s="1">
@@ -6092,7 +6095,7 @@
       </c>
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A714">
+      <c r="A714" s="4">
         <v>42306.923782256701</v>
       </c>
       <c r="B714" s="1">
@@ -6100,7 +6103,7 @@
       </c>
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A715">
+      <c r="A715" s="4">
         <v>42306.950303213998</v>
       </c>
       <c r="B715" s="1">
@@ -6108,7 +6111,7 @@
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A716">
+      <c r="A716" s="4">
         <v>42306.971553961099</v>
       </c>
       <c r="B716" s="1">
@@ -6116,7 +6119,7 @@
       </c>
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A717">
+      <c r="A717" s="4">
         <v>42306.993583028401</v>
       </c>
       <c r="B717" s="1">
@@ -6124,7 +6127,7 @@
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A718">
+      <c r="A718" s="4">
         <v>42306.9952339421</v>
       </c>
       <c r="B718" s="1">
@@ -6132,7 +6135,7 @@
       </c>
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A719">
+      <c r="A719" s="4">
         <v>42307.003839065001</v>
       </c>
       <c r="B719" s="1">
@@ -6140,7 +6143,7 @@
       </c>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A720">
+      <c r="A720" s="4">
         <v>42307.009426222998</v>
       </c>
       <c r="B720" s="1">
@@ -6148,7 +6151,7 @@
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A721">
+      <c r="A721" s="4">
         <v>42307.022652126303</v>
       </c>
       <c r="B721" s="1">
@@ -6156,7 +6159,7 @@
       </c>
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A722">
+      <c r="A722" s="4">
         <v>42307.036315965503</v>
       </c>
       <c r="B722" s="1">
@@ -6164,7 +6167,7 @@
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A723">
+      <c r="A723" s="4">
         <v>42307.055826741198</v>
       </c>
       <c r="B723" s="1">
@@ -6172,7 +6175,7 @@
       </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A724">
+      <c r="A724" s="4">
         <v>42307.069501830701</v>
       </c>
       <c r="B724" s="1">
@@ -6180,7 +6183,7 @@
       </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A725">
+      <c r="A725" s="4">
         <v>42307.096576468597</v>
       </c>
       <c r="B725" s="1">
@@ -6188,7 +6191,7 @@
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A726">
+      <c r="A726" s="4">
         <v>42307.097003829302</v>
       </c>
       <c r="B726" s="1">
@@ -6196,7 +6199,7 @@
       </c>
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A727">
+      <c r="A727" s="4">
         <v>42307.097742703401</v>
       </c>
       <c r="B727" s="1">
@@ -6204,7 +6207,7 @@
       </c>
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A728">
+      <c r="A728" s="4">
         <v>42307.104111511202</v>
       </c>
       <c r="B728" s="1">
@@ -6212,7 +6215,7 @@
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A729">
+      <c r="A729" s="4">
         <v>42307.113399689399</v>
       </c>
       <c r="B729" s="1">
@@ -6220,7 +6223,7 @@
       </c>
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A730">
+      <c r="A730" s="4">
         <v>42307.1180509892</v>
       </c>
       <c r="B730" s="1">
@@ -6228,7 +6231,7 @@
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A731">
+      <c r="A731" s="4">
         <v>42307.122105530201</v>
       </c>
       <c r="B731" s="1">
@@ -6236,7 +6239,7 @@
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A732">
+      <c r="A732" s="4">
         <v>42307.122783323503</v>
       </c>
       <c r="B732" s="1">
@@ -6244,7 +6247,7 @@
       </c>
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A733">
+      <c r="A733" s="4">
         <v>42307.130896572999</v>
       </c>
       <c r="B733" s="1">
@@ -6252,7 +6255,7 @@
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A734">
+      <c r="A734" s="4">
         <v>42307.143307969498</v>
       </c>
       <c r="B734" s="1">
@@ -6260,7 +6263,7 @@
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A735">
+      <c r="A735" s="4">
         <v>42307.146686435401</v>
       </c>
       <c r="B735" s="1">
@@ -6268,7 +6271,7 @@
       </c>
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A736">
+      <c r="A736" s="4">
         <v>42307.1613332204</v>
       </c>
       <c r="B736" s="1">
@@ -6276,7 +6279,7 @@
       </c>
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A737">
+      <c r="A737" s="4">
         <v>42307.167543410003</v>
       </c>
       <c r="B737" s="1">
@@ -6284,7 +6287,7 @@
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A738">
+      <c r="A738" s="4">
         <v>42307.173872096399</v>
       </c>
       <c r="B738" s="1">
@@ -6292,7 +6295,7 @@
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A739">
+      <c r="A739" s="4">
         <v>42307.175115947597</v>
       </c>
       <c r="B739" s="1">
@@ -6300,7 +6303,7 @@
       </c>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A740">
+      <c r="A740" s="4">
         <v>42307.182299620697</v>
       </c>
       <c r="B740" s="1">
@@ -6308,7 +6311,7 @@
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A741">
+      <c r="A741" s="4">
         <v>42307.188154538599</v>
       </c>
       <c r="B741" s="1">
@@ -6316,7 +6319,7 @@
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A742">
+      <c r="A742" s="4">
         <v>42307.200628124199</v>
       </c>
       <c r="B742" s="1">
@@ -6324,7 +6327,7 @@
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A743">
+      <c r="A743" s="4">
         <v>42307.209466250097</v>
       </c>
       <c r="B743" s="1">
@@ -6332,7 +6335,7 @@
       </c>
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A744">
+      <c r="A744" s="4">
         <v>42307.229381452496</v>
       </c>
       <c r="B744" s="1">
@@ -6340,7 +6343,7 @@
       </c>
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A745">
+      <c r="A745" s="4">
         <v>42307.274431459802</v>
       </c>
       <c r="B745" s="1">
@@ -6348,7 +6351,7 @@
       </c>
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A746">
+      <c r="A746" s="4">
         <v>42307.296929201199</v>
       </c>
       <c r="B746" s="1">
@@ -6356,7 +6359,7 @@
       </c>
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A747">
+      <c r="A747" s="4">
         <v>42307.298041810398</v>
       </c>
       <c r="B747" s="1">
@@ -6364,7 +6367,7 @@
       </c>
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A748">
+      <c r="A748" s="4">
         <v>42307.298421669002</v>
       </c>
       <c r="B748" s="1">
@@ -6372,7 +6375,7 @@
       </c>
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A749">
+      <c r="A749" s="4">
         <v>42307.3109613505</v>
       </c>
       <c r="B749" s="1">
@@ -6380,7 +6383,7 @@
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A750">
+      <c r="A750" s="4">
         <v>42307.313646493298</v>
       </c>
       <c r="B750" s="1">
@@ -6388,7 +6391,7 @@
       </c>
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A751">
+      <c r="A751" s="4">
         <v>42307.350038869699</v>
       </c>
       <c r="B751" s="1">
@@ -6396,7 +6399,7 @@
       </c>
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A752">
+      <c r="A752" s="4">
         <v>42307.352248227697</v>
       </c>
       <c r="B752" s="1">
@@ -6404,7 +6407,7 @@
       </c>
     </row>
     <row r="753" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A753">
+      <c r="A753" s="4">
         <v>42307.355320944996</v>
       </c>
       <c r="B753" s="1">
@@ -6412,7 +6415,7 @@
       </c>
     </row>
     <row r="754" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A754">
+      <c r="A754" s="4">
         <v>42307.364110078597</v>
       </c>
       <c r="B754" s="1">
@@ -6420,7 +6423,7 @@
       </c>
     </row>
     <row r="755" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A755">
+      <c r="A755" s="4">
         <v>42307.364268100799</v>
       </c>
       <c r="B755" s="1">
@@ -6428,7 +6431,7 @@
       </c>
     </row>
     <row r="756" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A756">
+      <c r="A756" s="4">
         <v>42307.369643718201</v>
       </c>
       <c r="B756" s="1">
@@ -6436,7 +6439,7 @@
       </c>
     </row>
     <row r="757" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A757">
+      <c r="A757" s="4">
         <v>42307.375576480699</v>
       </c>
       <c r="B757" s="1">
@@ -6444,7 +6447,7 @@
       </c>
     </row>
     <row r="758" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A758">
+      <c r="A758" s="4">
         <v>42307.376640456299</v>
       </c>
       <c r="B758" s="1">
@@ -6452,7 +6455,7 @@
       </c>
     </row>
     <row r="759" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A759">
+      <c r="A759" s="4">
         <v>42307.387972594202</v>
       </c>
       <c r="B759" s="1">
@@ -6460,7 +6463,7 @@
       </c>
     </row>
     <row r="760" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A760">
+      <c r="A760" s="4">
         <v>42307.393237076903</v>
       </c>
       <c r="B760" s="1">
@@ -6468,7 +6471,7 @@
       </c>
     </row>
     <row r="761" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A761">
+      <c r="A761" s="4">
         <v>42307.393570075998</v>
       </c>
       <c r="B761" s="1">
@@ -6476,7 +6479,7 @@
       </c>
     </row>
     <row r="762" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A762">
+      <c r="A762" s="4">
         <v>42307.400552061903</v>
       </c>
       <c r="B762" s="1">
@@ -6484,7 +6487,7 @@
       </c>
     </row>
     <row r="763" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A763">
+      <c r="A763" s="4">
         <v>42307.403783937603</v>
       </c>
       <c r="B763" s="1">
@@ -6492,7 +6495,7 @@
       </c>
     </row>
     <row r="764" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A764">
+      <c r="A764" s="4">
         <v>42307.409201557603</v>
       </c>
       <c r="B764" s="1">
@@ -6500,7 +6503,7 @@
       </c>
     </row>
     <row r="765" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A765">
+      <c r="A765" s="4">
         <v>42307.413519881702</v>
       </c>
       <c r="B765" s="1">
@@ -6508,7 +6511,7 @@
       </c>
     </row>
     <row r="766" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A766">
+      <c r="A766" s="4">
         <v>42307.414567899097</v>
       </c>
       <c r="B766" s="1">
@@ -6516,7 +6519,7 @@
       </c>
     </row>
     <row r="767" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A767">
+      <c r="A767" s="4">
         <v>42307.423883057701</v>
       </c>
       <c r="B767" s="1">
@@ -6524,7 +6527,7 @@
       </c>
     </row>
     <row r="768" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A768">
+      <c r="A768" s="4">
         <v>42307.426720089898</v>
       </c>
       <c r="B768" s="1">
@@ -6532,7 +6535,7 @@
       </c>
     </row>
     <row r="769" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A769">
+      <c r="A769" s="4">
         <v>42307.427319531002</v>
       </c>
       <c r="B769" s="1">
@@ -6540,7 +6543,7 @@
       </c>
     </row>
     <row r="770" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A770">
+      <c r="A770" s="4">
         <v>42307.435212271303</v>
       </c>
       <c r="B770" s="1">
@@ -6548,7 +6551,7 @@
       </c>
     </row>
     <row r="771" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A771">
+      <c r="A771" s="4">
         <v>42307.440007367397</v>
       </c>
       <c r="B771" s="1">
@@ -6556,7 +6559,7 @@
       </c>
     </row>
     <row r="772" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A772">
+      <c r="A772" s="4">
         <v>42307.440620349902</v>
       </c>
       <c r="B772" s="1">
@@ -6564,7 +6567,7 @@
       </c>
     </row>
     <row r="773" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A773">
+      <c r="A773" s="4">
         <v>42307.445107262</v>
       </c>
       <c r="B773" s="1">
@@ -6572,7 +6575,7 @@
       </c>
     </row>
     <row r="774" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A774">
+      <c r="A774" s="4">
         <v>42307.464377085897</v>
       </c>
       <c r="B774" s="1">
@@ -6580,7 +6583,7 @@
       </c>
     </row>
     <row r="775" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A775">
+      <c r="A775" s="4">
         <v>42307.464866356197</v>
       </c>
       <c r="B775" s="1">
@@ -6588,7 +6591,7 @@
       </c>
     </row>
     <row r="776" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A776">
+      <c r="A776" s="4">
         <v>42307.467919934898</v>
       </c>
       <c r="B776" s="1">
@@ -6596,7 +6599,7 @@
       </c>
     </row>
     <row r="777" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A777">
+      <c r="A777" s="4">
         <v>42307.468857865199</v>
       </c>
       <c r="B777" s="1">
@@ -6604,7 +6607,7 @@
       </c>
     </row>
     <row r="778" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A778">
+      <c r="A778" s="4">
         <v>42307.476411683303</v>
       </c>
       <c r="B778" s="1">
@@ -6612,7 +6615,7 @@
       </c>
     </row>
     <row r="779" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A779">
+      <c r="A779" s="4">
         <v>42307.479666343803</v>
       </c>
       <c r="B779" s="1">
@@ -6620,7 +6623,7 @@
       </c>
     </row>
     <row r="780" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A780">
+      <c r="A780" s="4">
         <v>42307.480588902603</v>
       </c>
       <c r="B780" s="1">
@@ -6628,7 +6631,7 @@
       </c>
     </row>
     <row r="781" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A781">
+      <c r="A781" s="4">
         <v>42307.492982035903</v>
       </c>
       <c r="B781" s="1">
@@ -6636,7 +6639,7 @@
       </c>
     </row>
     <row r="782" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A782">
+      <c r="A782" s="4">
         <v>42307.4985043739</v>
       </c>
       <c r="B782" s="1">
@@ -6644,7 +6647,7 @@
       </c>
     </row>
     <row r="783" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A783">
+      <c r="A783" s="4">
         <v>42307.513068704196</v>
       </c>
       <c r="B783" s="1">
@@ -6652,7 +6655,7 @@
       </c>
     </row>
     <row r="784" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A784">
+      <c r="A784" s="4">
         <v>42307.515825754403</v>
       </c>
       <c r="B784" s="1">
@@ -6660,7 +6663,7 @@
       </c>
     </row>
     <row r="785" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A785">
+      <c r="A785" s="4">
         <v>42307.516270381799</v>
       </c>
       <c r="B785" s="1">
@@ -6668,7 +6671,7 @@
       </c>
     </row>
     <row r="786" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A786">
+      <c r="A786" s="4">
         <v>42307.518541509802</v>
       </c>
       <c r="B786" s="1">
@@ -6676,7 +6679,7 @@
       </c>
     </row>
     <row r="787" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A787">
+      <c r="A787" s="4">
         <v>42307.532437024798</v>
       </c>
       <c r="B787" s="1">
@@ -6684,7 +6687,7 @@
       </c>
     </row>
     <row r="788" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A788">
+      <c r="A788" s="4">
         <v>42307.579771761899</v>
       </c>
       <c r="B788" s="1">
@@ -6692,7 +6695,7 @@
       </c>
     </row>
     <row r="789" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A789">
+      <c r="A789" s="4">
         <v>42307.5864249351</v>
       </c>
       <c r="B789" s="1">
@@ -6700,7 +6703,7 @@
       </c>
     </row>
     <row r="790" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A790">
+      <c r="A790" s="4">
         <v>42307.592505475201</v>
       </c>
       <c r="B790" s="1">
@@ -6708,7 +6711,7 @@
       </c>
     </row>
     <row r="791" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A791">
+      <c r="A791" s="4">
         <v>42307.604242244903</v>
       </c>
       <c r="B791" s="1">
@@ -6716,7 +6719,7 @@
       </c>
     </row>
     <row r="792" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A792">
+      <c r="A792" s="4">
         <v>42307.613289913701</v>
       </c>
       <c r="B792" s="1">
@@ -6724,7 +6727,7 @@
       </c>
     </row>
     <row r="793" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A793">
+      <c r="A793" s="4">
         <v>42307.618533143599</v>
       </c>
       <c r="B793" s="1">
@@ -6732,7 +6735,7 @@
       </c>
     </row>
     <row r="794" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A794">
+      <c r="A794" s="4">
         <v>42307.623663953498</v>
       </c>
       <c r="B794" s="1">
@@ -6740,7 +6743,7 @@
       </c>
     </row>
     <row r="795" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A795">
+      <c r="A795" s="4">
         <v>42307.631197659597</v>
       </c>
       <c r="B795" s="1">
@@ -6748,7 +6751,7 @@
       </c>
     </row>
     <row r="796" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A796">
+      <c r="A796" s="4">
         <v>42307.669827692203</v>
       </c>
       <c r="B796" s="1">
@@ -6756,7 +6759,7 @@
       </c>
     </row>
     <row r="797" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A797">
+      <c r="A797" s="4">
         <v>42307.675528504202</v>
       </c>
       <c r="B797" s="1">
@@ -6764,7 +6767,7 @@
       </c>
     </row>
     <row r="798" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A798">
+      <c r="A798" s="4">
         <v>42307.680375740303</v>
       </c>
       <c r="B798" s="1">
@@ -6772,7 +6775,7 @@
       </c>
     </row>
     <row r="799" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A799">
+      <c r="A799" s="4">
         <v>42307.6879851583</v>
       </c>
       <c r="B799" s="1">
@@ -6780,7 +6783,7 @@
       </c>
     </row>
     <row r="800" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A800">
+      <c r="A800" s="4">
         <v>42307.711160883999</v>
       </c>
       <c r="B800" s="1">
@@ -6788,7 +6791,7 @@
       </c>
     </row>
     <row r="801" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A801">
+      <c r="A801" s="4">
         <v>42307.711244227998</v>
       </c>
       <c r="B801" s="1">
@@ -6796,7 +6799,7 @@
       </c>
     </row>
     <row r="802" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A802">
+      <c r="A802" s="4">
         <v>42307.711882617099</v>
       </c>
       <c r="B802" s="1">
@@ -6804,7 +6807,7 @@
       </c>
     </row>
     <row r="803" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A803">
+      <c r="A803" s="4">
         <v>42307.738020866098</v>
       </c>
       <c r="B803" s="1">
@@ -6812,7 +6815,7 @@
       </c>
     </row>
     <row r="804" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A804">
+      <c r="A804" s="4">
         <v>42307.752640530904</v>
       </c>
       <c r="B804" s="1">
@@ -6820,7 +6823,7 @@
       </c>
     </row>
     <row r="805" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A805">
+      <c r="A805" s="4">
         <v>42307.763508493001</v>
       </c>
       <c r="B805" s="1">
@@ -6828,7 +6831,7 @@
       </c>
     </row>
     <row r="806" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A806">
+      <c r="A806" s="4">
         <v>42307.764272238099</v>
       </c>
       <c r="B806" s="1">
@@ -6836,7 +6839,7 @@
       </c>
     </row>
     <row r="807" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A807">
+      <c r="A807" s="4">
         <v>42307.776600700301</v>
       </c>
       <c r="B807" s="1">
@@ -6844,7 +6847,7 @@
       </c>
     </row>
     <row r="808" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A808">
+      <c r="A808" s="4">
         <v>42307.780433907799</v>
       </c>
       <c r="B808" s="1">
@@ -6852,7 +6855,7 @@
       </c>
     </row>
     <row r="809" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A809">
+      <c r="A809" s="4">
         <v>42307.804567256702</v>
       </c>
       <c r="B809" s="1">
@@ -6860,7 +6863,7 @@
       </c>
     </row>
     <row r="810" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A810">
+      <c r="A810" s="4">
         <v>42307.807958225603</v>
       </c>
       <c r="B810" s="1">
@@ -6868,7 +6871,7 @@
       </c>
     </row>
     <row r="811" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A811">
+      <c r="A811" s="4">
         <v>42307.820661591701</v>
       </c>
       <c r="B811" s="1">
@@ -6876,7 +6879,7 @@
       </c>
     </row>
     <row r="812" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A812">
+      <c r="A812" s="4">
         <v>42307.821770405797</v>
       </c>
       <c r="B812" s="1">
@@ -6884,7 +6887,7 @@
       </c>
     </row>
     <row r="813" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A813">
+      <c r="A813" s="4">
         <v>42307.825221514897</v>
       </c>
       <c r="B813" s="1">
@@ -6892,7 +6895,7 @@
       </c>
     </row>
     <row r="814" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A814">
+      <c r="A814" s="4">
         <v>42307.8326100743</v>
       </c>
       <c r="B814" s="1">
@@ -6900,7 +6903,7 @@
       </c>
     </row>
     <row r="815" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A815">
+      <c r="A815" s="4">
         <v>42307.845874352803</v>
       </c>
       <c r="B815" s="1">
@@ -6908,7 +6911,7 @@
       </c>
     </row>
     <row r="816" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A816">
+      <c r="A816" s="4">
         <v>42307.863458035703</v>
       </c>
       <c r="B816" s="1">
@@ -6916,7 +6919,7 @@
       </c>
     </row>
     <row r="817" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A817">
+      <c r="A817" s="4">
         <v>42307.867495696402</v>
       </c>
       <c r="B817" s="1">
@@ -6924,7 +6927,7 @@
       </c>
     </row>
     <row r="818" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A818">
+      <c r="A818" s="4">
         <v>42307.869927393702</v>
       </c>
       <c r="B818" s="1">
@@ -6932,7 +6935,7 @@
       </c>
     </row>
     <row r="819" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A819">
+      <c r="A819" s="4">
         <v>42307.881934987403</v>
       </c>
       <c r="B819" s="1">
@@ -6940,7 +6943,7 @@
       </c>
     </row>
     <row r="820" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A820">
+      <c r="A820" s="4">
         <v>42307.882442567497</v>
       </c>
       <c r="B820" s="1">
@@ -6948,7 +6951,7 @@
       </c>
     </row>
     <row r="821" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A821">
+      <c r="A821" s="4">
         <v>42307.886753883402</v>
       </c>
       <c r="B821" s="1">
@@ -6956,7 +6959,7 @@
       </c>
     </row>
     <row r="822" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A822">
+      <c r="A822" s="4">
         <v>42307.890036399796</v>
       </c>
       <c r="B822" s="1">
@@ -6964,7 +6967,7 @@
       </c>
     </row>
     <row r="823" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A823">
+      <c r="A823" s="4">
         <v>42307.893024017503</v>
       </c>
       <c r="B823" s="1">
@@ -6972,7 +6975,7 @@
       </c>
     </row>
     <row r="824" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A824">
+      <c r="A824" s="4">
         <v>42307.909254092898</v>
       </c>
       <c r="B824" s="1">
@@ -6980,7 +6983,7 @@
       </c>
     </row>
     <row r="825" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A825">
+      <c r="A825" s="4">
         <v>42307.930326230897</v>
       </c>
       <c r="B825" s="1">
@@ -6988,7 +6991,7 @@
       </c>
     </row>
     <row r="826" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A826">
+      <c r="A826" s="4">
         <v>42307.933462143097</v>
       </c>
       <c r="B826" s="1">
@@ -6996,7 +6999,7 @@
       </c>
     </row>
     <row r="827" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A827">
+      <c r="A827" s="4">
         <v>42307.956903016398</v>
       </c>
       <c r="B827" s="1">
@@ -7004,7 +7007,7 @@
       </c>
     </row>
     <row r="828" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A828">
+      <c r="A828" s="4">
         <v>42307.963718216401</v>
       </c>
       <c r="B828" s="1">
@@ -7012,7 +7015,7 @@
       </c>
     </row>
     <row r="829" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A829">
+      <c r="A829" s="4">
         <v>42307.970009198201</v>
       </c>
       <c r="B829" s="1">
@@ -7020,7 +7023,7 @@
       </c>
     </row>
     <row r="830" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A830">
+      <c r="A830" s="4">
         <v>42308.009020463003</v>
       </c>
       <c r="B830" s="1">
@@ -7028,7 +7031,7 @@
       </c>
     </row>
     <row r="831" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A831">
+      <c r="A831" s="4">
         <v>42308.0090491757</v>
       </c>
       <c r="B831" s="1">
@@ -7036,7 +7039,7 @@
       </c>
     </row>
     <row r="832" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A832">
+      <c r="A832" s="4">
         <v>42308.032129436098</v>
       </c>
       <c r="B832" s="1">
@@ -7044,7 +7047,7 @@
       </c>
     </row>
     <row r="833" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A833">
+      <c r="A833" s="4">
         <v>42308.035920855102</v>
       </c>
       <c r="B833" s="1">
@@ -7052,7 +7055,7 @@
       </c>
     </row>
     <row r="834" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A834">
+      <c r="A834" s="4">
         <v>42308.053725498998</v>
       </c>
       <c r="B834" s="1">
@@ -7060,7 +7063,7 @@
       </c>
     </row>
     <row r="835" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A835">
+      <c r="A835" s="4">
         <v>42308.065236292598</v>
       </c>
       <c r="B835" s="1">
@@ -7068,7 +7071,7 @@
       </c>
     </row>
     <row r="836" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A836">
+      <c r="A836" s="4">
         <v>42308.073381439899</v>
       </c>
       <c r="B836" s="1">
@@ -7076,7 +7079,7 @@
       </c>
     </row>
     <row r="837" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A837">
+      <c r="A837" s="4">
         <v>42308.075537260796</v>
       </c>
       <c r="B837" s="1">
@@ -7084,7 +7087,7 @@
       </c>
     </row>
     <row r="838" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A838">
+      <c r="A838" s="4">
         <v>42308.075723176102</v>
       </c>
       <c r="B838" s="1">
@@ -7092,7 +7095,7 @@
       </c>
     </row>
     <row r="839" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A839">
+      <c r="A839" s="4">
         <v>42308.079442417598</v>
       </c>
       <c r="B839" s="1">
@@ -7100,7 +7103,7 @@
       </c>
     </row>
     <row r="840" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A840">
+      <c r="A840" s="4">
         <v>42308.084843874502</v>
       </c>
       <c r="B840" s="1">
@@ -7108,7 +7111,7 @@
       </c>
     </row>
     <row r="841" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A841">
+      <c r="A841" s="4">
         <v>42308.1158128147</v>
       </c>
       <c r="B841" s="1">
@@ -7116,7 +7119,7 @@
       </c>
     </row>
     <row r="842" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A842">
+      <c r="A842" s="4">
         <v>42308.118308447301</v>
       </c>
       <c r="B842" s="1">
@@ -7124,7 +7127,7 @@
       </c>
     </row>
     <row r="843" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A843">
+      <c r="A843" s="4">
         <v>42308.140746723802</v>
       </c>
       <c r="B843" s="1">
@@ -7132,7 +7135,7 @@
       </c>
     </row>
     <row r="844" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A844">
+      <c r="A844" s="4">
         <v>42308.153906060899</v>
       </c>
       <c r="B844" s="1">
@@ -7140,7 +7143,7 @@
       </c>
     </row>
     <row r="845" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A845">
+      <c r="A845" s="4">
         <v>42308.184151610199</v>
       </c>
       <c r="B845" s="1">
@@ -7148,7 +7151,7 @@
       </c>
     </row>
     <row r="846" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A846">
+      <c r="A846" s="4">
         <v>42308.188264126002</v>
       </c>
       <c r="B846" s="1">
@@ -7156,7 +7159,7 @@
       </c>
     </row>
     <row r="847" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A847">
+      <c r="A847" s="4">
         <v>42308.211292400003</v>
       </c>
       <c r="B847" s="1">
@@ -7164,7 +7167,7 @@
       </c>
     </row>
     <row r="848" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A848">
+      <c r="A848" s="4">
         <v>42308.249378530898</v>
       </c>
       <c r="B848" s="1">
@@ -7172,7 +7175,7 @@
       </c>
     </row>
     <row r="849" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A849">
+      <c r="A849" s="4">
         <v>42308.250545859897</v>
       </c>
       <c r="B849" s="1">
@@ -7180,7 +7183,7 @@
       </c>
     </row>
     <row r="850" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A850">
+      <c r="A850" s="4">
         <v>42308.2511527284</v>
       </c>
       <c r="B850" s="1">
@@ -7188,7 +7191,7 @@
       </c>
     </row>
     <row r="851" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A851">
+      <c r="A851" s="4">
         <v>42308.264448993097</v>
       </c>
       <c r="B851" s="1">
@@ -7196,7 +7199,7 @@
       </c>
     </row>
     <row r="852" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A852">
+      <c r="A852" s="4">
         <v>42308.266628106401</v>
       </c>
       <c r="B852" s="1">
@@ -7204,7 +7207,7 @@
       </c>
     </row>
     <row r="853" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A853">
+      <c r="A853" s="4">
         <v>42308.279461126702</v>
       </c>
       <c r="B853" s="1">
@@ -7212,7 +7215,7 @@
       </c>
     </row>
     <row r="854" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A854">
+      <c r="A854" s="4">
         <v>42308.289091365703</v>
       </c>
       <c r="B854" s="1">
@@ -7220,7 +7223,7 @@
       </c>
     </row>
     <row r="855" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A855">
+      <c r="A855" s="4">
         <v>42308.300511997899</v>
       </c>
       <c r="B855" s="1">
@@ -7228,7 +7231,7 @@
       </c>
     </row>
     <row r="856" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A856">
+      <c r="A856" s="4">
         <v>42308.307544028503</v>
       </c>
       <c r="B856" s="1">
@@ -7236,7 +7239,7 @@
       </c>
     </row>
     <row r="857" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A857">
+      <c r="A857" s="4">
         <v>42308.326705548803</v>
       </c>
       <c r="B857" s="1">
@@ -7244,7 +7247,7 @@
       </c>
     </row>
     <row r="858" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A858">
+      <c r="A858" s="4">
         <v>42308.354628565801</v>
       </c>
       <c r="B858" s="1">
@@ -7252,7 +7255,7 @@
       </c>
     </row>
     <row r="859" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A859">
+      <c r="A859" s="4">
         <v>42308.358296416904</v>
       </c>
       <c r="B859" s="1">
@@ -7260,7 +7263,7 @@
       </c>
     </row>
     <row r="860" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A860">
+      <c r="A860" s="4">
         <v>42308.374343212599</v>
       </c>
       <c r="B860" s="1">
@@ -7268,7 +7271,7 @@
       </c>
     </row>
     <row r="861" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A861">
+      <c r="A861" s="4">
         <v>42308.389625997799</v>
       </c>
       <c r="B861" s="1">
@@ -7276,7 +7279,7 @@
       </c>
     </row>
     <row r="862" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A862">
+      <c r="A862" s="4">
         <v>42308.4096246095</v>
       </c>
       <c r="B862" s="1">
@@ -7284,7 +7287,7 @@
       </c>
     </row>
     <row r="863" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A863">
+      <c r="A863" s="4">
         <v>42308.410757405203</v>
       </c>
       <c r="B863" s="1">
@@ -7292,7 +7295,7 @@
       </c>
     </row>
     <row r="864" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A864">
+      <c r="A864" s="4">
         <v>42308.417110231501</v>
       </c>
       <c r="B864" s="1">
@@ -7300,7 +7303,7 @@
       </c>
     </row>
     <row r="865" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A865">
+      <c r="A865" s="4">
         <v>42308.442893786203</v>
       </c>
       <c r="B865" s="1">
@@ -7308,7 +7311,7 @@
       </c>
     </row>
     <row r="866" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A866">
+      <c r="A866" s="4">
         <v>42308.4500338176</v>
       </c>
       <c r="B866" s="1">
@@ -7316,7 +7319,7 @@
       </c>
     </row>
     <row r="867" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A867">
+      <c r="A867" s="4">
         <v>42308.460547648901</v>
       </c>
       <c r="B867" s="1">
@@ -7324,7 +7327,7 @@
       </c>
     </row>
     <row r="868" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A868">
+      <c r="A868" s="4">
         <v>42308.467665989803</v>
       </c>
       <c r="B868" s="1">
@@ -7332,7 +7335,7 @@
       </c>
     </row>
     <row r="869" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A869">
+      <c r="A869" s="4">
         <v>42308.473024396299</v>
       </c>
       <c r="B869" s="1">
@@ -7340,7 +7343,7 @@
       </c>
     </row>
     <row r="870" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A870">
+      <c r="A870" s="4">
         <v>42308.490728434001</v>
       </c>
       <c r="B870" s="1">
@@ -7348,7 +7351,7 @@
       </c>
     </row>
     <row r="871" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A871">
+      <c r="A871" s="4">
         <v>42308.493558416099</v>
       </c>
       <c r="B871" s="1">
@@ -7356,7 +7359,7 @@
       </c>
     </row>
     <row r="872" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A872">
+      <c r="A872" s="4">
         <v>42308.521117700402</v>
       </c>
       <c r="B872" s="1">
@@ -7364,7 +7367,7 @@
       </c>
     </row>
     <row r="873" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A873">
+      <c r="A873" s="4">
         <v>42308.540230447397</v>
       </c>
       <c r="B873" s="1">
@@ -7372,7 +7375,7 @@
       </c>
     </row>
     <row r="874" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A874">
+      <c r="A874" s="4">
         <v>42308.542816092297</v>
       </c>
       <c r="B874" s="1">
@@ -7380,7 +7383,7 @@
       </c>
     </row>
     <row r="875" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A875">
+      <c r="A875" s="4">
         <v>42308.543919080999</v>
       </c>
       <c r="B875" s="1">
@@ -7388,7 +7391,7 @@
       </c>
     </row>
     <row r="876" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A876">
+      <c r="A876" s="4">
         <v>42308.551974835304</v>
       </c>
       <c r="B876" s="1">
@@ -7396,7 +7399,7 @@
       </c>
     </row>
     <row r="877" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A877">
+      <c r="A877" s="4">
         <v>42308.576313480298</v>
       </c>
       <c r="B877" s="1">
@@ -7404,7 +7407,7 @@
       </c>
     </row>
     <row r="878" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A878">
+      <c r="A878" s="4">
         <v>42308.583069671702</v>
       </c>
       <c r="B878" s="1">
@@ -7412,7 +7415,7 @@
       </c>
     </row>
     <row r="879" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A879">
+      <c r="A879" s="4">
         <v>42308.5834568551</v>
       </c>
       <c r="B879" s="1">
@@ -7420,7 +7423,7 @@
       </c>
     </row>
     <row r="880" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A880">
+      <c r="A880" s="4">
         <v>42308.597719800098</v>
       </c>
       <c r="B880" s="1">
@@ -7428,7 +7431,7 @@
       </c>
     </row>
     <row r="881" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A881">
+      <c r="A881" s="4">
         <v>42308.626453221397</v>
       </c>
       <c r="B881" s="1">
@@ -7436,7 +7439,7 @@
       </c>
     </row>
     <row r="882" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A882">
+      <c r="A882" s="4">
         <v>42308.630339076502</v>
       </c>
       <c r="B882" s="1">
@@ -7444,7 +7447,7 @@
       </c>
     </row>
     <row r="883" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A883">
+      <c r="A883" s="4">
         <v>42308.648349253999</v>
       </c>
       <c r="B883" s="1">
@@ -7452,7 +7455,7 @@
       </c>
     </row>
     <row r="884" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A884">
+      <c r="A884" s="4">
         <v>42308.6615928385</v>
       </c>
       <c r="B884" s="1">
@@ -7460,7 +7463,7 @@
       </c>
     </row>
     <row r="885" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A885">
+      <c r="A885" s="4">
         <v>42308.663525863703</v>
       </c>
       <c r="B885" s="1">
@@ -7468,7 +7471,7 @@
       </c>
     </row>
     <row r="886" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A886">
+      <c r="A886" s="4">
         <v>42308.684744214697</v>
       </c>
       <c r="B886" s="1">
@@ -7476,7 +7479,7 @@
       </c>
     </row>
     <row r="887" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A887">
+      <c r="A887" s="4">
         <v>42308.691523498303</v>
       </c>
       <c r="B887" s="1">
@@ -7484,7 +7487,7 @@
       </c>
     </row>
     <row r="888" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A888">
+      <c r="A888" s="4">
         <v>42308.704011058398</v>
       </c>
       <c r="B888" s="1">
@@ -7492,7 +7495,7 @@
       </c>
     </row>
     <row r="889" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A889">
+      <c r="A889" s="4">
         <v>42308.728840715201</v>
       </c>
       <c r="B889" s="1">
@@ -7500,7 +7503,7 @@
       </c>
     </row>
     <row r="890" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A890">
+      <c r="A890" s="4">
         <v>42308.729914329997</v>
       </c>
       <c r="B890" s="1">
@@ -7508,7 +7511,7 @@
       </c>
     </row>
     <row r="891" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A891">
+      <c r="A891" s="4">
         <v>42308.734387914803</v>
       </c>
       <c r="B891" s="1">
@@ -7516,7 +7519,7 @@
       </c>
     </row>
     <row r="892" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A892">
+      <c r="A892" s="4">
         <v>42308.7425196185</v>
       </c>
       <c r="B892" s="1">
@@ -7524,7 +7527,7 @@
       </c>
     </row>
     <row r="893" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A893">
+      <c r="A893" s="4">
         <v>42308.745858340197</v>
       </c>
       <c r="B893" s="1">
@@ -7532,7 +7535,7 @@
       </c>
     </row>
     <row r="894" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A894">
+      <c r="A894" s="4">
         <v>42308.776517215199</v>
       </c>
       <c r="B894" s="1">
@@ -7540,7 +7543,7 @@
       </c>
     </row>
     <row r="895" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A895">
+      <c r="A895" s="4">
         <v>42308.777779371499</v>
       </c>
       <c r="B895" s="1">
@@ -7548,7 +7551,7 @@
       </c>
     </row>
     <row r="896" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A896">
+      <c r="A896" s="4">
         <v>42308.785106663898</v>
       </c>
       <c r="B896" s="1">
@@ -7556,7 +7559,7 @@
       </c>
     </row>
     <row r="897" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A897">
+      <c r="A897" s="4">
         <v>42308.786675290597</v>
       </c>
       <c r="B897" s="1">
@@ -7564,7 +7567,7 @@
       </c>
     </row>
     <row r="898" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A898">
+      <c r="A898" s="4">
         <v>42308.788746696497</v>
       </c>
       <c r="B898" s="1">
@@ -7572,7 +7575,7 @@
       </c>
     </row>
     <row r="899" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A899">
+      <c r="A899" s="4">
         <v>42308.7891906859</v>
       </c>
       <c r="B899" s="1">
@@ -7580,7 +7583,7 @@
       </c>
     </row>
     <row r="900" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A900">
+      <c r="A900" s="4">
         <v>42308.802614918997</v>
       </c>
       <c r="B900" s="1">
@@ -7588,7 +7591,7 @@
       </c>
     </row>
     <row r="901" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A901">
+      <c r="A901" s="4">
         <v>42308.806873135502</v>
       </c>
       <c r="B901" s="1">
@@ -7596,7 +7599,7 @@
       </c>
     </row>
     <row r="902" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A902">
+      <c r="A902" s="4">
         <v>42308.808503932698</v>
       </c>
       <c r="B902" s="1">
@@ -7604,7 +7607,7 @@
       </c>
     </row>
     <row r="903" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A903">
+      <c r="A903" s="4">
         <v>42308.810115213899</v>
       </c>
       <c r="B903" s="1">
@@ -7612,7 +7615,7 @@
       </c>
     </row>
     <row r="904" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A904">
+      <c r="A904" s="4">
         <v>42308.811514433</v>
       </c>
       <c r="B904" s="1">
@@ -7620,7 +7623,7 @@
       </c>
     </row>
     <row r="905" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A905">
+      <c r="A905" s="4">
         <v>42308.820830206299</v>
       </c>
       <c r="B905" s="1">
@@ -7628,7 +7631,7 @@
       </c>
     </row>
     <row r="906" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A906">
+      <c r="A906" s="4">
         <v>42308.8415152866</v>
       </c>
       <c r="B906" s="1">
@@ -7636,7 +7639,7 @@
       </c>
     </row>
     <row r="907" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A907">
+      <c r="A907" s="4">
         <v>42308.849614906198</v>
       </c>
       <c r="B907" s="1">
@@ -7644,7 +7647,7 @@
       </c>
     </row>
     <row r="908" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A908">
+      <c r="A908" s="4">
         <v>42308.853287679398</v>
       </c>
       <c r="B908" s="1">
@@ -7652,7 +7655,7 @@
       </c>
     </row>
     <row r="909" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A909">
+      <c r="A909" s="4">
         <v>42308.854774917803</v>
       </c>
       <c r="B909" s="1">
@@ -7660,7 +7663,7 @@
       </c>
     </row>
     <row r="910" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A910">
+      <c r="A910" s="4">
         <v>42308.864309938399</v>
       </c>
       <c r="B910" s="1">
@@ -7668,7 +7671,7 @@
       </c>
     </row>
     <row r="911" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A911">
+      <c r="A911" s="4">
         <v>42308.880411095401</v>
       </c>
       <c r="B911" s="1">
@@ -7676,7 +7679,7 @@
       </c>
     </row>
     <row r="912" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A912">
+      <c r="A912" s="4">
         <v>42308.919673053599</v>
       </c>
       <c r="B912" s="1">
@@ -7684,7 +7687,7 @@
       </c>
     </row>
     <row r="913" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A913">
+      <c r="A913" s="4">
         <v>42308.929949905301</v>
       </c>
       <c r="B913" s="1">
@@ -7692,7 +7695,7 @@
       </c>
     </row>
     <row r="914" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A914">
+      <c r="A914" s="4">
         <v>42308.931626146303</v>
       </c>
       <c r="B914" s="1">
@@ -7700,7 +7703,7 @@
       </c>
     </row>
     <row r="915" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A915">
+      <c r="A915" s="4">
         <v>42308.958123499302</v>
       </c>
       <c r="B915" s="1">
@@ -7708,7 +7711,7 @@
       </c>
     </row>
     <row r="916" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A916">
+      <c r="A916" s="4">
         <v>42308.971835878998</v>
       </c>
       <c r="B916" s="1">
@@ -7716,7 +7719,7 @@
       </c>
     </row>
     <row r="917" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A917">
+      <c r="A917" s="4">
         <v>42308.975740113703</v>
       </c>
       <c r="B917" s="1">
@@ -7724,7 +7727,7 @@
       </c>
     </row>
     <row r="918" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A918">
+      <c r="A918" s="4">
         <v>42308.990134305401</v>
       </c>
       <c r="B918" s="1">
@@ -7732,7 +7735,7 @@
       </c>
     </row>
     <row r="919" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A919">
+      <c r="A919" s="4">
         <v>42308.990851367897</v>
       </c>
       <c r="B919" s="1">
@@ -7740,7 +7743,7 @@
       </c>
     </row>
     <row r="920" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A920">
+      <c r="A920" s="4">
         <v>42308.999738271799</v>
       </c>
       <c r="B920" s="1">
@@ -7748,7 +7751,7 @@
       </c>
     </row>
     <row r="921" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A921">
+      <c r="A921" s="4">
         <v>42309.004507002101</v>
       </c>
       <c r="B921" s="1">
@@ -7756,7 +7759,7 @@
       </c>
     </row>
     <row r="922" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A922">
+      <c r="A922" s="4">
         <v>42309.020307393097</v>
       </c>
       <c r="B922" s="1">
@@ -7764,7 +7767,7 @@
       </c>
     </row>
     <row r="923" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A923">
+      <c r="A923" s="4">
         <v>42309.032377907002</v>
       </c>
       <c r="B923" s="1">
@@ -7772,7 +7775,7 @@
       </c>
     </row>
     <row r="924" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A924">
+      <c r="A924" s="4">
         <v>42309.0337625928</v>
       </c>
       <c r="B924" s="1">
@@ -7780,7 +7783,7 @@
       </c>
     </row>
     <row r="925" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A925">
+      <c r="A925" s="4">
         <v>42309.050805167899</v>
       </c>
       <c r="B925" s="1">
@@ -7788,7 +7791,7 @@
       </c>
     </row>
     <row r="926" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A926">
+      <c r="A926" s="4">
         <v>42309.059383077598</v>
       </c>
       <c r="B926" s="1">
@@ -7796,7 +7799,7 @@
       </c>
     </row>
     <row r="927" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A927">
+      <c r="A927" s="4">
         <v>42309.063202408302</v>
       </c>
       <c r="B927" s="1">
@@ -7804,7 +7807,7 @@
       </c>
     </row>
     <row r="928" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A928">
+      <c r="A928" s="4">
         <v>42309.069101163601</v>
       </c>
       <c r="B928" s="1">
@@ -7812,7 +7815,7 @@
       </c>
     </row>
     <row r="929" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A929">
+      <c r="A929" s="4">
         <v>42309.085456832399</v>
       </c>
       <c r="B929" s="1">
@@ -7820,7 +7823,7 @@
       </c>
     </row>
     <row r="930" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A930">
+      <c r="A930" s="4">
         <v>42309.110522407304</v>
       </c>
       <c r="B930" s="1">
@@ -7828,7 +7831,7 @@
       </c>
     </row>
     <row r="931" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A931">
+      <c r="A931" s="4">
         <v>42309.1411012444</v>
       </c>
       <c r="B931" s="1">
@@ -7836,7 +7839,7 @@
       </c>
     </row>
     <row r="932" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A932">
+      <c r="A932" s="4">
         <v>42309.1536571123</v>
       </c>
       <c r="B932" s="1">
@@ -7844,7 +7847,7 @@
       </c>
     </row>
     <row r="933" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A933">
+      <c r="A933" s="4">
         <v>42309.163794409898</v>
       </c>
       <c r="B933" s="1">
@@ -7852,7 +7855,7 @@
       </c>
     </row>
     <row r="934" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A934">
+      <c r="A934" s="4">
         <v>42309.169215690097</v>
       </c>
       <c r="B934" s="1">
@@ -7860,7 +7863,7 @@
       </c>
     </row>
     <row r="935" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A935">
+      <c r="A935" s="4">
         <v>42309.206468259203</v>
       </c>
       <c r="B935" s="1">
@@ -7868,7 +7871,7 @@
       </c>
     </row>
     <row r="936" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A936">
+      <c r="A936" s="4">
         <v>42309.250061943298</v>
       </c>
       <c r="B936" s="1">
@@ -7876,7 +7879,7 @@
       </c>
     </row>
     <row r="937" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A937">
+      <c r="A937" s="4">
         <v>42309.259716205801</v>
       </c>
       <c r="B937" s="1">
@@ -7884,7 +7887,7 @@
       </c>
     </row>
     <row r="938" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A938">
+      <c r="A938" s="4">
         <v>42309.261632723399</v>
       </c>
       <c r="B938" s="1">
@@ -7892,7 +7895,7 @@
       </c>
     </row>
     <row r="939" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A939">
+      <c r="A939" s="4">
         <v>42309.300008947299</v>
       </c>
       <c r="B939" s="1">
@@ -7900,7 +7903,7 @@
       </c>
     </row>
     <row r="940" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A940">
+      <c r="A940" s="4">
         <v>42309.323736211503</v>
       </c>
       <c r="B940" s="1">
@@ -7908,7 +7911,7 @@
       </c>
     </row>
     <row r="941" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A941">
+      <c r="A941" s="4">
         <v>42309.325359199502</v>
       </c>
       <c r="B941" s="1">
@@ -7916,7 +7919,7 @@
       </c>
     </row>
     <row r="942" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A942">
+      <c r="A942" s="4">
         <v>42309.337489243502</v>
       </c>
       <c r="B942" s="1">
@@ -7924,7 +7927,7 @@
       </c>
     </row>
     <row r="943" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A943">
+      <c r="A943" s="4">
         <v>42309.339409756401</v>
       </c>
       <c r="B943" s="1">
@@ -7932,7 +7935,7 @@
       </c>
     </row>
     <row r="944" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A944">
+      <c r="A944" s="4">
         <v>42309.3410922978</v>
       </c>
       <c r="B944" s="1">
@@ -7940,7 +7943,7 @@
       </c>
     </row>
     <row r="945" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A945">
+      <c r="A945" s="4">
         <v>42309.372521078498</v>
       </c>
       <c r="B945" s="1">
@@ -7948,7 +7951,7 @@
       </c>
     </row>
     <row r="946" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A946">
+      <c r="A946" s="4">
         <v>42309.428332588403</v>
       </c>
       <c r="B946" s="1">
@@ -7956,7 +7959,7 @@
       </c>
     </row>
     <row r="947" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A947">
+      <c r="A947" s="4">
         <v>42309.450367685997</v>
       </c>
       <c r="B947" s="1">
@@ -7964,7 +7967,7 @@
       </c>
     </row>
     <row r="948" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A948">
+      <c r="A948" s="4">
         <v>42309.462268564101</v>
       </c>
       <c r="B948" s="1">
@@ -7972,7 +7975,7 @@
       </c>
     </row>
     <row r="949" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A949">
+      <c r="A949" s="4">
         <v>42309.463118721898</v>
       </c>
       <c r="B949" s="1">
@@ -7980,7 +7983,7 @@
       </c>
     </row>
     <row r="950" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A950">
+      <c r="A950" s="4">
         <v>42309.475906633503</v>
       </c>
       <c r="B950" s="1">
@@ -7988,7 +7991,7 @@
       </c>
     </row>
     <row r="951" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A951">
+      <c r="A951" s="4">
         <v>42309.480008923398</v>
       </c>
       <c r="B951" s="1">
@@ -7996,7 +7999,7 @@
       </c>
     </row>
     <row r="952" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A952">
+      <c r="A952" s="4">
         <v>42309.531161030798</v>
       </c>
       <c r="B952" s="1">
@@ -8004,7 +8007,7 @@
       </c>
     </row>
     <row r="953" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A953">
+      <c r="A953" s="4">
         <v>42309.5329582087</v>
       </c>
       <c r="B953" s="1">
@@ -8012,7 +8015,7 @@
       </c>
     </row>
     <row r="954" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A954">
+      <c r="A954" s="4">
         <v>42309.5335465112</v>
       </c>
       <c r="B954" s="1">
@@ -8020,7 +8023,7 @@
       </c>
     </row>
     <row r="955" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A955">
+      <c r="A955" s="4">
         <v>42309.538685446998</v>
       </c>
       <c r="B955" s="1">
@@ -8028,7 +8031,7 @@
       </c>
     </row>
     <row r="956" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A956">
+      <c r="A956" s="4">
         <v>42309.542157077703</v>
       </c>
       <c r="B956" s="1">
@@ -8036,7 +8039,7 @@
       </c>
     </row>
     <row r="957" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A957">
+      <c r="A957" s="4">
         <v>42309.5430869708</v>
       </c>
       <c r="B957" s="1">
@@ -8044,7 +8047,7 @@
       </c>
     </row>
     <row r="958" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A958">
+      <c r="A958" s="4">
         <v>42309.5445011888</v>
       </c>
       <c r="B958" s="1">
@@ -8052,7 +8055,7 @@
       </c>
     </row>
     <row r="959" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A959">
+      <c r="A959" s="4">
         <v>42309.5452352992</v>
       </c>
       <c r="B959" s="1">
@@ -8060,7 +8063,7 @@
       </c>
     </row>
     <row r="960" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A960">
+      <c r="A960" s="4">
         <v>42309.559945456</v>
       </c>
       <c r="B960" s="1">
@@ -8068,7 +8071,7 @@
       </c>
     </row>
     <row r="961" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A961">
+      <c r="A961" s="4">
         <v>42309.573657314198</v>
       </c>
       <c r="B961" s="1">
@@ -8076,7 +8079,7 @@
       </c>
     </row>
     <row r="962" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A962">
+      <c r="A962" s="4">
         <v>42309.595034167003</v>
       </c>
       <c r="B962" s="1">
@@ -8084,7 +8087,7 @@
       </c>
     </row>
     <row r="963" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A963">
+      <c r="A963" s="4">
         <v>42309.596054039699</v>
       </c>
       <c r="B963" s="1">
@@ -8092,7 +8095,7 @@
       </c>
     </row>
     <row r="964" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A964">
+      <c r="A964" s="4">
         <v>42309.598688099497</v>
       </c>
       <c r="B964" s="1">
@@ -8100,7 +8103,7 @@
       </c>
     </row>
     <row r="965" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A965">
+      <c r="A965" s="4">
         <v>42309.603194001298</v>
       </c>
       <c r="B965" s="1">
@@ -8108,7 +8111,7 @@
       </c>
     </row>
     <row r="966" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A966">
+      <c r="A966" s="4">
         <v>42309.615177357198</v>
       </c>
       <c r="B966" s="1">
@@ -8116,7 +8119,7 @@
       </c>
     </row>
     <row r="967" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A967">
+      <c r="A967" s="4">
         <v>42309.625309895797</v>
       </c>
       <c r="B967" s="1">
@@ -8124,7 +8127,7 @@
       </c>
     </row>
     <row r="968" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A968">
+      <c r="A968" s="4">
         <v>42309.626806871202</v>
       </c>
       <c r="B968" s="1">
@@ -8132,7 +8135,7 @@
       </c>
     </row>
     <row r="969" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A969">
+      <c r="A969" s="4">
         <v>42309.634144775999</v>
       </c>
       <c r="B969" s="1">
@@ -8140,7 +8143,7 @@
       </c>
     </row>
     <row r="970" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A970">
+      <c r="A970" s="4">
         <v>42309.641793700699</v>
       </c>
       <c r="B970" s="1">
@@ -8148,7 +8151,7 @@
       </c>
     </row>
     <row r="971" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A971">
+      <c r="A971" s="4">
         <v>42309.661838599102</v>
       </c>
       <c r="B971" s="1">
@@ -8156,7 +8159,7 @@
       </c>
     </row>
     <row r="972" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A972">
+      <c r="A972" s="4">
         <v>42309.669989953698</v>
       </c>
       <c r="B972" s="1">
@@ -8164,7 +8167,7 @@
       </c>
     </row>
     <row r="973" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A973">
+      <c r="A973" s="4">
         <v>42309.685556997203</v>
       </c>
       <c r="B973" s="1">
@@ -8172,7 +8175,7 @@
       </c>
     </row>
     <row r="974" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A974">
+      <c r="A974" s="4">
         <v>42309.688666050097</v>
       </c>
       <c r="B974" s="1">
@@ -8180,7 +8183,7 @@
       </c>
     </row>
     <row r="975" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A975">
+      <c r="A975" s="4">
         <v>42309.692884256998</v>
       </c>
       <c r="B975" s="1">
@@ -8188,7 +8191,7 @@
       </c>
     </row>
     <row r="976" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A976">
+      <c r="A976" s="4">
         <v>42309.697745248799</v>
       </c>
       <c r="B976" s="1">
@@ -8196,7 +8199,7 @@
       </c>
     </row>
     <row r="977" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A977">
+      <c r="A977" s="4">
         <v>42309.707853931497</v>
       </c>
       <c r="B977" s="1">
@@ -8204,7 +8207,7 @@
       </c>
     </row>
     <row r="978" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A978">
+      <c r="A978" s="4">
         <v>42309.711396035498</v>
       </c>
       <c r="B978" s="1">
@@ -8212,7 +8215,7 @@
       </c>
     </row>
     <row r="979" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A979">
+      <c r="A979" s="4">
         <v>42309.762222655001</v>
       </c>
       <c r="B979" s="1">
@@ -8220,7 +8223,7 @@
       </c>
     </row>
     <row r="980" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A980">
+      <c r="A980" s="4">
         <v>42309.766228976703</v>
       </c>
       <c r="B980" s="1">
@@ -8228,7 +8231,7 @@
       </c>
     </row>
     <row r="981" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A981">
+      <c r="A981" s="4">
         <v>42309.777192003603</v>
       </c>
       <c r="B981" s="1">
@@ -8236,7 +8239,7 @@
       </c>
     </row>
     <row r="982" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A982">
+      <c r="A982" s="4">
         <v>42309.803357647397</v>
       </c>
       <c r="B982" s="1">
@@ -8244,7 +8247,7 @@
       </c>
     </row>
     <row r="983" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A983">
+      <c r="A983" s="4">
         <v>42309.808579745601</v>
       </c>
       <c r="B983" s="1">
@@ -8252,7 +8255,7 @@
       </c>
     </row>
     <row r="984" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A984">
+      <c r="A984" s="4">
         <v>42309.817234629103</v>
       </c>
       <c r="B984" s="1">
@@ -8260,7 +8263,7 @@
       </c>
     </row>
     <row r="985" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A985">
+      <c r="A985" s="4">
         <v>42309.8244759464</v>
       </c>
       <c r="B985" s="1">
@@ -8268,7 +8271,7 @@
       </c>
     </row>
     <row r="986" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A986">
+      <c r="A986" s="4">
         <v>42309.8342851903</v>
       </c>
       <c r="B986" s="1">
@@ -8276,7 +8279,7 @@
       </c>
     </row>
     <row r="987" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A987">
+      <c r="A987" s="4">
         <v>42309.836131826101</v>
       </c>
       <c r="B987" s="1">
@@ -8284,7 +8287,7 @@
       </c>
     </row>
     <row r="988" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A988">
+      <c r="A988" s="4">
         <v>42309.840001215402</v>
       </c>
       <c r="B988" s="1">
@@ -8292,7 +8295,7 @@
       </c>
     </row>
     <row r="989" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A989">
+      <c r="A989" s="4">
         <v>42309.842376805202</v>
       </c>
       <c r="B989" s="1">
@@ -8300,7 +8303,7 @@
       </c>
     </row>
     <row r="990" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A990">
+      <c r="A990" s="4">
         <v>42309.866905733303</v>
       </c>
       <c r="B990" s="1">
@@ -8308,7 +8311,7 @@
       </c>
     </row>
     <row r="991" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A991">
+      <c r="A991" s="4">
         <v>42309.867041329198</v>
       </c>
       <c r="B991" s="1">
@@ -8316,7 +8319,7 @@
       </c>
     </row>
     <row r="992" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A992">
+      <c r="A992" s="4">
         <v>42309.879385186199</v>
       </c>
       <c r="B992" s="1">
@@ -8324,7 +8327,7 @@
       </c>
     </row>
     <row r="993" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A993">
+      <c r="A993" s="4">
         <v>42309.908677112398</v>
       </c>
       <c r="B993" s="1">
@@ -8332,7 +8335,7 @@
       </c>
     </row>
     <row r="994" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A994">
+      <c r="A994" s="4">
         <v>42309.919544073397</v>
       </c>
       <c r="B994" s="1">
@@ -8340,7 +8343,7 @@
       </c>
     </row>
     <row r="995" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A995">
+      <c r="A995" s="4">
         <v>42309.920498064399</v>
       </c>
       <c r="B995" s="1">
@@ -8348,7 +8351,7 @@
       </c>
     </row>
     <row r="996" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A996">
+      <c r="A996" s="4">
         <v>42309.923089730299</v>
       </c>
       <c r="B996" s="1">
@@ -8356,7 +8359,7 @@
       </c>
     </row>
     <row r="997" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A997">
+      <c r="A997" s="4">
         <v>42309.923128454699</v>
       </c>
       <c r="B997" s="1">
@@ -8364,7 +8367,7 @@
       </c>
     </row>
     <row r="998" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A998">
+      <c r="A998" s="4">
         <v>42309.934390100803</v>
       </c>
       <c r="B998" s="1">
@@ -8372,7 +8375,7 @@
       </c>
     </row>
     <row r="999" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A999">
+      <c r="A999" s="4">
         <v>42309.9641231852</v>
       </c>
       <c r="B999" s="1">
@@ -8380,7 +8383,7 @@
       </c>
     </row>
     <row r="1000" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A1000">
+      <c r="A1000" s="4">
         <v>42309.982067280704</v>
       </c>
       <c r="B1000" s="1">
@@ -8388,7 +8391,7 @@
       </c>
     </row>
     <row r="1001" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A1001">
+      <c r="A1001" s="4">
         <v>42309.983137901203</v>
       </c>
       <c r="B1001" s="1">

--- a/DATA624/project_1/Waterflow_Pipe1.xlsx
+++ b/DATA624/project_1/Waterflow_Pipe1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/olivia/Documents/CUNY/CUNY_GITHUB_submissions/DATA624/project_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B835723-2D5F-B248-B95C-EA48FAE5E5F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34AAE628-2DD4-B646-A8D8-3C3685EB233E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3000" yWindow="6280" windowWidth="20500" windowHeight="7680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3880" yWindow="2740" windowWidth="20500" windowHeight="11720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Waterflow_Pipe1" sheetId="1" r:id="rId1"/>
